--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="620" customWidth="1" min="9" max="9"/>
+    <col width="618" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -544,157 +544,157 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Para Pizza Stamp Octogonal Nº25 c/ 25</t>
+          <t>Cerveja Lata 8x Heineken 269ml</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Stamp</t>
+          <t>Heineken</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>c/ 25</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CAIXA P/ PIZZA STAMP OCT. Nº25 C/ 25UND</t>
+          <t>CERVEJA HEINEKEN 8X269ML R$ 34,99</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>28.9</v>
+        <v>34.99</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Marmitex com Tampa Nº8 Wyda c/ 100</t>
+          <t>Cerveja Lata 12x Amstel 269ml</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Wyda</t>
+          <t>Amstel</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>c/ 100</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>MARMITEX WYDA Nº8 MÁQUINA C/ TAMPA C/ 100UND</t>
+          <t>CERVEJA AMSTEL 12X269ML R$ 34,99</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>45.9</v>
+        <v>34.99</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bobina Picotada 40x50cm Giopack 10kg</t>
+          <t>Refrigerante Fanta 2L</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Giopack</t>
+          <t>Fanta</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>BOBINA PICOTADA GIOPACK 40X50CM 10KG</t>
+          <t>FANTAS 2LT R$ 8,99</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -704,47 +704,47 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Achocolatado em Pó Toddy 750g</t>
+          <t>Energetico Monster Lata 473ml</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Toddy</t>
+          <t>Monster</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>473ml</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Achocolatado em Pó Toddy 750g</t>
+          <t>MONSTER 473ML R$ 9,99</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>16.99</v>
+        <v>9.99</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -754,97 +754,93 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Polpa de Acerola Ricaeli 1.02kg</t>
+          <t>Achocolatado em Pó Toddy 750g</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ricaeli</t>
+          <t>Toddy</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1.02kg</t>
+          <t>750g</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>POLPA RICAELI ACEROLA BARRA 1,02KG</t>
+          <t>TODDY 750G R$ 15,99</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>17.9</v>
+        <v>15.99</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795068826_18587301715067900_3736282338032078257_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzI4ODE4NzMzNjU0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kw9fDMjw_VwQ7kNvwE3DJAg&amp;_nc_oc=AdrJrccRDVkUXkf620KJ1WEy4EUkXgZDG0hExMEaFqgo5HqPHYejGnJYDmHZUwfaumM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLD6FONLiwBNpsDV1rjcUeekUPI3xnGHdAIIl0jmLKcbQ&amp;oe=6AB07C48</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Polpa de Fruta Acerola Ricaeli 1.02kg</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Ricaeli</t>
-        </is>
-      </c>
+          <t>Sobrecoxa de Frango kg</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1.02kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>POLPA RICAELI ACEROLA BARRA 1,02KG</t>
+          <t>COXA E SOBRECOXA DORSAL Kg R$ 5,99</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>17.9</v>
+        <v>5.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/794492536_18095987363531849_466674493406548250_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNDA3OTQ0NzU2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZPyG7ifrSDYQ7kNvwG6EIY4&amp;_nc_oc=AdrVuJGN_Q6671Z0J_WadyEAMV34F0S8918okGQv1h66chFXeMjiqMGnG9LhKxPtmgc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQIGQLWlrFEZDbhl4SfcADAXC_wRLzJJ-hR62pogj_1D6Q&amp;oe=6AB07C94</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -854,47 +850,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hambúrguer Carne Bovina Aves Perdigão 56g</t>
+          <t>Coxas Sobrecoxas de Frango Canção 1kg</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Canção</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>HAMBÚRGUER PERDIGÃO CARNE BOVINA E AVES 56G</t>
+          <t>Coxas Sobrecoxas Canção R$ 7,99 UN</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1.39</v>
+        <v>7.99</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -904,43 +900,47 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Dorso de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>Frango Passarinho Congelado Iqf Bello 800g</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>DORSO DE FRANGO KG 4,99</t>
+          <t>Frango Passarinho Bello Pacote Iqf 800gr R$ 9,59 UN</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>4.99</v>
+        <v>9.59</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -950,43 +950,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Pescoço de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>Coxinha de Asa Congelada Iqf Bello 800g</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>PESCOÇO DE FRANGO KG</t>
+          <t>Coxinhas De Asa Bello Pacote Iqf 800gr R$ 10,99 UN</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -996,36 +1000,40 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pé de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
+          <t>Frango Passarinho Sadia 1kg</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>PÉ DE FRANGO KG 6,99</t>
+          <t>Frango a Passarinho Sadia Zip 1 Kg</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.99</v>
+        <v>13.98</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
@@ -1042,43 +1050,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Moela de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>Filé de Peito de Frango Avenorte kg</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Avenorte</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO KG 11,99</t>
+          <t>FILÉ DE PEITO AVENORTE 800GR R$ 13,99</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1088,47 +1100,47 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Sadia kg</t>
+          <t>Filé de Sassami Bello 800g</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Sadia Pct. 1 Kg 13,99</t>
+          <t>Filé Sassami Bello Zip 800g</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>13.99</v>
+        <v>14.78</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1138,10 +1150,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Língua Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Miúdos Bovinos Figado Mocotó Sulbeef Kg</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Sulbeef</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1149,32 +1165,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>LÍNGUA BOVINO KG</t>
+          <t>Miúdos Bovino Figado E Mocotó Sulbeef R$ 12,99 KG</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1184,7 +1200,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Coração Bovino Kg</t>
+          <t>Músculo Bovino c/ Osso kg</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1195,25 +1211,25 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO Kg R$ 7,49</t>
+          <t>MÚSCULO C/ OSSO KG</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>7.49</v>
+        <v>17.99</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1246,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Coração Bovino Kg</t>
+          <t>Acém Bovino c/ Osso kg</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1241,32 +1257,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO KG</t>
+          <t>ACÉM C/ OSSO KG</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1276,7 +1292,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Ossobuco Bovino Kg</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
@@ -1287,32 +1303,32 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>MOCOTÓ BOVINO KG</t>
+          <t>OSSOBUCO Kg R$ 19,99</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>8.99</v>
+        <v>19.99</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/795946636_18095987354531849_1912901089651838506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNTQ3MjEzNzI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JsgZDWGmOPoQ7kNvwEa525y&amp;_nc_oc=Adrbj00xgVvj7eUEXS7JbqZL4d2rBNS_rjM98V83bVZAgnLCpdAWCPov9AOc4Rx0Px8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQJcL0tu4f2vjeCPB62MkNKIsd3_5El9BH24hnXQgY6NFQ&amp;oe=6AB097D7</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1322,7 +1338,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Acém Bovino c/ Osso kg</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1333,32 +1349,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Kg R$ 8,99</t>
+          <t>ACEM C/OSSO Kg R$ 19,99</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.99</v>
+        <v>19.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/794492536_18095987363531849_466674493406548250_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNDA3OTQ0NzU2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZPyG7ifrSDYQ7kNvwG6EIY4&amp;_nc_oc=AdrVuJGN_Q6671Z0J_WadyEAMV34F0S8918okGQv1h66chFXeMjiqMGnG9LhKxPtmgc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQIGQLWlrFEZDbhl4SfcADAXC_wRLzJJ-hR62pogj_1D6Q&amp;oe=6AB07C94</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1368,7 +1384,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Acém Bovino c/ Osso kg</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -1379,32 +1395,32 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>MOCOTÓ BOVINO Kg R$ 8,99</t>
+          <t>Acém com Osso Kg</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>8.99</v>
+        <v>22.48</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1414,7 +1430,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Carne Moída Bovina kg</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1425,25 +1441,25 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>CARNE MOÍDA R$ 22,99 Kg</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9.99</v>
+        <v>22.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811437725_18095831099531849_3017443872855645947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTIwNDYwOTk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=tPP_L67hhEkQ7kNvwGnH9O3&amp;_nc_oc=Adrr-CdpxmFC5219FNATropxDMMQAANtNOrMmlFkH8kK_Rz6w2QHInsLw2Y6SAK0Y7A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQKt767kGdRqx1c_9hRDkC4d-bLGKY0P-43dKUk9hixLzQ&amp;oe=6AB07EDC</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1476,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Paleta Bovina kg</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -1471,32 +1487,32 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>FÍGADO BOVINO KG</t>
+          <t>PALETA C/ OSSO KG</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>9.99</v>
+        <v>23.99</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809202059_18586780822067900_5792794545078375602_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4NTk3ODc4Mzg2NjA3ODAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1GDrV_LQlXcQ7kNvwGmB2w6&amp;_nc_oc=AdocF3DI9527HHx2h_hKskYAF-yTTsSi1TLB9ZrD4b9Y1Dtou1MBzNk1jZJpPedzCJU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLD_tmL7DUpcHEXlkzs3R1FMYlucQQfoQnhY5qQDWlRJA&amp;oe=6AAF3EB7</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1506,7 +1522,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Recorte Bovino Kg</t>
+          <t>Paleta Bovina kg</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1517,25 +1533,25 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>RECORTE BOVINO KG 9,99</t>
+          <t>PALETA C/ OSSO Kg R$ 23,99</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.99</v>
+        <v>23.99</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/794492536_18095987363531849_466674493406548250_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNDA3OTQ0NzU2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZPyG7ifrSDYQ7kNvwG6EIY4&amp;_nc_oc=AdrVuJGN_Q6671Z0J_WadyEAMV34F0S8918okGQv1h66chFXeMjiqMGnG9LhKxPtmgc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQIGQLWlrFEZDbhl4SfcADAXC_wRLzJJ-hR62pogj_1D6Q&amp;oe=6AB07C94</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1568,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Paleta Bovina kg</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -1563,32 +1579,32 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg R$ 9,99</t>
+          <t>Paleta com Osso Kg</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9.99</v>
+        <v>24.48</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1598,7 +1614,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Ponta de Peito com Osso Kg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1609,32 +1625,32 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg R$ 9,99</t>
+          <t>PONTA DE PEITO C/ OSSO KG</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1644,7 +1660,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Coração Bovino Kg</t>
+          <t>Filé de Agulha Kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1655,32 +1671,32 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Coração Bovino Kg R$ 9,99</t>
+          <t>FILÉ DE AGULHA KG</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1690,7 +1706,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Filé de Agulha Kg</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1701,25 +1717,25 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino - Kg 9,99</t>
+          <t>FILÉ AGULHA Kg R$ 26,99</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.99</v>
+        <v>26.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/794492536_18095987363531849_466674493406548250_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNDA3OTQ0NzU2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZPyG7ifrSDYQ7kNvwG6EIY4&amp;_nc_oc=AdrVuJGN_Q6671Z0J_WadyEAMV34F0S8918okGQv1h66chFXeMjiqMGnG9LhKxPtmgc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQIGQLWlrFEZDbhl4SfcADAXC_wRLzJJ-hR62pogj_1D6Q&amp;oe=6AB07C94</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1752,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Contrafilé Bovino kg</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -1747,32 +1763,32 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO Kg R$ 9,99</t>
+          <t>BISTECA DO C. FILÉ R$ 34,99 Kg</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>9.99</v>
+        <v>34.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811437725_18095831099531849_3017443872855645947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTIwNDYwOTk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=tPP_L67hhEkQ7kNvwGnH9O3&amp;_nc_oc=Adrr-CdpxmFC5219FNATropxDMMQAANtNOrMmlFkH8kK_Rz6w2QHInsLw2Y6SAK0Y7A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQKt767kGdRqx1c_9hRDkC4d-bLGKY0P-43dKUk9hixLzQ&amp;oe=6AB07EDC</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1782,7 +1798,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Coxão Mole Bovino kg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1793,25 +1809,25 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino - Kg 10,99</t>
+          <t>Capa do Coxão Mole Kg</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>10.99</v>
+        <v>36.98</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1844,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Coxão Duro Bovino kg</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -1839,32 +1855,32 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>FÍGADO BOVINO Kg R$ 10,99</t>
+          <t>COXÃO DURO Kg R$ 36,99</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>10.99</v>
+        <v>36.99</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/795946636_18095987354531849_1912901089651838506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNTQ3MjEzNzI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JsgZDWGmOPoQ7kNvwEa525y&amp;_nc_oc=Adrbj00xgVvj7eUEXS7JbqZL4d2rBNS_rjM98V83bVZAgnLCpdAWCPov9AOc4Rx0Px8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQJcL0tu4f2vjeCPB62MkNKIsd3_5El9BH24hnXQgY6NFQ&amp;oe=6AB097D7</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1874,10 +1890,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Coxão Duro Bovino Sulbeef kg</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sulbeef</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1885,32 +1905,32 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg 12,99</t>
+          <t>Coxão Duro E Cupim Sulbeef R$ 38,99 KG</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12.99</v>
+        <v>38.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1920,7 +1940,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ossobuco Bovino Kg</t>
+          <t>Coxão Duro Bovino kg</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -1931,25 +1951,25 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>OSSOBUCO Kg R$ 19,99</t>
+          <t>Coxão Duro Kg</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>19.99</v>
+        <v>42.98</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1986,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Carne Moída Bovina kg</t>
+          <t>Coxão Mole Bovino kg</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1977,32 +1997,32 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Carne Moída Kg R$ 22,99</t>
+          <t>Coxão Mole Kg</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>22.99</v>
+        <v>46.98</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2012,10 +2032,14 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída Bovina kg</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
+          <t>Picanha Bovina Sulbeef kg</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Sulbeef</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2023,45 +2047,49 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>CARNE MOÍDA R$ 22,99 Kg</t>
+          <t>Filé Mingnon/ Picanha Sulbeef R$ 64,99 KG</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>22.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811437725_18095831099531849_3017443872855645947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTIwNDYwOTk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=tPP_L67hhEkQ7kNvwEo4rrH&amp;_nc_oc=Adp1UltyP2m3SR1Shmrs9LA6l7ru6hpdZYjvjC_gYHGh6gwRPo0DwVJe0cj-kvcDJrY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJQDALm69_D9BUQti30T2OcgIg7a-eh0SJSiqgffEV0Tw&amp;oe=6AAF2D5C</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Tambatinga Sem Escamas Dona Fresca Kg</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Dona Fresca</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2069,170 +2097,178 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina para Panela Kg R$ 24,99</t>
+          <t>Tambatinga Sem Escamas Dona Fresca R$ 22,99 KG</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>24.99</v>
+        <v>22.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/809409702_18197653978382122_174505750771845123_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NjAwNzkyNDY0OTc3NDQzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eDZNaLI6KE4Q7kNvwFORsP9&amp;_nc_oc=AdrSzC6hXuuRR-hKMsiNcRXFYurb-NnBHmLlfG8sIt3iBlhZkRw1MphfrtOH8lMM4C8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=DDIuk0Qv9ZyInMz8tmSWtQ&amp;_nc_ss=7a22e&amp;oh=00_AQIekdsCG0KtcSOs5MI7uNknuB_t0UbQHlS2N3Yxo8G23w&amp;oe=6AAF3119</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRJRa0pE1l/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Rabo Bovino Kg</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
+          <t>Filé de Tilápia com Pele Bello 800g</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>RABO BOVINO Kg R$ 27,99</t>
+          <t>Filé De Tilápia Com Pele Bello Pct 800g R$ 24,99 UN</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>27.99</v>
+        <v>24.99</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+          <t>Prato Saudável Filé de Peixe Mach Foods</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Mach Foods</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>BISTECA DO C. FILÉ R$ 34,99 Kg</t>
+          <t>Prato Saudável c/ Filé de Peixe</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>34.99</v>
+        <v>37.9</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811437725_18095831099531849_3017443872855645947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTIwNDYwOTk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=tPP_L67hhEkQ7kNvwEo4rrH&amp;_nc_oc=Adp1UltyP2m3SR1Shmrs9LA6l7ru6hpdZYjvjC_gYHGh6gwRPo0DwVJe0cj-kvcDJrY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJQDALm69_D9BUQti30T2OcgIg7a-eh0SJSiqgffEV0Tw&amp;oe=6AAF2D5C</t>
+          <t>https://scontent-ord5-1.cdninstagram.com/v/t39.30808-6/802976447_1376651451221479_8395420181839414581_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzA3ODkwMjQ5MzA1MjY1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZsH16uoBEOAQ7kNvwEPju--&amp;_nc_oc=Ado1uk1u4e5z3wOT6xOF4P28Uab3ItuGHw_eGsOPYPKU0je7CoNV0Gc-0NLNejqxC7Y-8pCm76Py0u7e2IbUUsaq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=7XW8mKzYSOmB1t3eX-9yuw&amp;_nc_ss=7a22e&amp;oh=00_AQL8xvEhqFmkXMnJADrUHjlfoP25vjndUYeCaVQwICnokA&amp;oe=6AB082A9</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdU8yYMDSZP/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Patinho Bovino kg</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
+          <t>Pintado Inteiro Esvicerado Dona Fresca 1kg</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Dona Fresca</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>PATINHO BOVINO Kg R$ 37,99</t>
+          <t>Pintado Inteiro Esvicerado Dona Fresca R$ 39,99 KG</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>37.99</v>
+        <v>39.99</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2242,47 +2278,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Hambúrguer Perdigão Carne Bovina Aves 56g</t>
+          <t>Salsicha Hot Dog Bello kg</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>56g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>HAMBÚRGUER PERDIGÃO CARNE BOVINA E AVES 56G</t>
+          <t>SALSICHA BELLO Kg R$ 7,99</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1.39</v>
+        <v>7.99</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/795946636_18095987354531849_1912901089651838506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNTQ3MjEzNzI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JsgZDWGmOPoQ7kNvwEa525y&amp;_nc_oc=Adrbj00xgVvj7eUEXS7JbqZL4d2rBNS_rjM98V83bVZAgnLCpdAWCPov9AOc4Rx0Px8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQJcL0tu4f2vjeCPB62MkNKIsd3_5El9BH24hnXQgY6NFQ&amp;oe=6AB097D7</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2292,7 +2328,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Pé Suíno Kg</t>
+          <t>Paleta Bovina kg</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
@@ -2303,434 +2339,430 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>PÉ SUÍNO KG 9,99</t>
+          <t>Paleta Suína Kg</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>9.99</v>
+        <v>8.98</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Para Pizza Stamp Octogonal Nº25 c/ 25</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Stamp</t>
-        </is>
-      </c>
+          <t>Paleta Bovina kg</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>c/ 25</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>CAIXA P/ PIZZA STAMP OCT. Nº25 C/ 25UND</t>
+          <t>PALETA SUÍNA KG</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>28.9</v>
+        <v>8.99</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sabonete em Barra Palmolive 150g</t>
+          <t>Salsicha Hot Dog Seara kg</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Palmolive</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>SABONETE EM BARRA PALMOLIVE 150G</t>
+          <t>SALSICHA SEARA KG R$ 8,99</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Desodorante Aerosol Herbíssimo 150ml</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Herbíssimo</t>
-        </is>
-      </c>
+          <t>Pernil Suíno kg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>DESODORANTE AEROSOL HERBÍSSIMO 150ML</t>
+          <t>Pernil Suíno Kg</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>8.99</v>
+        <v>9.98</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Hidratante Corporal Flor de Ypê 400ml</t>
+          <t>Paleta Bovina Frigorifico Ochove kg</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Frigorifico Ochove</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>400ml</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>HIDRATANTE CORPORAL FLOR DE YPÊ 400ML</t>
+          <t>Pernil E Paleta Suíno Frigorifico Ochove R$ 10,99 KG</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>16.99</v>
+        <v>10.99</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Creme Facial Nivea 100g</t>
+          <t>Bisteca Suína Excelência kg</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Nivea</t>
+          <t>Excelência</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>CREME FACIAL NIVEA 100G</t>
+          <t>Bisteca Suína Excelência R$ 12,99 KG</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>23.99</v>
+        <v>12.99</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/809209423_18377807587237813_5374175614829990930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzQxODU3OTI2NzQ1ODg4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=HmEmbP_7H0oQ7kNvwF9D1Uq&amp;_nc_oc=AdrXo9bUGYdShUtZ8kzFbT6pTa1u719tZFag-GWHmxcIXXDEfFVd2kv5Ecr8v8bQc1TtgXdRdvaZMoyw28zgMMft&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJnM2vc9W9knYSjrjiPktOiiU_SFYiw5NQ0r64l2m5X7w&amp;oe=6AB06F2D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Sabonete Líquido Natural Oil Nivea 200ml</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Nivea</t>
-        </is>
-      </c>
+          <t>Bisteca Suína kg</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>SABONETE LÍQUIDO NIVEA NATURAL OIL 200ML</t>
+          <t>BISTECA SUÍNA KG</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>32.99</v>
+        <v>14.99</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795341823_18587301568067900_8497743799821946660_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzIxNDMxNzI1MTI3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Izx-Bto-NREQ7kNvwGHOUt3&amp;_nc_oc=Adot-SeBwTDleRiXjs1U3W1qAeKX2nbOBgZhl-MZUh4XTSny3SntJtOGtsJyCGVhxpM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLF90B1aLdPhWAeAVPFh5GFSrYetWe-Y_ogbyBwcaHC2Q&amp;oe=6AB070E4</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Toalha de Papel 600 Toalhas Mili</t>
+          <t>Linguiça Toscana Perdigão kg</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mili</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>Perdigão</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>TOALHA DE PAPEL MILI 600 TOALHAS</t>
+          <t>LINGUIÇA PERDIGÃO KG R$ 14,99</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>24.9</v>
+        <v>14.99</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/813344887_18587301634067900_8134807848346414765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxMzIzODYzNTg0MTAyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9ZuOo129ZT4Q7kNvwEBxBUQ&amp;_nc_oc=Adpi6o_9S1jJfin2e7Z84Kn34xYvMsG_DrBuErjTaIFX9grKVZqmrhg7tpRuOIwFYmM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLwbngRAgcD2cTV6uMCLb5gCDrdstHF5vSWZAYNbOiayw&amp;oe=6AB071C2</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Toalha de Papel 600 Toalhas Mili</t>
+          <t>Linguiça Toscana Perdigão kg</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Mili</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
+          <t>Perdigão</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>TOALHA DE PAPEL MILI 600 TOALHAS</t>
+          <t>Linguiça Suína Perdigão R$ 14,99 KG</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>24.9</v>
+        <v>14.99</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Linguiça Toscana kg</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2741,25 +2773,25 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>LARANJA KG 1,99</t>
+          <t>LINGUIÇA FINA APIMENTADA Kg R$ 16,99</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.99</v>
+        <v>16.99</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/795946636_18095987354531849_1912901089651838506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNTQ3MjEzNzI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JsgZDWGmOPoQ7kNvwEa525y&amp;_nc_oc=Adrbj00xgVvj7eUEXS7JbqZL4d2rBNS_rjM98V83bVZAgnLCpdAWCPov9AOc4Rx0Px8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQJcL0tu4f2vjeCPB62MkNKIsd3_5El9BH24hnXQgY6NFQ&amp;oe=6AB097D7</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
@@ -2771,61 +2803,69 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Alho Kg</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>Costela Suína Excelência Kg</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Excelência</t>
+        </is>
+      </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Alho Nacional R$ 2,49 A Cada 100g</t>
+          <t>Costela Suína Excelência R$ 18,99 KG</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.49</v>
+        <v>18.99</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>Linguiça Toscana Fricó kg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Fricó</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2833,42 +2873,42 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LARANJA PERA RIO Kg R$ 2,49</t>
+          <t>Linguiça Fina Apimentada Fricó R$ 19,99 KG</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2.49</v>
+        <v>19.99</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://instagram.fgdl9-1.fna.fbcdn.net/v/t51.82787-15/810962695_18377807584237813_5175983818023423599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NzQxODU3ODM4OTY5NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=B8Hb5Hj6NSUQ7kNvwEuM1_o&amp;_nc_oc=Adpb09U6bxQsx3qlEucg0BX9Q2x5zes8G79fQPOd1ge5onbtAIzyNd5MbZTSK9Vi-8cJyJwNq1x9snDcvsFlH-QQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl9-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQJ4Vg1n8LiMZUbKSgZqpkluBPcvB_4M-3H22eYrKnkm8A&amp;oe=6AB06ACA</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Batata Doce Kg</t>
+          <t>Bisteca Mineira Kg</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -2879,78 +2919,82 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BATATA DOCE Kg R$ 2,49</t>
+          <t>Bisteca Mineira Kg</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2.49</v>
+        <v>34.98</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://instagram.fcul1-2.fna.fbcdn.net/v/t39.30808-6/799251072_1522685429904573_2605074150271105599_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQ4MjEzMTgyNDY5MjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MXZMMk1THKgQ7kNvwGXzDo4&amp;_nc_oc=AdqpHY69z9g32GQAq5sOG1QJ5FshdLLw2REGKg7EnDMZdNMS8P8pDXW_UEwzke7hJAUFTD6_8wVsYsTk6tDxcKzX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcul1-2.fna&amp;_nc_gid=_zWB6iDN9C8gNPfUTWaPRQ&amp;_nc_ss=7a22e&amp;oh=00_AQLm8lXo2E_zfYUHYQzpjSBvb5cQf7369lZzKvH88RmHBQ&amp;oe=6AB08D1E</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWYd9PoM2v/</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>Milk Shake Chocolate Mach Foods 300ml</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Mach Foods</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>BANANA NANICA Kg R$ 2,69</t>
+          <t>SORVETE MACH FOODS MILK SHAKE CHOCOLATE 300ML</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2.69</v>
+        <v>12.98</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102759_18095831108531849_1023534374486459264_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTA1Mzg5NTQ0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9lImnxAV6ToQ7kNvwE1xxs6&amp;_nc_oc=Adq-jGT4eHZUnjECzk5JQ-IBIDyIUIrOuHslbVBSVhY0R1OSxhlGNiLmAMGjniQ_r9Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQLvJ-0IgP2aSeQevTQ2lngEj5Sqlq8QGxbUdG7s4idWXg&amp;oe=6AAF3B15</t>
+          <t>https://scontent-ord5-2.cdninstagram.com/v/t39.30808-6/811830268_1376651457888145_5114741585810459432_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NzA3ODkwMjY2MDg1MTUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=rl6JK7uFXfYQ7kNvwEgek0f&amp;_nc_oc=AdqIlcIdWmFcpL7JPEGk3oZ1IMxJaVTR9oUJz7PryaCFUPJQYoUyUGKQ-WDi44n7DAHfKbdNrueHmNBqXoATL9GS&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=7XW8mKzYSOmB1t3eX-9yuw&amp;_nc_ss=7a22e&amp;oh=00_AQIEqjQkNfcRvdAY6tqmr54gj-oyMsq5SY8anyBTD7wXAQ&amp;oe=6AB06BB7</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdU8yYMDSZP/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -2971,32 +3015,32 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BATATA DOCE KG 2,79</t>
+          <t>BATATA DOCE Kg R$ 2,49</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3006,7 +3050,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
+          <t>Laranja Pera Kg</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -3017,32 +3061,32 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>BANANA NANICA KG 2,99</t>
+          <t>LARANJA PERA RIO Kg R$ 2,49</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2.99</v>
+        <v>2.49</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3052,7 +3096,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá Kg</t>
+          <t>Banana Nanica Kg</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -3063,32 +3107,32 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá Kg R$ 2,99</t>
+          <t>BANANA NANICA R$ 2,69 Kg</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102759_18095831108531849_1023534374486459264_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTA1Mzg5NTQ0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Jlc9JsJFXUwQ7kNvwHdcNgX&amp;_nc_oc=AdpD1Lu3t4qQGaOlNHB1O-GZzO7kRiCEtaeSeuPDgszBgRznoT4lTulYTP0tl6rUJp0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJNUOb_DshVi85rGa3WLQu6BzYZHJdbGGYmrCa4dfLgQw&amp;oe=6AB08C95</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3098,7 +3142,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Melancia Kg</t>
+          <t>Laranja Pera Kg</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -3109,32 +3153,32 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Melancia Kg 2,99</t>
+          <t>LARANJA PERA RIO 2,69 kg</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3144,7 +3188,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Abóbora Cabotiá Kg</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -3155,32 +3199,32 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Laranja Pera Rio - Kg 2,99</t>
+          <t>ABOBORA CABOTIA Kg R$ 3,49</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3190,7 +3234,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Repolho Verde Kg</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -3201,32 +3245,32 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Laranja Nacional R$ 2,99 KG</t>
+          <t>REPOLHO VERDE Kg R$ 3,79</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3236,14 +3280,10 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Batata Doce Kg</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -3251,32 +3291,32 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá - Kg</t>
+          <t>BATATA DOCE 3,99 kg</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3286,7 +3326,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá Kg</t>
+          <t>Beterraba Kg</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -3297,11 +3337,11 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ABOBORA CABOTIA Kg R$ 3,49</t>
+          <t>BETERRABA 3,99 kg</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3310,19 +3350,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3332,14 +3372,10 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Beterraba Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -3347,32 +3383,32 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Beterraba Kg</t>
+          <t>REPOLHO VERDE 3,99 kg</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3382,7 +3418,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>Maçã Kg</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -3393,11 +3429,11 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE Kg R$ 3,79</t>
+          <t>Maça KG R$ 4,49</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>3.79</v>
+        <v>4.49</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3406,19 +3442,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://instagram.fmad20-1.fna.fbcdn.net/v/t51.82787-15/810623418_18587064529067900_3113824482793674713_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4Njc0MTg1MDg2NjQ3MDgyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4vluJg_MQHwQ7kNvwECBc8N&amp;_nc_oc=AdoA5gwbEVFnhbVjun7XIGWz4ioX2Ab7el282lRsOpZPXVIf-f3HZozItAvTSJzvmZM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmad20-1.fna&amp;_nc_gid=Pi9Bm4ERsLd1TlWjfS0YSw&amp;_nc_ss=7a22e&amp;oh=00_AQJ-M-w16gTy59ZVA2mChXuePh9tAwE7Bq6FNbzAzPSHiQ&amp;oe=6AB061B0</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdTwJc4FE-r/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3428,7 +3464,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Beterraba Kg</t>
+          <t>Abacate Kg</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -3439,32 +3475,32 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Beterraba Kg R$ 3,99</t>
+          <t>ABACATE Kg R$ 4,49</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3474,7 +3510,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -3485,32 +3521,32 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg R$ 3,99</t>
+          <t>MAMÃO FORMOSA Kg R$ 4,49</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3520,7 +3556,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -3531,32 +3567,32 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg R$ 3,99</t>
+          <t>CENOURA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3566,7 +3602,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
+          <t>Batata Inglesa Kg</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -3577,32 +3613,32 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica - Kg 3,99</t>
+          <t>BATATA LAVADA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3612,14 +3648,10 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Chuchu Kg</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -3627,32 +3659,32 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>CHUCHU 4,99 kg</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3662,43 +3694,43 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Kabotiã 1kg</t>
+          <t>Tomate Italiano Kg</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Kabotiã R$ 3,99 KG</t>
+          <t>TOMATE ITALIANO R$ 5,49 Kg</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>3.99</v>
+        <v>5.49</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102759_18095831108531849_1023534374486459264_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTA1Mzg5NTQ0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Jlc9JsJFXUwQ7kNvwHdcNgX&amp;_nc_oc=AdpD1Lu3t4qQGaOlNHB1O-GZzO7kRiCEtaeSeuPDgszBgRznoT4lTulYTP0tl6rUJp0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJNUOb_DshVi85rGa3WLQu6BzYZHJdbGGYmrCa4dfLgQw&amp;oe=6AB08C95</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3708,43 +3740,43 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>Cebola Nacional Kg</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde R$ 3,99 KG</t>
+          <t>CEBOLA Kg R$ 5,49</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>3.99</v>
+        <v>5.49</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwER2cSE&amp;_nc_oc=AdqXnKv29AOqlfsz-50Y7DIQAV7xSF_IrT7Y8YrbLuKXdVzWNo0vWBIzgDw32191R24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQJ-f5OeaBKP2opYidu_tlehZl6uqabAqfa42pkX6kNZZA&amp;oe=6AB07BE3</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3754,7 +3786,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Mandioca Kg</t>
+          <t>Tomate Longa Vida Kg</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -3765,32 +3797,32 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>MANDIOCA KG 4,49</t>
+          <t>TOMATE LV Kg R$ 5,49</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.49</v>
+        <v>5.49</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808802752_18586780840067900_4554123868867436270_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTk3ODgwNzE2OTYyNTI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PWHrg84JzAIQ7kNvwFuj1L3&amp;_nc_oc=AdodVnLRi7gy4FmRkmr30viAIpzXQYDF_DDsYlul3n-pBaa6dSnIHiz5dVo4YNv5UHQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=V-gIJAlsLuZonpLhFh99tQ&amp;_nc_ss=7a22e&amp;oh=00_AQLyuG8iwInoBdlCG4yqoWBPSGX-kxAwMr2-3_QXLF-zCw&amp;oe=6AAF2611</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRCp9klEZ2/</t>
+          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3800,7 +3832,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Maçã Kg</t>
+          <t>Banana Prata Kg</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -3811,11 +3843,11 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>MAÇÃ KG R$ 4,49</t>
+          <t>BANANA PRATA 5,99 kg</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3824,12 +3856,12 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/810623418_18587064529067900_3113824482793674713_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4Njc0MTg1MDg2NjQ3MDgyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sR8pXKHJvY0Q7kNvwER5d1U&amp;_nc_oc=AdrsQyZLJ02KZ6-8Z1lWTEnYgSSPFRGx1weG7Pd3LIEAVux7lqY-xVWWA3UCKZjpZ-2oesrngGuYmXBn110sA-TX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=X3ip3QZElf9DoqJWO8fSuQ&amp;_nc_ss=7a22e&amp;oh=00_AQI377m59R5lzQBPPiUr7rwRwVhquuz_TqPpUXpw8u46YQ&amp;oe=6AAF1030</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdTwJc4FE-r/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
@@ -3846,22 +3878,22 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
+          <t>Uva Niagara 500g</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>ABACATE Kg R$ 4,49</t>
+          <t>UVA VITORIA BDJ R$ 6,99</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3870,7 +3902,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -3892,7 +3924,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
+          <t>Manga Tommy Kg</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -3903,11 +3935,11 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>MAMÃO FORMOSA Kg R$ 4,49</t>
+          <t>MANGA TOMMY Kg R$ 6,99</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3916,7 +3948,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwGFQhEP&amp;_nc_oc=AdrgAGepgCzzZ2o0AgiQAAjmyDAkYjzPlfHoNpHJzjqsLl74h2LEM_5Bp_VOarrgob0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=4C5Cs87t_dbzmMuuMn6_yg&amp;_nc_ss=7a22e&amp;oh=00_AQLfDOzaKBygJs6HzL9q309GyQogsRo0Nlq2WyPyadgwbA&amp;oe=6AB06799</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -3928,7 +3960,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3938,7 +3970,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
+          <t>Pepino Japonês Kg</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -3949,32 +3981,32 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>ABACATE KG 4,59</t>
+          <t>PEPINO JAPONÊS 6,99 kg</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4.59</v>
+        <v>6.99</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -3984,7 +4016,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
@@ -3995,32 +4027,32 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>BATATA KG 4,99</t>
+          <t>MAMÃO FORMOSA 6,99 kg</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4030,43 +4062,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Batata Doce Kg</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>Uva Niagara Vitória 500g</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Batata Doce R$ 4,99 KG</t>
+          <t>UVA VITÓRIA SEM SEMENTES BDJ 500G 8,99</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4076,43 +4112,43 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Cebola Nacional Kg</t>
+          <t>Limão Taiti Kg</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Cebola Nacional R$ 4,99 KG</t>
+          <t>LIMÃO TAITI 11,99 kg</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4122,43 +4158,47 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>Maçã Turma da Mônica 1kg</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Turma Da Mônica</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica R$ 4,99 KG</t>
+          <t>MAÇÃ TURMA MÔNICA 11,99 1kg</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t39.30808-6/807699306_1681930047270726_1300756400736070045_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzA2MzM2NjA3ODAxNDIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D3rTv9SA5TAQ7kNvwGfBNdj&amp;_nc_oc=Adpir32H7ixU3_mDdcKg4ZbJzaoAXHg5tVX3MkK3Nf23Nj5wBZX3ePSy1IT57Dqo8WQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQKukdZL_eDCE_Wn1puiZglkuGcxe3hvxhzUsN2Ji6cC1w&amp;oe=6AB09583</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4168,7 +4208,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Mandioca Kg</t>
+          <t>Alho Kg</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -4179,25 +4219,25 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MANDIOCA Kg R$ 4,99</t>
+          <t>ALHO GRANEL 22,99 kg</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>4.99</v>
+        <v>22.99</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/809939935_18095758838531849_6369815637718061540_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk5OTY1MDg1MDM4MTY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Uu9ygyxPTFoQ7kNvwGmecvK&amp;_nc_oc=AdoRCbaU8PO4IveA00T4yuJg1OLtJKwy9LWfvXjpBIX51aWo1fW1vQ5JCbihA94uTFURX9nH6i3BAOwvx7ewlIfC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7iz8UKfZvcdtbZXC7lzyMw&amp;_nc_ss=7a22e&amp;oh=00_AQK-Mc61U3sTO73CYITLILQ_X6CB1LhGCJ4mxVDq5_CIHA&amp;oe=6AAF33CE</t>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t39.30808-6/803101764_1681930043937393_8926449708464949008_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NzA2MzM2NTgyNjMyODkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PRmn_Bc3tkwQ7kNvwECUYUl&amp;_nc_oc=AdoF2J2woGZ0NAinD7AQ01dGJM0WLuKCL3LF-mhqwMbjqlGnUtk_9rbKtH9xnKgySYA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=NkwWMDWeUlio70L1IBY48A&amp;_nc_ss=7a22e&amp;oh=00_AQLx3THva4FD6pLpZERCL4Jv9jNE5XAe4RprmXJg81Ruyw&amp;oe=6AB08F94</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRHZBPxJ9d/</t>
+          <t>https://www.instagram.com/p/DdU5QS2DS3N/</t>
         </is>
       </c>
     </row>
@@ -4209,41 +4249,45 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Creme Culinário Triangulo Mineiro 200g</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Triangulo Mineiro</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>CENOURA Kg R$ 4,99</t>
+          <t>CREME CULINARIO TRIANGULO 200G R$ 1,99</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/808847574_18095987384531849_6741248101073260208_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjc1NTUxMzg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ttBxgp72VfoQ7kNvwF_7DmZ&amp;_nc_oc=AdqKfoeXfx82YSPI7vp95BvkVnVhrA0Gp5d4okSNhTIxRKct1rEOaqw6gUsEY725BHI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKRUrhSmH_7_wl9TOoyEnY0LDqMpjEOeQd6BHpEiNBQMw&amp;oe=6AB07D84</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
@@ -4255,41 +4299,45 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
+          <t>Leite Integral Piracanjuba 1L</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Piracanjuba</t>
+        </is>
+      </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>BATATA LAVADA Kg R$ 4,99</t>
+          <t>LEITE PIRACANJUBA SEMI E DESNATADO 1LT R$ 5,99</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/812903732_18095987372531849_1537119090747111941_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjAxNzI3Mjc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pxqhc0muYnYQ7kNvwHSQ9U2&amp;_nc_oc=AdqEHYQh14DVK-qSl2Nq6gfKFH6Bhqve4VZ7cVDLNO0niJIsru-M21HIXvlImaS_1J4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKX3OQwLBWzS81LADMzDAd0gfUNL1FKAaP-kQSoZB7pRg&amp;oe=6AB07AE1</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
@@ -4301,225 +4349,245 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>Desinfetante Zupp 2L</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Zupp</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>CENOURA KG 5,49</t>
+          <t>DESINFETANTE ZUPP 2LT</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>5.49</v>
+        <v>6.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811373905_18587301739067900_3006429185396623069_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzQxMzMwODUyMTMzODU0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8oryN0XvpkMQ7kNvwGMZyEd&amp;_nc_oc=AdqEA5lFUDKU40_w4wQgAawP2Vggo1ucuNIsfW-tYT7FVq2WitBq_9dfvyOaBe61AIE&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQICqB3WBS6QcY7L7KxeIRFVq2uKNvpIPWzcByVH-kSDZg&amp;oe=6AB06604</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Banana Terra Kg</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr"/>
+          <t>Desinfetante Zupp 2L</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Zupp</t>
+        </is>
+      </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>BANANA TERRA KG 5,49</t>
+          <t>DESINF. ZUPP 2LT R$ 6,99</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>5.49</v>
+        <v>6.99</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
+          <t>https://instagram.fsyd3-2.fna.fbcdn.net/v/t51.82787-15/813804585_18095987396531849_5289153121879299473_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNzE0MTUwMzE5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sBQDw_MD8MsQ7kNvwEiw4ts&amp;_nc_oc=Adp612Vp1otEsjfbHf17pkxzxRv2mwyI7h5VY7tZ-ICNX9bLakcPBw0HaKUKNPVN7EY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQLkoxNm614K_IzGT211V16WTLjgFPteT0Lw-qi0uo2VEQ&amp;oe=6AB08D27</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
+          <t>Desinfetante Pinho Sol 2L</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Pinho Sol</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg 5,49</t>
+          <t>PINHO SOL 1LT R$ 9,99</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>5.49</v>
+        <v>9.99</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://instagram.fsyd3-2.fna.fbcdn.net/v/t51.82787-15/813804585_18095987396531849_5289153121879299473_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNzE0MTUwMzE5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sBQDw_MD8MsQ7kNvwEiw4ts&amp;_nc_oc=Adp612Vp1otEsjfbHf17pkxzxRv2mwyI7h5VY7tZ-ICNX9bLakcPBw0HaKUKNPVN7EY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQLkoxNm614K_IzGT211V16WTLjgFPteT0Lw-qi0uo2VEQ&amp;oe=6AB08D27</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Tomate Longa Vida Kg</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr"/>
+          <t>Detergente Líquido Zupp 500ml</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Zupp</t>
+        </is>
+      </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>TOMATE LV Kg R$ 5,49</t>
+          <t>DETERGENTE ZUPP 500G</t>
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>5.49</v>
+        <v>1.99</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811373905_18587301739067900_3006429185396623069_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzQxMzMwODUyMTMzODU0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8oryN0XvpkMQ7kNvwGMZyEd&amp;_nc_oc=AdqEA5lFUDKU40_w4wQgAawP2Vggo1ucuNIsfW-tYT7FVq2WitBq_9dfvyOaBe61AIE&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQICqB3WBS6QcY7L7KxeIRFVq2uKNvpIPWzcByVH-kSDZg&amp;oe=6AB06604</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Cebola Nacional Kg</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>Sabão em Pó Assim 1.6kg</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Assim</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>CEBOLA Kg R$ 5,49</t>
+          <t>SABÃO ASSIM 800G</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>5.49</v>
+        <v>6.99</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102544_18095831081531849_2604010637428187235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NjQ0MzEyMDAxMzUyODkzMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q4fglDHdZTAQ7kNvwHcd3Oo&amp;_nc_oc=AdqIYADBrsDPd31_zbQANBS0Nq58CcDWzjhhMlKGbuApWzz4V2qwe3d9UIxdeKn1vDs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJoaIWMV39-9IbWsUG__p8FK_7ZSuV00swOl-PIGlVcJQ&amp;oe=6AAF2A63</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811373905_18587301739067900_3006429185396623069_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NzQxMzMwODUyMTMzODU0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8oryN0XvpkMQ7kNvwGMZyEd&amp;_nc_oc=AdqEA5lFUDKU40_w4wQgAawP2Vggo1ucuNIsfW-tYT7FVq2WitBq_9dfvyOaBe61AIE&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQICqB3WBS6QcY7L7KxeIRFVq2uKNvpIPWzcByVH-kSDZg&amp;oe=6AB06604</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
@@ -4531,403 +4599,427 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Tomate Italiano Kg</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>Amaciante Ypê 2L</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Ypê</t>
+        </is>
+      </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>TOMATE ITALIANO Kg R$ 5,49</t>
+          <t>AMAC YPÊ 2LT R$ 9,99</t>
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>5.49</v>
+        <v>9.99</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102759_18095831108531849_1023534374486459264_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMTA1Mzg5NTQ0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=9lImnxAV6ToQ7kNvwE1xxs6&amp;_nc_oc=Adq-jGT4eHZUnjECzk5JQ-IBIDyIUIrOuHslbVBSVhY0R1OSxhlGNiLmAMGjniQ_r9Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQLvJ-0IgP2aSeQevTQ2lngEj5Sqlq8QGxbUdG7s4idWXg&amp;oe=6AAF3B15</t>
+          <t>https://instagram.fsyd3-2.fna.fbcdn.net/v/t51.82787-15/813804585_18095987396531849_5289153121879299473_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNzE0MTUwMzE5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sBQDw_MD8MsQ7kNvwEiw4ts&amp;_nc_oc=Adp612Vp1otEsjfbHf17pkxzxRv2mwyI7h5VY7tZ-ICNX9bLakcPBw0HaKUKNPVN7EY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQLkoxNm614K_IzGT211V16WTLjgFPteT0Lw-qi0uo2VEQ&amp;oe=6AB08D27</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Cebola Nacional Kg</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>Sabão em Pó Assim 1.6kg</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Assim</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>2.2kg</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>CEBOLA KG 5,79</t>
+          <t>SABÃO PÓ ASSIM 2,2KG R$ 18,99</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>5.79</v>
+        <v>18.99</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
+          <t>https://instagram.fsyd3-2.fna.fbcdn.net/v/t51.82787-15/813804585_18095987396531849_5289153121879299473_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNzE0MTUwMzE5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sBQDw_MD8MsQ7kNvwEiw4ts&amp;_nc_oc=Adp612Vp1otEsjfbHf17pkxzxRv2mwyI7h5VY7tZ-ICNX9bLakcPBw0HaKUKNPVN7EY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQLkoxNm614K_IzGT211V16WTLjgFPteT0Lw-qi0uo2VEQ&amp;oe=6AB08D27</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
+          <t>Arroz Branco Tipo 1 Grão Rico 5kg</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Grão Rico</t>
+        </is>
+      </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg R$ 5,99</t>
+          <t>ARROZ GRÃO RICO 5KG R$ 16,49</t>
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>5.99</v>
+        <v>16.49</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/812903732_18095987372531849_1537119090747111941_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjAxNzI3Mjc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pxqhc0muYnYQ7kNvwHSQ9U2&amp;_nc_oc=AdqEHYQh14DVK-qSl2Nq6gfKFH6Bhqve4VZ7cVDLNO0niJIsru-M21HIXvlImaS_1J4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKX3OQwLBWzS81LADMzDAd0gfUNL1FKAaP-kQSoZB7pRg&amp;oe=6AB07AE1</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Maçã Kg</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>Arroz Branco Tipo 1 Rei 5kg</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Rei</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Maçã Nacional Kg 5,99</t>
+          <t>ARROZ REI 5KG</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811994240_18587301694067900_743017156705893519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NzQxMzI2NjIwOTIxNjg0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XPdXAuBiq2QQ7kNvwGbKI7X&amp;_nc_oc=Adovh6F5eN_pXXJLyWEsG57X6MJs0jSZ8UejXzOPqWeDgGVK1-5OWUUIrBkj7jITybk&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLLNNgU-9cP4gfgq4loo4csvHnHGqHQJHFWgTMXssmc1A&amp;oe=6AB08CEA</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr"/>
+          <t>Açúcar Cristal Doce Dia 2kg</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Doce Dia</t>
+        </is>
+      </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa - Kg 5,99</t>
+          <t>AÇÚCAR DOCE 2KG</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>5.99</v>
+        <v>4.29</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811994240_18587301694067900_743017156705893519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NzQxMzI2NjIwOTIxNjg0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XPdXAuBiq2QQ7kNvwGbKI7X&amp;_nc_oc=Adovh6F5eN_pXXJLyWEsG57X6MJs0jSZ8UejXzOPqWeDgGVK1-5OWUUIrBkj7jITybk&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLLNNgU-9cP4gfgq4loo4csvHnHGqHQJHFWgTMXssmc1A&amp;oe=6AB08CEA</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Batata Inglesa Desconhecida Kg</t>
+          <t>Rosquinha Sabor Coco Adoralle 500g</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Desconhecida</t>
+          <t>Adoralle</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
+          <t>ROSCA COCO ADORALLE 500G R$ 4,99</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/808847574_18095987384531849_6741248101073260208_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjc1NTUxMzg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ttBxgp72VfoQ7kNvwF_7DmZ&amp;_nc_oc=AdqKfoeXfx82YSPI7vp95BvkVnVhrA0Gp5d4okSNhTIxRKct1rEOaqw6gUsEY725BHI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKRUrhSmH_7_wl9TOoyEnY0LDqMpjEOeQd6BHpEiNBQMw&amp;oe=6AB07D84</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Desconhecida Kg</t>
+          <t>Rosquinha Coco Mabel 600g</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Desconhecida</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>600g</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>ROSQUINHA MABEL 600G R$ 6,99</t>
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795068826_18587301715067900_3736282338032078257_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzI4ODE4NzMzNjU0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kw9fDMjw_VwQ7kNvwE3DJAg&amp;_nc_oc=AdrJrccRDVkUXkf620KJ1WEy4EUkXgZDG0hExMEaFqgo5HqPHYejGnJYDmHZUwfaumM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLD6FONLiwBNpsDV1rjcUeekUPI3xnGHdAIIl0jmLKcbQ&amp;oe=6AB07C48</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Banana da Terra Desconhecida Kg</t>
+          <t>Café Tradicional Quitada 500g</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Desconhecida</t>
+          <t>Quitada</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>250g</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Banana da Terra - Kg</t>
+          <t>CAFÉ QUITADA 250G R$ 13,99</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/808847574_18095987384531849_6741248101073260208_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjc1NTUxMzg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ttBxgp72VfoQ7kNvwF_7DmZ&amp;_nc_oc=AdqKfoeXfx82YSPI7vp95BvkVnVhrA0Gp5d4okSNhTIxRKct1rEOaqw6gUsEY725BHI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKRUrhSmH_7_wl9TOoyEnY0LDqMpjEOeQd6BHpEiNBQMw&amp;oe=6AB07D84</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr"/>
+          <t>Farinha de Trigo Tipo 1 Ventureli 1kg</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Ventureli</t>
+        </is>
+      </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>TRIGO VENTURELI 1KG</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
@@ -4935,91 +5027,99 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508001237813_6232705703747551776_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NTk2MTk1NjA1MjAxNDM1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PvQmCa4D-2gQ7kNvwFYbGSB&amp;_nc_oc=Adpj4RULhSw6Cf80SpnyUI-Jw3-i9S--dOBFYDB7Z_xNnSza8o2WsQM_jXiqcPQeeBJTnbPydmgAHlvGaOpvCZt5&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKB1QalvlgVuhBetgENLEBMbFRRnYuW6tY-LQHBxaQ7OA&amp;oe=6AAF387C</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811994240_18587301694067900_743017156705893519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NzQxMzI2NjIwOTIxNjg0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XPdXAuBiq2QQ7kNvwGbKI7X&amp;_nc_oc=Adovh6F5eN_pXXJLyWEsG57X6MJs0jSZ8UejXzOPqWeDgGVK1-5OWUUIrBkj7jITybk&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLLNNgU-9cP4gfgq4loo4csvHnHGqHQJHFWgTMXssmc1A&amp;oe=6AB08CEA</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>Milho Verde Sofruta 170g</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Sofruta</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>170g</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Abacate R$ 5,99 KG</t>
+          <t>MILHO SOFRUTA 170G R$ 2,89</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>5.99</v>
+        <v>2.89</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795068826_18587301715067900_3736282338032078257_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzI4ODE4NzMzNjU0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kw9fDMjw_VwQ7kNvwE3DJAg&amp;_nc_oc=AdrJrccRDVkUXkf620KJ1WEy4EUkXgZDG0hExMEaFqgo5HqPHYejGnJYDmHZUwfaumM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLD6FONLiwBNpsDV1rjcUeekUPI3xnGHdAIIl0jmLKcbQ&amp;oe=6AB07C48</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr"/>
+          <t>Feijão Carioca Dona Dé 1kg</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Dona Dé</t>
+        </is>
+      </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Batata Monalisa R$ 5,99 KG</t>
+          <t>FEIJÃO DONA DE PRETO 1KG R$ 5,99</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
@@ -5027,63 +5127,67 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/812903732_18095987372531849_1537119090747111941_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjAxNzI3Mjc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pxqhc0muYnYQ7kNvwHSQ9U2&amp;_nc_oc=AdqEHYQh14DVK-qSl2Nq6gfKFH6Bhqve4VZ7cVDLNO0niJIsru-M21HIXvlImaS_1J4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKX3OQwLBWzS81LADMzDAd0gfUNL1FKAaP-kQSoZB7pRg&amp;oe=6AB07AE1</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Batatinha Kg</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>Feijão Carioca Kumbuca 1kg</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Kumbuca</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Batatinha Kg R$ 6,79</t>
+          <t>FEIJÃO KUMBUCA 1KG</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>6.79</v>
+        <v>6.99</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811994240_18587301694067900_743017156705893519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NzQxMzI2NjIwOTIxNjg0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XPdXAuBiq2QQ7kNvwGbKI7X&amp;_nc_oc=Adovh6F5eN_pXXJLyWEsG57X6MJs0jSZ8UejXzOPqWeDgGVK1-5OWUUIrBkj7jITybk&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLLNNgU-9cP4gfgq4loo4csvHnHGqHQJHFWgTMXssmc1A&amp;oe=6AB08CEA</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
@@ -5095,63 +5199,67 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Manga Kg</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr"/>
+          <t>Macarrão Espaguete Galo 500g</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Galo</t>
+        </is>
+      </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>MANGA KG 6,99</t>
+          <t>MACARRÃO GALO 500G R$ 3,99</t>
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795068826_18587301715067900_3736282338032078257_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzI4ODE4NzMzNjU0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kw9fDMjw_VwQ7kNvwE3DJAg&amp;_nc_oc=AdrJrccRDVkUXkf620KJ1WEy4EUkXgZDG0hExMEaFqgo5HqPHYejGnJYDmHZUwfaumM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLD6FONLiwBNpsDV1rjcUeekUPI3xnGHdAIIl0jmLKcbQ&amp;oe=6AB07C48</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Uva Niagara Vitória 500g</t>
+          <t>Macarrão Espaguete Galo 500g</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Galo</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5161,117 +5269,125 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>UVA VITÓRIA BDJ 6,99</t>
+          <t>MAC GALO ESPAGUETE 8 500G R$ 3,99</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://instagram.fsyd4-2.fna.fbcdn.net/v/t51.82787-15/808847574_18095987384531849_6741248101073260208_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjc1NTUxMzg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ttBxgp72VfoQ7kNvwF_7DmZ&amp;_nc_oc=AdqKfoeXfx82YSPI7vp95BvkVnVhrA0Gp5d4okSNhTIxRKct1rEOaqw6gUsEY725BHI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd4-2.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKRUrhSmH_7_wl9TOoyEnY0LDqMpjEOeQd6BHpEiNBQMw&amp;oe=6AB07D84</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr"/>
+          <t>Tomate Longa Vida Predilecta Kg</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Predilecta</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formoso R$ 6,99 KG</t>
+          <t>MOLHO PREDILECTA 300G R$ 1,49</t>
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>6.99</v>
+        <v>1.49</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/795068826_18587301715067900_3736282338032078257_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzQxMzI4ODE4NzMzNjU0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kw9fDMjw_VwQ7kNvwE3DJAg&amp;_nc_oc=AdrJrccRDVkUXkf620KJ1WEy4EUkXgZDG0hExMEaFqgo5HqPHYejGnJYDmHZUwfaumM&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLD6FONLiwBNpsDV1rjcUeekUPI3xnGHdAIIl0jmLKcbQ&amp;oe=6AB07C48</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Uva Niagara 500g</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>Óleo de Soja Liza 900ml</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Liza</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>900ml</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>UVA VITORIA BDJ R$ 6,99</t>
+          <t>ÓLEO LIZA 900ML</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>6.99</v>
+        <v>6.49</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://scontent-ber1-1.cdninstagram.com/v/t51.82787-15/811994240_18587301694067900_743017156705893519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NzQxMzI2NjIwOTIxNjg0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XPdXAuBiq2QQ7kNvwGbKI7X&amp;_nc_oc=Adovh6F5eN_pXXJLyWEsG57X6MJs0jSZ8UejXzOPqWeDgGVK1-5OWUUIrBkj7jITybk&amp;_nc_ad=z-m&amp;_nc_cid=1365&amp;_nc_zt=23&amp;_nc_ht=scontent-ber1-1.cdninstagram.com&amp;_nc_gid=wDQUY9jsjP4tXaN6Cz8Fgw&amp;_nc_ss=7a22e&amp;oh=00_AQLLNNgU-9cP4gfgq4loo4csvHnHGqHQJHFWgTMXssmc1A&amp;oe=6AB08CEA</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWI0w2lN1L/</t>
         </is>
       </c>
     </row>
@@ -5283,3043 +5399,145 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Manga Tommy Kg</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
+          <t>Óleo de Soja Liza 900ml</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Liza</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>900ml</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>MANGA TOMMY Kg R$ 6,99</t>
+          <t>ÓLEO DE SOJA LIZA 900ML R$ 6,49</t>
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>6.99</v>
+        <v>6.49</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/811102562_18095831090531849_4806140992173407267_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjQ0MzEyMDI0MDE0NDY2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wxbbr1PFWckQ7kNvwHpRCZu&amp;_nc_oc=AdoslWW-Fdxa905MyE2B9A6ShuaIWD1ctB1FnydZ8UCr7irXX6KTJqng5jB-qkP0Zhc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=WWsBoW2SjU9dktGG2UodzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJPOWk-iA9ysmTvmjTKDXTuUbKFh7rtSTomjSwJHvthBw&amp;oe=6AAF1619</t>
+          <t>https://instagram.fsyd3-1.fna.fbcdn.net/v/t51.82787-15/812903732_18095987372531849_1537119090747111941_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4NzQ0MjAzNjAxNzI3Mjc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pxqhc0muYnYQ7kNvwHSQ9U2&amp;_nc_oc=AdqEHYQh14DVK-qSl2Nq6gfKFH6Bhqve4VZ7cVDLNO0niJIsru-M21HIXvlImaS_1J4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd3-1.fna&amp;_nc_gid=fmiDGAlROeKAb2IGJHbVIw&amp;_nc_ss=7a22e&amp;oh=00_AQKX3OQwLBWzS81LADMzDAd0gfUNL1FKAaP-kQSoZB7pRg&amp;oe=6AB07AE1</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSsPN_DT5v/</t>
+          <t>https://www.instagram.com/p/DdWPXiokRo9/</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Abacaxi Pérola un</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>Bacon em Manta Mach Foods kg</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Mach Foods</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Abacaxi Un R$ 7,19</t>
+          <t>X-Bacon de R$ 33,90 por R$ 28,90</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>7.19</v>
+        <v>28.9</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
+          <t>https://scontent-ord5-1.cdninstagram.com/v/t39.30808-6/807658088_1376651454554812_6623453831289175346_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzA3ODkwMjEyMzkyNzUwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FAg8C63xHrcQ7kNvwFU2NTZ&amp;_nc_oc=AdpXpvQ6nD0QAlf9Yt106eI7w4cvxEJ8NjrosEbWWxzxZidvCLkj1q5I9LLMWuQEoyB47zc6uWz7AqTzJLHMQAHV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=7XW8mKzYSOmB1t3eX-9yuw&amp;_nc_ss=7a22e&amp;oh=00_AQLAGkk31Eh4TxFpvD0xfijP4VJMapNEO87mcIbCtnN9FA&amp;oe=6AB07074</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
+          <t>https://www.instagram.com/p/DdU8yYMDSZP/</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Abacaxi Pérola un</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
+          <t>Alho Dabrasa Kg</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Dabrasa</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>450g</t>
+        </is>
+      </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>ABACAXI GRAÚDO UNIDADE 7,99</t>
+          <t>Pão De Alho Dabrasa Sabores 450g</t>
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
+          <t>https://instagram.fgdl17-1.fna.fbcdn.net/v/t51.82787-15/812535592_18377807602237813_4975415513285451361_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NzQxODU3ODQyMzAwNDcwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=Zsd1Nn-361YQ7kNvwGw-6ZF&amp;_nc_oc=AdoriLFkTh5l0SahutsGGvxatR33xdsT-JgKnLWZH7So7Xb9YssWhAacdx_JUFuiFT88Y8rKeILPNMEGP6tdvEvF&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgdl17-1.fna&amp;_nc_gid=zO1gC0wTim82vT6PI2zqTg&amp;_nc_ss=7a22e&amp;oh=00_AQLsWU20bJ8P3pegJVIwVZEz5CnbBxcCvsLynEii2ZLGtw&amp;oe=6AB0945F</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Ovos Brancos c/ 30</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>c/ 20</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>OVOS BRANCO 20X1 7,99</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado São Pedro</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Uva Niagara Vitória 500g</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Uva Vitória 500g R$ 7,99</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Uva Niagara 500g</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Uva Vitória Bdj. 500g 7,99</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/809026866_18194605591391764_8818956106260600919_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTYwODI4MDQ4NDQwMjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=v0Z40WOtmLYQ7kNvwHG6HTM&amp;_nc_oc=AdrhGqpudLKhninmH2s-KQGLTosGnTvzCw35-_Cv3lqcv-PTlLA46nbU22vBHw_IHCY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQKhpj5bE6l-XMMF1wPDSUoGn8m1ZhVW0cOqn_GktwsoWg&amp;oe=6AAF3E95</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Uva Niagara 500g</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Uva Vitória/Isís Bandeja 500G R$ 7,99 UN</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado São Pedro</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Maçã Fuji Kg</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Maçã Fuji Kg R$ 8,39</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado São Pedro</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Ovos Brancos c/ 30 Campo Verde</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Campo Verde</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Ovos Brancos Campo Verde c/20 R$ 10,39</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/810090930_18197654596382122_3495655905768859727_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NjAxMjI2OTIyNTEyNTQyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4xL2q_UzDVkQ7kNvwE1Mw1T&amp;_nc_oc=Adq5c7cPR-aYXi0MpXQZT4NHgApwrfAXVY7aWDA37kRPEILW1iQ4n3DeaLCrC0YMuTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=L_38kJebuM903lPZfBjKDA&amp;_nc_ss=7a22e&amp;oh=00_AQLf0WdRuLcPQb3GyGkag6aXOcmZZxCUOAAFh3ryCUZbvw&amp;oe=6AAF23D7</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRKQpBgyYs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Ovos Brancos c/ 30 Mantiqueira</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Mantiqueira</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>c/ 20</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Ovo Mantiqueira Com 20 Unidades R$ 12,99 UN</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fbne5-1.fna.fbcdn.net/v/t51.82787-15/809645783_18377508013237813_8470053041970738622_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4NTk2MTk1ODIwOTY1MTg4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ELl8WzxY2ykQ7kNvwHj54-m&amp;_nc_oc=AdoBGdIiGxO2T0AU2OWyzVqpJxfKoblLo85ahqp3oM-S9QGcg14dZDuDOuEwf1Yne0l1_ebUdx123j8lXqGYlC_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne5-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQLz0qQUN4h-qqwgk4TUz63CHGJezpidOuqeBD42wTyZzQ&amp;oe=6AAF29B2</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Hortifruti / Ovos</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>Ovos Brancos c/ 30 Mantiqueira</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Mantiqueira</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>c/ 30</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Ovos Brancos Mantiqueira Bdj. c/ 30 Und.</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Laticínios / Leites e Derivados</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Margarina c/ Sal Deline 500g</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Deline</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>MARGARINA DELINE C/SAL 1KG</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Laticínios / Leites e Derivados</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Margarina c/ Sal Deline 500g</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Deline</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>MARGARINA DELINE C/SAL 1KG</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Laticínios / Leites e Derivados</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Chantilly Chanty Mix Amélia 1L</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Amélia</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>CHANTILLY AMÉLIA CHANTY MIX 1L</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Laticínios / Leites e Derivados</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Chantilly Chanty Mix Amélia 1L</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>Amélia</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>CHANTILLY AMÉLIA CHANTY MIX 1L</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Vassoura Multiuso Condor</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Condor</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>VASSOURA CONDOR MULTIUSO PP UNI</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Limpador Perfumado Casaflor 1.75L</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Casaflor</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>1.75L</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>LIMPADOR PERFUMADO CASAFLOR 1,75LT</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Saponáceo Cremoso Cif 450ml</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Cif</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>450ml</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>SAPONÁCEO CIF CREMOSO ORIGINAL LV 450ML PG 360ML UNI</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Difusor de Aromas Coala 100ml</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Coala</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>DIFUSOR AROMAS COALA 100ML</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Bobina Picotada 40x50cm Giopack 10kg</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Giopack</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>BOBINA PICOTADA GIOPACK 40X50CM 10KG</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Detergente Líquido Minuano 500ml</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>Minuano</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>DETERGENTE MINUANO 500ML</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Tixan Ypê</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>1.6kg</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>SABÃO PÓ TIXAN YPÊ CX C/ 1,6KG</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Detergente Líquido Limpol 500ml</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>Limpol</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>5L</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>DETERGENTE LIMPOL NEUTRO 5L</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Detergente Líquido Limpol 500ml</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Limpol</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>5L</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>DETERGENTE LIMPOL NEUTRO 5L</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Lava Roupas Líquido Ciclo Rápido Omo 1.4L</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>1.4L</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>LAVA-ROUPAS OMO CICLO RÁPIDO 1,4L</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fsyd11-2.fna.fbcdn.net/v/t39.30808-6/800260195_1680677417395989_6052030066023472506_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NjA3NjkwODc2MDM2OTgxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ceekuYgMiu4Q7kNvwFp5A4E&amp;_nc_oc=AdrUTXjkQr5ZmvBsM1Jl8zkmJRRWoje48qMPEjTvlT-mt1-rK4qlymDeWF6j-bwjZGo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd11-2.fna&amp;_nc_gid=FBYN45jntEBcmcn2HUrm_g&amp;_nc_ss=7a22e&amp;oh=00_AQJJA0EwsVrC4QDFHOSY-c1sYCmq8ib7RLBnb_8hFaVNsA&amp;oe=6AAF2170</t>
-        </is>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdRY9RSDIqW/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>SABÃO EM PÓ OMO PERFECT WHITE 4KG</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>SABÃO EM PÓ OMO PERFECT WHITE 4KG</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>5.6kg</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>SABÃO EM PÓ OMO LAVAGEM PERFEITA BAG 5,6KG</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>5.6kg</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>SABÃO EM PÓ OMO LAVAGEM PERFEITA BAG 5,6KG</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Batata Inglesa Pratic Leve Kg</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Pratic Leve</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>BATATA PALHA PRATIC LEVE PREMIUM EXTRA FINA 400G</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Batata Inglesa Pratic Leve Kg</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>Pratic Leve</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>BATATA PALHA PRATIC LEVE PREMIUM EXTRA FINA 400G</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Granola Maçã Mel Kodilar 1kg</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Kodilar</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>GRANOLA KODILAR MAÇÃ E MEL 1KG</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Granola Maçã Mel Kodilar 1kg</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Kodilar</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>GRANOLA KODILAR MAÇÃ E MEL 1KG</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Mistura para Bolo Chocolate Renata 400g</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Renata</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Mistura para Bolo Renata 400g</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Farinha de Trigo Tipo 1 Anaconda 1kg</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>Anaconda</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>FARINHA DE TRIGO ANACONDA 5KG</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I137" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Farinha de Trigo Tipo 1 Anaconda 1kg</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Anaconda</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>FARINHA DE TRIGO ANACONDA 5KG</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Incoco 2kg</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>Incoco</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>COCO RALADO INCOCO S/AÇÚCAR 1KG</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Fécula Amafil 22.5kg</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Amafil</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>22.5kg</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>SUPER FÉCULA AMAFIL 22,5KG</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Farináceos</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Fécula de Mandioca Amafil 22.5kg</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>Amafil</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>22.5kg</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>SUPER FÉCULA AMAFIL 22,5KG</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Feijão Carioca Kumbuca 1kg</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Kumbuca</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Feijão Carioca Kumbuca 1 Kg</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Amendoim Torrado Mape 1kg</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Mape</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>Amendoim Mape 1 kg R$ 14,99 UN</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t51.82787-15/809939882_18377507998237813_1274288975600878843_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NTk2MTk1NzA4NDA0NDg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n2sY0gV9TpwQ7kNvwElUGe0&amp;_nc_oc=Adpus8hv7kDn7StCZRErk7NgnfI8MRwL5YCrJBz2TGzdyz0P7gb4JsW2dn2MVhKv6whFSx-qIvYvVYrGW-bUgHLR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=xcsysJd7dJEeOQw5LtRuxA&amp;_nc_ss=7a22e&amp;oh=00_AQKp_1V5ULFRsLFk16CHwmDquKsn8Ci4WJeEosidPsjO8w&amp;oe=6AAF35E0</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdQ-2EUlqcK/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Champignon Gran Romano 1.01kg</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Gran Romano</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>1.01kg</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>CHAMPIGNON GRAN ROMANO FATIADO 1,01KG</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Champignon Gran Romano 1.01kg</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Gran Romano</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>1.01kg</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>CHAMPIGNON GRAN ROMANO FATIADO 1,01KG</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Incoco 2kg</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Incoco</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>COCO RALADO INCOCO S/AÇÚCAR 1KG</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Massas</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>Macarrão Espaguete Galo 500g</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>Galo</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>Macarrão Sêmola Galo Espaguete N°8 500g</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I147" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t51.82787-15/808786763_18194605573391764_8637120294653794930_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NTYwODI1MDE1ODQxMjE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EM-XyOpgmw0Q7kNvwHs95MM&amp;_nc_oc=Adq9swQ1XrXzYDzWoWg-rCSpcJhc1IGccKPoKoogI-Lq1d3l4VeYVsLYvbKZ7ln907s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=PEYjWdLLZRg56QfirQZvTQ&amp;_nc_ss=7a22e&amp;oh=00_AQJfbke6z4nGugpr_CH_U-kZaUt-tfmuc8LvqYvRlP5GPA&amp;oe=6AAF1C03</t>
-        </is>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdPuaaaiel-/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Molho Shoyu Ponzan Karui 1.01L</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Karui</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>1.01L</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>MOLHO SHOYU KARUI PONZAN 1,01L</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Molho Shoyu Karui Ponzan 1.01L</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>Karui Ponzan</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>1.01L</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>MOLHO SHOYU KARUI PONZAN 1,01L</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Tomate Longa Vida Fugini Kg</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Fugini</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>1.7kg</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>EXTRATO DE TOMATE FUGINI SACHÊ 1,7KG</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Tomate Longa Vida Fugini Kg</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>Fugini</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>1.7kg</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>EXTRATO DE TOMATE FUGINI SACHÊ 1,7KG</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I151" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Alho Estrela Kg</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Estrela</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>TEMPERO ESTRELA KI ALHO 1KG</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Alho Estrela Kg</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>Estrela</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>TEMPERO ESTRELA KI ALHO 1KG</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Mostarda Amarela Cepêra 3.3kg</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Cepêra</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>3.3kg</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>MOSTARDA CEPÊRA AMARELA 3,3KG</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Mostarda Amarela Cepêra 3.3kg</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>Cepêra</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>3.3kg</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>MOSTARDA CEPÊRA AMARELA 3,3KG</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Maionese Hellmann's 1.6kg</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Hellmann'S</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>1.6kg</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>MAIONESE HELLMANN'S BAG 1,6KG</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Maionese Hellmann's Bag 1.6kg</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>Hellmann'S</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>1.6kg</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>MAIONESE HELLMANN'S BAG 1,6KG</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Molho de Pimenta Caseiro D'ajuda 3.2L</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>D'Ajuda</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>3.2L</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>MOLHO DE PIMENTA D'AJUDA CASEIRO 3,2L</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802811527_1373956478157643_7332524772867260721_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzQxNDUwMzI2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6sR_1NITBDwQ7kNvwHhx1Pi&amp;_nc_oc=AdrElzS5oXBph-WpsupSJfG8im604tZKD-c54yJefDcncRx9jXRoqfB0KrewiA3YeoPRAzPGEhHndJ3_FBlX0XIq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQJ1whdM3dd-l_ERrCBFi20yqCy1oqFV3wzfjTjSzBHqag&amp;oe=6AAF30B3</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>Molho de Pimenta Caseiro D'ajuda 3.2L</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>D'Ajuda</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>3.2L</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>MOLHO DE PIMENTA D'AJUDA CASEIRO 3,2L</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I159" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/799983711_1373956454824312_4247189602231464541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4NTYzMzg3Nzk5MzI4NTgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-zY_pS8UjtAQ7kNvwHHYcSa&amp;_nc_oc=AdoD4kQrrAw8ijIKzrrQKM7-fRi3dn7fQCRDaMsu6wY1W9pMfbotvwySooPEaxLbIEX5tcRfnu1S19vA1O9gitpw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQL-Oxyna6rAhFXuHsGQ4uQBg2hYvTcZVPiGhint7i-2LA&amp;oe=6AAF33B2</t>
-        </is>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Beterraba Kg</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>BETERRABA KG 4,19</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280658_18586933327067900_8967671399210914403_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NjM1MTI0NTE2NjQ2MjkzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VGio4S2NXpQQ7kNvwEokYIM&amp;_nc_oc=AdrZg0LcAs66rYo_Q-pQBQvB1EWT7kqVlCIXdY-t8ZoPJA-FPryB-JrOqaL4-pPOkjnPRFCBYXJdlVByaoreXTXV&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQK-QuSbisNGA3VJJa_vyq8r_qUe0gGxk74jzhfjTekuUg&amp;oe=6AAF2464</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Morgote Kg</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>MORGOTE KG 7,39</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806280672_18586933348067900_5813014675912392816_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4NjM1MTI3NDU1MTc3Mjk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=QaahGgns67UQ7kNvwF9wvXM&amp;_nc_oc=AdoK8VQVcsv0i2OYBB8gKz-HxGdOAdK2DQCGpS0HrOjZurUAuElCzSWZZnp32jfMngu-yTfBCNONqlOjEVphRcA2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=uvded34zNID89bealkDhHA&amp;_nc_ss=7a22e&amp;oh=00_AQLCGjow6aK75fWgWJDjC9kDp0OAFLktP9Td7IA25EJK2A&amp;oe=6AAF1630</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdSXWJalfYt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Marmitex com Tampa Wyda Nº8 c/ 100</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Wyda</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>c/ 100</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>MARMITEX WYDA Nº8 MÁQUINA C/ TAMPA C/ 100UND</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>Palito para Espeto de Bambu 30cm Paraná c/ 50</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>Paraná</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>c/ 50</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>PALITO PARANÁ ESPETO DE BAMBU 30CM C/ 50UND</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/802717756_1373956501490974_8815510270807842297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NTYzMzg3NjgzNTY2MDU4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ViXhykCZt7EQ7kNvwHRXsDO&amp;_nc_oc=Adr02k-BOixQ0vDM9jcMLWGDIYZxeY-0PlumscfSMgsA-2gK-B5gfT8IYQSmfNeLbjNMgz6U5f1TvwFgWbtYZxk1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKoQKI2GbZ_MzdjzjFdyJQdJ8VuQfA02qQAI7T6Z0CJBQ&amp;oe=6AAF4605</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Espeto de Bambu 30cm Paraná c/ 50</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Paraná</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>c/ 50</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>PALITO PARANÁ ESPETO DE BAMBU 30CM C/ 50UND</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-hou1-1.cdninstagram.com/v/t39.30808-6/803268794_1373956538157637_1110008139259589825_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NTYzMzg3NzY5MTI5OTMzNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=-XdCCJZildUQ7kNvwG0VJKB&amp;_nc_oc=AdrImf8hfm8946pj5Y5onKqG2C-3_Fi8TCXJy057Gj_-OHWvyTbWoUdwrtx4D77C-ML7vZzw9UPn5acQkcnGX6wJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=yYSIYOqkdKV7lfGB2xRqxg&amp;_nc_ss=7a22e&amp;oh=00_AQKJO1YlTe-gtoGPCRj9zXi_SYP1j2uhuiTGYbph3umf5Q&amp;oe=6AAF2E11</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdP0OiGDS85/</t>
+          <t>https://www.instagram.com/p/DdWKCIKlkxV/</t>
         </is>
       </c>
     </row>
@@ -8334,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8378,16 +5596,16 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6.382857142857143</v>
+        <v>21.56333333333333</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2.49</v>
+        <v>7.99</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>14.99</v>
+        <v>64.98999999999999</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -8397,16 +5615,16 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>33.11458333333334</v>
+        <v>26.59333333333333</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>1.39</v>
+        <v>12.98</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>109.9</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -8416,92 +5634,73 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>10.44833333333333</v>
+        <v>10.75388888888889</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>37.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7.417272727272728</v>
+        <v>7.965</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>16.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>15.57333333333333</v>
+        <v>25.66</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.99</v>
+        <v>8.98</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>32.99</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>9.289999999999999</v>
+        <v>12.765</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2.99</v>
+        <v>1.49</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>6.612222222222222</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>11.99</v>
+        <v>34.99</v>
       </c>
     </row>
   </sheetData>
@@ -8515,7 +5714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8549,33 +5748,33 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="B2" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>37.4</v>
+        <v>34.99</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28.9</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>79.90000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>79.90000000000001</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -8585,13 +5784,13 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>17.59666666666666</v>
+        <v>12.99</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>16.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -8601,13 +5800,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7.556666666666668</v>
+        <v>11.04428571428572</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -8617,90 +5816,90 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>14.84416666666667</v>
+        <v>29.4875</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5.69</v>
+        <v>31.4675</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.39</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>28.9</v>
+        <v>14.63071428571429</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28.9</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>17.39</v>
+        <v>12.98</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.99</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>24.9</v>
+        <v>6.09</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>24.9</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>5.441515151515151</v>
+        <v>3.99</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1.99</v>
@@ -8709,161 +5908,209 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>16.695</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>25.972</v>
+        <v>9.49</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>8.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>43.72777777777778</v>
+        <v>17.24</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2.99</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>24.4</v>
+        <v>4.29</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>18.9</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>49.74833333333333</v>
+        <v>5.99</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>24.536</v>
+        <v>13.99</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>6.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4.59</v>
+        <v>5.99</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>23.74833333333333</v>
+        <v>5.29</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>9.9</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>19.16</v>
+        <v>3.99</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4.19</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Pet Shop</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Óleos e Azeites</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>2.79</v>
+      <c r="C22" s="6" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>11.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="63" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="77" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="620" customWidth="1" min="9" max="9"/>
+    <col width="618" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -544,7 +544,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -554,47 +554,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Copo Descartável Fonplast 100 180ml</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Fonplast</t>
-        </is>
-      </c>
+          <t>Copo Americano 190ml</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>180ml</t>
+          <t>190ml</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>COPO DESCARTÁVEL FONPLAST 180ML C/ 100UND</t>
+          <t>Copo Americano 190 ml</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3.99</v>
+        <v>1.49</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -604,47 +600,47 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Copo Descartável Fonplast 100 180ml</t>
+          <t>Assadeira Vidro Reta com Tampa Marinex 3.5L</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Fonplast</t>
+          <t>Marinex</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>180ml</t>
+          <t>3.5L</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>COPO DESCARTÁVEL FONPLAST 180ML C/ 100UND</t>
+          <t>Assadeira Marinex Reta com Tampa 3,5 litros R$ 49,90</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>3.99</v>
+        <v>49.9</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -654,47 +650,43 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pilha Rayovac Alcalina Aa c/ 4</t>
+          <t>Varal de Chão Mor Slim Branco</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Rayovac</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>c/ 4</t>
-        </is>
-      </c>
+          <t>Mor</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>PILHA RAYOVAC ALCALINA AA PEQUENA C/ 4UND</t>
+          <t>VARAL CHÃO MOR SLIM BRANCO UNI</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.99</v>
+        <v>119.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -704,47 +696,43 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Pilha Alcalina Aa Pequena Rayovac c/ 4</t>
+          <t>Liquidificador Mondial Preto L900 127v</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Rayovac</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>c/ 4</t>
-        </is>
-      </c>
+          <t>Mondial</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>PILHA RAYOVAC ALCALINA AA PEQUENA C/ 4UND</t>
+          <t>LIQUIDIFICADOR MONDIAL PRETO L900 127V UNI</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>12.99</v>
+        <v>129.9</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -754,339 +742,343 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bule Térmico Tramontina Exata 500ml</t>
+          <t>Ventilador Mondial Power 40cm 127v</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tramontina</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
+          <t>Mondial</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BULE TÉRMICO TRAMONTINA EXATA 500ML</t>
+          <t>VENTILADOR MONDIAL SUPER POWER 40CM 127V UNI DE: R$ 199,99 POR: R$ 159,90</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>41.9</v>
+        <v>159.9</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Bule Térmico Exata Tramontina 500ml</t>
+          <t>Gin Rock's 1L</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Tramontina</t>
+          <t>Rock'S</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>BULE TÉRMICO TRAMONTINA EXATA 500ML</t>
+          <t>BEBIDA GIN ROCK'S 1L DE: R$ 35,99 POR: R$ 26,99</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>41.9</v>
+        <v>26.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Lixeira Mor Linha Ágata 3L</t>
+          <t>Vinho Reservado Concha Toro Concha Y Toro 750ml</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Concha Y Toro</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3L</t>
+          <t>750ml</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>LIXEIRA MOR LINHA ÁGATA 3L</t>
+          <t>VINHO CHILENO RESERVADO CONCHA Y TORO 750ML DE: R$ 48,99 POR: R$ 34,99</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>54.9</v>
+        <v>34.99</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Grelha Tramontina Inox 72x23cm</t>
+          <t>Cerveja Lata Itaipava 269ml</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Tramontina</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>Itaipava</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>269ml</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>GRELHA TRAMONTINA INOX 72X23CM</t>
+          <t>Cerveja Itaipava lata 269 mL</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/809209189_18378178603237813_4341481546895005542_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1MjMxMjQ1MTk5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ltusphbvbjUQ7kNvwHWptYf&amp;_nc_oc=Adqobdk4EhA_pDwSoN4MAOGE9ieVB-p6BIIBGirchg6MVpJXK-gOa58hkqUL8dlPb6uRGk9vLRyil8fHoEDmUYWZ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKU5WNF10-qia92LY4Dzmrh4C4zaNj1uYD0_5444pzabQ&amp;oe=6AB44D3A</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Grelha Inox Tramontina 72x23cm</t>
+          <t>Cerveja Long Neck Stella Artois 330ml</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tramontina</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>Stella Artois</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>330ml</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>GRELHA TRAMONTINA INOX 72X23CM</t>
+          <t>Cerveja Stella Artois Long Neck Tradicional 330ml R$ 6,99</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>6.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Térmica Mor 34L</t>
+          <t>Cerveja Extra Long Neck Corona 330ml</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Corona</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>34L</t>
+          <t>330ml</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>CAIXA TÉRMICA MOR 34L</t>
+          <t>CERVEJA CORONA EXTRA 330ML DE: R$ 7,59 POR: R$ 6,99</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>6.99</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Térmica Mor 34L</t>
+          <t>Cerveja 12x Itaipava 269ml</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Itaipava</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34L</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA TÉRMICA MOR 34L</t>
+          <t>CERVEJA ITAIPAVA CX C/12X269ML DE: R$ 35,88 POR: R$ 26,99</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>26.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1096,47 +1088,47 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Skol Antarctica 350ml</t>
+          <t>Cerveja Michelob Ultra 6x 330ml</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Michelob Ultra</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>330ml</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Skol ou Antarctica Litrinho Retornável VD 300ml</t>
+          <t>CERVEJA MICHELOB ULTRA CX C/6X330ML DE: R$ 47,94 POR: R$ 36,99</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2.49</v>
+        <v>36.99</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1146,47 +1138,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Original Litrinho Retornável Antarctica 300ml</t>
+          <t>Cerveja Pilsen Lata Pack 15 Skol 269ml</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Skol</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Original Litrinho Retornável VD 300ml</t>
+          <t>Cerveja Skol 269ml Multipack c/15 Latas R$ 43,35</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3.09</v>
+        <v>43.35</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1196,26 +1188,26 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Extra Long Neck Corona 330ml</t>
+          <t>Cerveja Original Lata Pack 15 269ml</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Corona</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA CORONA EXTRA 330ML DE: R$ 7,59 POR: R$ 6,99</t>
+          <t>Cerveja Original Multipack C/ 15 Latas de 269ml R$ 50,85</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6.99</v>
+        <v>50.85</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1224,12 +1216,12 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
@@ -1241,81 +1233,81 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cerveja 12 Itaipava 269ml</t>
+          <t>Refrigerante Guaraná Antarctica 2L</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Itaipava</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CERVEJA ITAIPAVA CX C/12X269ML</t>
+          <t>REFRIGERANTE GUARANÁ ANTARCTICA ORIGINAL 2L DE: R$ 9,49 POR: R$ 8,99</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>25.99</v>
+        <v>8.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Pure Gold 8x Stella Artois 269ml</t>
+          <t>Refrigerante Pet Coca-Cola 2.5L</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Stella Artois</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>2.5L</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA STELLA ARTOIS PURE GOLD CX C/8X269ML DE: R$ 38,32 POR: R$ 32,99</t>
+          <t>Refrigerante Coca-Cola Tradicional/Zero PET 2,5 litros R$ 11,49</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>32.99</v>
+        <v>11.49</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1324,162 +1316,162 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Pack 15 Latas Skol 269ml</t>
+          <t>Uva Niagara Garibaldi 500g</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Skol</t>
+          <t>Garibaldi</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>1.5L</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Skol Multipack c/ 15 Und. Lata 269ml</t>
+          <t>SUCO UVA TINTO INTEGRAL GARIBALDI 1,5LTS</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43.35</v>
+        <v>15.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Original Pack 15 Latas Antarctica 269ml</t>
+          <t>Achocolatado em Pó Toddy 750g</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Toddy</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>750g</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Original Multipack c/ 15 Und. Lata 269ml</t>
+          <t>ACHOCOLATADO PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>50.85</v>
+        <v>16.99</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Pet Antarctica 2L</t>
+          <t>Água Mineral Puríssima Fardo 12x 500ml</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Puríssima</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Antarctica 2 Litros</t>
+          <t>ÁGUA MINERAL PURÍSSIMA COM E SEM GÁS FD C/ 12X497/ 500ML</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.69</v>
+        <v>23.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -1491,152 +1483,152 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Original Antarctica 2L</t>
+          <t>Empanado de Frango Perdigão 100g</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Perdigão</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANÁ ANTARCTICA ORIGINAL 2L DE: R$ 9,49 POR: R$ 8,99</t>
+          <t>EMPANADO FRANGO TRADICIONAL PERDIGÃO 100G</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>8.99</v>
+        <v>1.89</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Energético Monster Lata 473ml</t>
+          <t>Frango Oriental Pedaços Seara 275g</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>473ml</t>
+          <t>275g</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Energético Monster 473ml</t>
+          <t>FRANGO ORIENTAL SEARA PEDAÇOS 275G</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Uva Niagara Garibaldi 500g</t>
+          <t>Sobrecoxa de Frango Canção kg</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Garibaldi</t>
+          <t>Canção</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Suco Garibaldi 1,5 Litro</t>
+          <t>Coxas e Sobrecoxa Canção R$ 7,99 kg</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1646,47 +1638,43 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Empanado de Frango Sadia 100g</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Coxinha das Asas de Frango Sem Tempero Kg</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>EMPANADO DE FRANGO SADIA 100G</t>
+          <t>COXINHAS DAS ASAS FRANGO S/TEMPERO</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.49</v>
+        <v>11.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1696,47 +1684,47 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Super Frango kg</t>
+          <t>Moela de Frango Seara 1kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Super Frango</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Super Frango EUA 600g</t>
+          <t>MOELA FRANGO SEARA BDJ 1KG DE: R$ 19,99 POR: R$ 15,99</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1746,47 +1734,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Meio da Asa de Frango Sabor México Frango Super Frango 600g</t>
+          <t>Frango Inteiro Nho Bento kg</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Super Frango</t>
+          <t>Nho Bento</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Meio da Asa de Frango Super Frango México 600g</t>
+          <t>FRANGO INTEIRO CAIPIRA NHO BENTO</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1796,12 +1784,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Coxa de Frango Iqf Sadia 1kg</t>
+          <t>Filé de Peito de Frango Lar kg</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Lar</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1811,32 +1799,32 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA IQF PCT 1KG</t>
+          <t>FILÉ PEITO FRANGO LAR BDJ C/1KG DE: R$ 24,99 POR: R$ 18,99</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>9.99</v>
+        <v>18.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1846,12 +1834,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Coxa de Frango Iqf Sadia 1kg</t>
+          <t>Meio das Asas de Frango Seara 1kg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1861,25 +1849,25 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA IQF PCT 1KG DE R$ 12,49 POR: R$ 9,99 UND</t>
+          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -1891,67 +1879,67 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Sobrecoxa de Frango Seara kg</t>
+          <t>Hambúrguer Bovino Aves Sadia 56g</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>56g</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>COXAS E SOBRECOXAS FRANGO SEARA R$ 9,99 Kg</t>
+          <t>HAMBÚRGUER BOVINO E AVES SADIA 56G</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>9.99</v>
+        <v>1.39</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813606357_1683503363780061_5346559934286841060_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODE1NDk1OTI1NDA5MTk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K8T4jVFSle4Q7kNvwFW0osS&amp;_nc_oc=AdpYSNtZS4eZxSlFWQhHbN5IVGw6HKHTKVLIhoJzapByFNO8e1Tk27ymu-9rqigbITE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQIEA6tVoTXgnc2WN3L2Mn0YUTynd6yaMADHfyE6tpy3gw&amp;oe=6AB30471</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Frango Passarinho Lar 1kg</t>
+          <t>Costela Bovina Sulbeef kg</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Lar</t>
+          <t>Sulbeef</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1961,11 +1949,11 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO LAR PCT C/1KG</t>
+          <t>Costela Bovina Sulbeef R$ 22,99 kg</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>11.99</v>
+        <v>22.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1974,12 +1962,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
@@ -1991,45 +1979,41 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Coxas de Frango Sadia 1kg</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Costela Bovina Minga kg</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>COXAS FRANGO SADIA PCT C/1KG</t>
+          <t>COSTELA MINGA kg R$ 25,99</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>12.99</v>
+        <v>25.99</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2041,45 +2025,41 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sobrecoxas de Frango Sadia 1kg</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Contrafilé Bovino kg</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>SOBRECOXAS FRANGO SADIA BDJ C/1KG</t>
+          <t>CAPA CONTRA FILÉ BOV. kg R$ 37,99</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>13.99</v>
+        <v>37.99</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2091,45 +2071,41 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Meio das Asas Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Cupim Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG</t>
+          <t>CUPIM BOV. kg R$ 45,99</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>25.99</v>
+        <v>45.99</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2141,45 +2117,41 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Coração de Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Picanha Bovina kg</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CORAÇÃO FRANGO SEARA PCT C/1KG</t>
+          <t>PICANHA FATIADA BOV. kg R$ 45,99</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>35.99</v>
+        <v>45.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2168,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovina Kg</t>
+          <t>Maminha Bovina kg</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -2207,25 +2179,25 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>MOCOTÓ BOV. R$ 12,99 Kg</t>
+          <t>Maminha Bov. kg R$ 49,99</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>12.99</v>
+        <v>49.99</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813878262_1683503290446735_5692864880221851576_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODE1NDk1OTcwNzA5MDAxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4uaQxp_qrL8Q7kNvwFM626O&amp;_nc_oc=Adq0ErP9ugSNWAVuDFwIDb9JsH6NS2IftZupW1DfFhaFQ2AHFYihI6wIj87Tqyf2IUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQIuEZHuRLI98d3TXPBu_M4GGRnZLF4ZWdztvFDYuJys7A&amp;oe=6AB31C1D</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2214,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Dobradinha Bovina Kg</t>
+          <t>Alcatra Bovina kg</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -2253,163 +2225,167 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>DOBRADINHA BOV. R$ 18,99 Kg</t>
+          <t>Coração Alcátra kg R$ 49,99</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18.99</v>
+        <v>49.99</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814584728_1683503263780071_1762437614910095390_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODE1NDk2MDY0NjU4MDQzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5Q8Zuy6OLKUQ7kNvwEepjEu&amp;_nc_oc=Adp9faIa3zy_AfOi5RnM7zok8BSdnWQjiqCITuRKB_c1atDottmDHSN9cwzYLfz4TX4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQIuzc-ubv42GVHf2n5Q50gsSDYMYmduPfd1fYjJD96QDw&amp;oe=6AB317CE</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
+          <t>Camarão Inteiro Costa Sul 400g</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Costa Sul</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Costela Bovina Kg</t>
+          <t>CAMARÃO COSTA SUL INTEIRO PCT C/ 400G</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>21.99</v>
+        <v>24.99</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Filé de Tilápia Bello 800g</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina R$ 21,99 KG</t>
+          <t>FILÉ PEIXE TILÁPIA BELLO 800G DE: R$ 48,99 POR: R$ 35,99</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>21.99</v>
+        <v>35.99</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída Bovina kg</t>
+          <t>Peixe Inteiro Pintado</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída R$ 28,99 KG</t>
+          <t>PEIXE INTEIRO PINTADO</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>28.99</v>
+        <v>42.99</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2421,271 +2397,295 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Costela Janelão Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>Mortadela Defumada Seara 180g</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>180g</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>COSTELA JANELÃO BOV R$ 29,99 Kg</t>
+          <t>MORTADELA DEFUMADA SEARA 180G</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>29.99</v>
+        <v>7.99</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813825529_1683503330446731_7808177810740837586_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODE1NDk1OTM5NjY4NTQwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nvJJfJIrzpoQ7kNvwHjkhEb&amp;_nc_oc=AdpbHtVkYLItm2-DTwW0-nUL3kx8EvLTCljB5-THhQsr3YBFzEx7HVaF7e8FpeuCHk0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQJHlAK79VlFlNierXM7Y21kHWhggc-WUcEoSOdi8mELZQ&amp;oe=6AB3188E</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ponta de Peito Bovino Sem Osso Kg</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
+          <t>Linguiça Toscana Seara kg</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>370g</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Ponta de Peito Bovino sem Osso Kg</t>
+          <t>LINGUIÇA PAIO SEARA 370G</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>31.99</v>
+        <v>8.99</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ponta de Peito Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Salsicha Hot Dog Perdigão kg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Perdigão</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Ponta de Peito Bovino R$ 31,99 KG</t>
+          <t>Salsicha Seara/ Perdigão R$ 9,99 kg</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>31.99</v>
+        <v>9.99</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Músculo Bovino c/ Osso kg</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
+          <t>Presunto Cozido Seara kg</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>180g</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Músculo sem Osso R$ 32,99 KG</t>
+          <t>PRESUNTO FATIADO SEARA 180G</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>32.99</v>
+        <v>9.99</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Bisteca Contrafilé Bovina kg</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Linguiça Toscana Sadia kg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Bisteca Bovina Kg</t>
+          <t>LINGUIÇA TIPO PORTUGUESA SADIA 400G</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>33.99</v>
+        <v>9.99</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr"/>
+          <t>Pernil Suíno Max Free kg</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Max Free</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Coxão Duro R$ 35,99 KG</t>
+          <t>Pernil Suíno Frigorífico Max Free R$ 10,99 kg</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>35.99</v>
+        <v>10.99</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
@@ -2697,15 +2697,19 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>Salsicha Hot Dog Perdigão kg</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Perdigão</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2713,71 +2717,75 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>CAPA CONTRA FILÉ BOV. R$ 37,99 Kg</t>
+          <t>SALSICHA HOT DOG PERDIGÃO</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>37.99</v>
+        <v>10.99</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813582771_1683503367113394_6305376521844167938_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODE1NDk1OTA4NjI5MjExNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Q6brmyjqX3oQ7kNvwFwVO-6&amp;_nc_oc=AdrV0qOIa9pxPTUOWeQoWweb6EGadSggQ8hKJYVReCgxAXxJ7iVVWnRVD4aQFO8-HXQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQKpIqkINqo9jjthK-saChqJNWmn_KQKUwtfHB3Z7oUKxw&amp;oe=6AB2FD6E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Bisteca Contrafilé Bovina kg</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr"/>
+          <t>Linguiça Toscana Perdigão kg</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Perdigão</t>
+        </is>
+      </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BISTECA BOV. R$ 38,99 Kg</t>
+          <t>Linguiça Suína Perdigão R$ 14,99 kg</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>38.99</v>
+        <v>14.99</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813837244_1683503280446736_4465832855299439554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODE1NDk1ODY5MjA2NzQxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mMXgcfe29i4Q7kNvwGpto0-&amp;_nc_oc=AdpvoXj0sYSbyritSNTPOrbqXC-Y3imC2i8VRNeIbsMGh_DfrwtmvWFuSmNoiz1BVY0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQL1otPhP-46hcpqr3xI2EbLNqJgy2Ws9-R90nDq2DWsjg&amp;oe=6AB33080</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
@@ -2789,15 +2797,19 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>Linguiça Toscana Excelência kg</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Excelência</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2805,284 +2817,292 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>COXÃO DURO BOV. R$ 39,99 Kg</t>
+          <t>LINGUIÇA TOSCANA EXCELÊNCIA kg R$ 16,99</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>39.99</v>
+        <v>16.99</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813582784_1683503293780068_8818531689853998301_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODE1NDk1OTM0NjM1MDg2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LWmNIXB998wQ7kNvwGGTQ0q&amp;_nc_oc=AdpyW86R6RhMidjevkdhc2yWA43Mgz5vrqpZUvDXyl33eq58DQhkZGhtNgoXxVlzbx0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQKWJAeyQPKUIuixYUrKv8dCv1vNMkV7iTWkpSHKP8P1sw&amp;oe=6AB324D2</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Fraldinha Bovina Friboi kg</t>
+          <t>Costela Suína Max Free 1kg</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Friboi</t>
+          <t>Max Free</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Fraldinha Friboi R$ 42,99 KG</t>
+          <t>Costela Suína Max Free R$ 18,99 kg</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>42.99</v>
+        <v>18.99</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Alcatra Bovina kg</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>Linguiça Toscana Fricó kg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Fricó</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Alcatra com Maminha R$ 47,99 KG</t>
+          <t>Linguiça Fina Apimentada Fricó R$ 19,99 kg</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>47.99</v>
+        <v>19.99</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>Linguiça Calabresa Excelência kg</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Excelência</t>
+        </is>
+      </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Contra Filé Bovino Kg</t>
+          <t>Linguiça Calabresa Excelência R$ 19,99 kg</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>51.99</v>
+        <v>19.99</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Camarão Inteiro Congelado Fisgo 150g</t>
+          <t>Presunto Cozido Excelência kg</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Fisgo</t>
+          <t>Excelência</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>CAMARÃO FISGO 10/30 INTEIRO CONGELADO 150G</t>
+          <t>Presunto Cozido Excelência R$ 22,99 kg</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>11.49</v>
+        <v>22.99</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Camarão Inteiro Congelado Fisgo 150g</t>
+          <t>Mortadela Defumada Seara 1kg</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Fisgo</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>CAMARÃO FISGO 10/30 INTEIRO CONGELADO 150G DE R$ 14,90 POR: R$ 11,49 UND</t>
+          <t>Mortadela Seara Defumada R$ 25,99 kg</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>11.49</v>
+        <v>25.99</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Filé de Peixe Tilápia Seara 600g</t>
+          <t>Bacon em Manta Seara kg</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3092,16 +3112,16 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>FILÉ PEIXE TILÁPIA SEARA PCT C/600G</t>
+          <t>Bacon Manta Seara R$ 29,99 kg</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>32.99</v>
+        <v>29.99</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3110,94 +3130,90 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Sadia 200g</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Mandioca Congelada Kg</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Sadia Fatiada - 200g</t>
+          <t>Mandioca Congelada kg R$ 5,99</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813756458_18195006382391764_173094445756565630_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMzMTY3ODkzODkyNjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WvxC04rd5GsQ7kNvwEfGniw&amp;_nc_oc=AdpRKJN_cJ37tp0NJOqwyoPe8pX9GaDXg7AYbRrFY-3dbcvoIQhr8fxUHty3QSDBXP0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=U0yLOy2JR7ejSHOGGrso_A&amp;_nc_ss=7a22e&amp;oh=00_AQIm62y9aIHARzghoXiRL5wyJP7FPJVIF_MiQfiILx9Qpg&amp;oe=6AB30531</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZZofpl4yN/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Alho Perdigão Kg</t>
+          <t>Tekitos Seara 300g</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Linguica Na Brasa Perdigão Alho e Ervas 600g</t>
+          <t>TEKITOS TRADICIONAL SEARA 300G</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -3205,429 +3221,449 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Paleta Bovina kg</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
+          <t>Lasanha Sabores Sadia 600g</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>600g</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Pernil ou Paleta Suína - Kg</t>
+          <t>LASANHA SADIA SABORES 600G</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pernil Suíno kg</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>Sorvete Gebon 1.5L</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Gebon</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1.5L</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Pernil Suíno R$ 10,99 KG</t>
+          <t>Sorvete Gebon Sabores 1,5 litros R$ 22,99 un</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>10.99</v>
+        <v>22.99</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Paleta Bovina kg</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
+          <t>Açaí Origem Toda Hora 1.5L</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Origem Toda Hora</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1.5L</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Paleta Suína R$ 10,99 KG</t>
+          <t>AÇAÍ ORIGEM TODA HORA 1,5L</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>10.99</v>
+        <v>22.99</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Paleta Bovina kg</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>Sabonete em Barra Fragrâncias Nivea 85g</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Nivea</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>85g</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Paleta / Pernil Suíno R$ 10,99 Kg</t>
+          <t>Sabonete em Barra Nivea Fragrâncias 85g</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>10.99</v>
+        <v>2.29</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813825506_1683503307113400_5307059315658949494_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODE1NDk1OTk4MzkyODQzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=411PCd-_vUIQ7kNvwHS0yM7&amp;_nc_oc=Ado59hzVq9FJpH3aI23boAvGyptKZNC-zjqb3ZU643SP8-YrG0cda_0hAlE7zF5aDTc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQKXjK3GSk9Mjn0iJe25-X14IJKCSDyXmlfxqT6w-Xj1cA&amp;oe=6AB32C31</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Perdigão kg</t>
+          <t>Creme Dental Dentes Brancos Sorriso 120g</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Sorriso</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>120g</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Suína Perdigão Kg</t>
+          <t>Creme Dental Sorriso Dentes Brancos 120 g</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>13.99</v>
+        <v>4.99</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia5-2.cdninstagram.com/v/t51.82787-15/813912362_18195006856391764_5838021063099320911_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNjA2MjkyNjExNTQ3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wJKCj54gwdwQ7kNvwHoGuru&amp;_nc_oc=Adri4L8tdnydtjliTqzkjh3kRantgE7NrFI0YTFX3sjZv95XVpIJtYNDC4OU2kJqVJPrmlX4eEljyfuZek3sSv6c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-2.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKuneYVlvRhT7KOxWuW23rq-j13BvzP-5IShwFCmFDBNg&amp;oe=6AB31776</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Bisteca Suína kg</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Kit Shampoo Condicionador Seda 300ml</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Seda</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>BISTECA SUÍNA R$ 13,99 / Kg</t>
+          <t>Kit Shampoo Seda 300 ml + Condicionador 190 ml</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>13.99</v>
+        <v>16.99</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813520341_1683503353780062_7189419010486612385_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODE1NDk1OTA5NDY5MTU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7JWbW2AqgQ4Q7kNvwHFeORN&amp;_nc_oc=AdojpHI-TBr4brDstCBYcoPd2Xjt8plEq_qEJw34HxndbYaZiPdEP72_rhiZnDQtkh8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQL4RyRr7rik1ivvX2HpFX8FPR2JRZ2Wba8jDBw724UDWA&amp;oe=6AB3080B</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Presunto Cozido Sadia kg</t>
+          <t>Shampoo Huggies 360ml</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Huggies</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Presunto Sadia Barra ou Pedaço Kg</t>
+          <t>SHAMPOO HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>14.99</v>
+        <v>16.99</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Excelência kg</t>
+          <t>Shampoo Huggies 360ml</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Excelência</t>
+          <t>Huggies</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Excelência R$ 15,99 KG</t>
+          <t>SHAMPOO HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>15.99</v>
+        <v>16.99</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Perdigão kg</t>
+          <t>Shampoo Kids Huggies 360ml</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Huggies</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Suína Perdigão Kg</t>
+          <t>SHAMPOO HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
@@ -3635,237 +3671,245 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/813546232_1683503327113398_7309874569615464394_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODE1NDk1OTUyMjU1NTg4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjA0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=jjbIyMdmp3UQ7kNvwGLwkti&amp;_nc_oc=AdpYz-kRePV3bQOjttSB2ag2OPr7ZdfSPHvsi_fiRNzfEqDF-z5HUwb95lLaYvKTbiI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=gy2XljP3VIWXve-rbkSKfA&amp;_nc_ss=7a22e&amp;oh=00_AQJubaTmxqSPnFQ23P8JUGuMS1D9FcBhlVWtFIez-l9axg&amp;oe=6AB32774</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdYxdO-DStG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Costela Suína Kg</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Condicionador Huggies 360ml</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Huggies</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Costela Suína R$ 19,99 KG</t>
+          <t>CONDICIONADOR HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>19.99</v>
+        <v>17.9</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana kg</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr"/>
+          <t>Condicionador Huggies 360ml</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Huggies</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Apimentada R$ 21,99 KG</t>
+          <t>CONDICIONADOR HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>21.99</v>
+        <v>17.9</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fumu3-1.fna.fbcdn.net/v/t51.82787-15/814407250_17910545913496981_4976285175004348142_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODUxOTE4MjE3MTM2MTIwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Vgn--kejP8MQ7kNvwGVcolz&amp;_nc_oc=AdpX4H3hun6dcnRRFPRgeCYd6GubaxWwT05421ECPValx_vq0LtDtItfuLgUTEtnlFc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fumu3-1.fna&amp;_nc_gid=6RXbZVPxh7o2R61nRAzL_g&amp;_nc_ss=7a22e&amp;oh=00_AQLYdUX7vHt8I5IVqPPnOeZwg9KWZsLdVoI0b8p_Hiibdg&amp;oe=6AB33148</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaERBpJ8-3/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Perdigão Ouro Kg</t>
+          <t>Condicionador Kids Huggies 360ml</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Huggies</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>MORTADELA DEFUMADA PERDIGÃO OURO</t>
+          <t>CONDICIONADOR HUGGIES 360ML</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>24.99</v>
+        <v>17.9</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Presunto Cozido kg</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
+          <t>Absorvente Noturno 30 Intimus</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Intimus</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>PRESUNTO FATIADO</t>
+          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>24.99</v>
+        <v>25.99</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Bacon em Manta Excelência kg</t>
+          <t>Absorvente Noturno Intimus c/ 30</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Excelência</t>
+          <t>Intimus</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>BACON DEFUMADO EXCELÊNCIA DE: R$ 38,99 POR: R$ 25,99 KG</t>
+          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
@@ -3873,74 +3917,74 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Açaí Origem Toda Hora 1.5L</t>
+          <t>Absorvente Intimus Noturno Leve Mais Pague Menos c/ 30</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Origem Toda Hora</t>
+          <t>Intimus</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>c/ 30</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>AÇAÍ ORIGEM TODA HORA 1,5L</t>
+          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>22.99</v>
+        <v>25.99</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3950,40 +3994,36 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Sabonete em Barra Protex 85g</t>
+          <t>Roupa Íntima Unissex Classic Plenitud</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Protex</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>85g</t>
-        </is>
-      </c>
+          <t>Plenitud</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Sabonete em Barra Protex, fragrâncias, 85g</t>
+          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3.29</v>
+        <v>28.9</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
@@ -4000,40 +4040,40 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Máxima Proteção Anticáries Colgate 90g</t>
+          <t>Roupa Íntima Unissex Classic Plenitud c/ 8</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Colgate</t>
+          <t>Plenitud</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>90g</t>
+          <t>c/ 8</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>CREME DENTAL COLGATE MÁXIMA PROTEÇÃO ANTICÁRIES 90G</t>
+          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4.99</v>
+        <v>28.9</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
@@ -4050,47 +4090,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Creme Dental Máxima Proteção Anticáries Colgate 90g</t>
+          <t>Roupa Íntima Plenitud Unissex Classic c/ 8</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Colgate</t>
+          <t>Plenitud</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>90g</t>
+          <t>c/ 8</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>CREME DENTAL COLGATE MÁXIMA PROTEÇÃO ANTICÁRIES 90G</t>
+          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4.99</v>
+        <v>28.9</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4100,47 +4140,43 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Total 12 Colgate 90g</t>
+          <t>Absorvente Noturno Suave Abas 24 Intimus</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Colgate</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>90g</t>
-        </is>
-      </c>
+          <t>Intimus</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Colgate Total, sabores, 90 g</t>
+          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>10.99</v>
+        <v>31.9</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4150,47 +4186,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Óleo de Soja Paixão 900ml</t>
+          <t>Absorvente Noturno Suave com Abas Intimus c/ 24</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Paixão</t>
+          <t>Intimus</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>c/ 24</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Óleo Corporal Paixão, fragrâncias, 100 ml</t>
+          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>13.99</v>
+        <v>31.9</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4200,47 +4236,47 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Shampoo Dove 190ml</t>
+          <t>Absorvente Intimus Noturno Suave com Abas c/ 24</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Intimus</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>190ml</t>
+          <t>c/ 24</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Shampoo Dove 190 ml</t>
+          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>15.99</v>
+        <v>31.9</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4250,47 +4286,43 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Gel Fixador Bozzano 300g</t>
+          <t>Fralda Supreme Mega Huggies</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Bozzano</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
+          <t>Huggies</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Gel Fixador Bozzano 300g</t>
+          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>18.99</v>
+        <v>54.9</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4300,47 +4332,43 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Creme Facial Nivea 100g</t>
+          <t>Fralda Supreme Mega Huggies</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Nivea</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
+          <t>Huggies</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Creme Facial Nivea Potinho 100g</t>
+          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>22.99</v>
+        <v>54.9</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4350,143 +4378,143 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Condicionador Dove 190ml</t>
+          <t>Fralda Supreme Mega Huggies</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Dove</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>190ml</t>
-        </is>
-      </c>
+          <t>Huggies</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Condicionador Dove 190ml</t>
+          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>22.99</v>
+        <v>54.9</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Luva de Látex Descartável com Amido Volk Tamanho c/ 100</t>
+          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Volk</t>
+          <t>Duetto</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>c/ 100</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>LUVA VOLK LÁTEX TAM G C/AMIDO C/ 100UND</t>
+          <t>Papel Higiênico Duetto Folha Dupla 30 m com 12 unidades</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>23.9</v>
+        <v>16.99</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Tinta de Cabelo Koleston</t>
+          <t>Papel A4 Chamex 500 Folhas 75g</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Koleston</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>Chamex</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>75g</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Tinta Koleston, todas as cores</t>
+          <t>PAPEL A4 75G CHAMEX C/500 FOLHAS</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>24.99</v>
+        <v>27.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -4496,182 +4524,190 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Toalha de Papel Máxim Decor 200 Toalhas</t>
+          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Máxim</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr"/>
+          <t>Mili</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>c/ 24</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>TOALHA DE PAPEL MÁXIM DECOR 200 TOALHAS</t>
+          <t>PAPEL HIGIÊNICO MILI SENSITIVE CARE PCT C/ 24 ROLOS</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>7.49</v>
+        <v>39.99</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Toalha de Papel Maxim Decor 200 Toalhas Máxim</t>
+          <t>Achocolatado Líquido Pirakids 200ml</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Máxim</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
+          <t>Pirakids</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>TOALHA DE PAPEL MÁXIM DECOR 200 TOALHAS</t>
+          <t>Achocolatado Líquido Pirakids 200ml R$ 1,29</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>7.49</v>
+        <v>1.29</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
+          <t>Creme de Leite Piracanjuba 200g</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Mili</t>
+          <t>Piracanjuba</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>PAPEL HIGIÊNICO MILI FOLHA DUPLA 30M 12 ROLOS</t>
+          <t>CREME LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>18.9</v>
+        <v>2.99</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
+          <t>Leite Integral Piracanjuba 1L</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Mili</t>
+          <t>Piracanjuba</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>PAPEL HIGIÊNICO MILI FOLHA DUPLA 30M 12 ROLOS</t>
+          <t>Leite UHT Piracanjuba Integral/Semidesnatado/Desnatado 1 Litro R$ 6,99 UN</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>18.9</v>
+        <v>6.99</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/814124080_18378178621237813_8140421816201533348_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1Mzk5ODM0ODAxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OKVTVwPFdrcQ7kNvwFQoYiF&amp;_nc_oc=AdrtbWnEh6udxDhPxzFbu1TEJIOapw09aOO5r62VHZOUNt2Z9LjSOJLmOFIOENHeavP2TX1APHCiMO66xAy8BP-l&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQJbhnlOg0mUYw2ulv-G6j-I7217oYLjEvmxf56AT0qLCQ&amp;oe=6AB45481</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
@@ -4683,140 +4719,152 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Papel A4 Chamex 500 Folhas 75g</t>
+          <t>Leite Integral Piracanjuba 1L</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Chamex</t>
+          <t>Piracanjuba</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>75g</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>PAPEL A4 75G CHAMEX C/500 FOLHAS DE: R$ 46,99 POR: R$ 27,99</t>
+          <t>LEITE INTEGRAL PIRACANJUBA 1L</t>
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>27.99</v>
+        <v>6.99</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Banana da Terra Kg</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>Leite Condensado Piracanjuba 395g</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Piracanjuba</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>395g</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Banana da Terra Kg</t>
+          <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Abacaxi Pérola un</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr"/>
+          <t>Queijo Mussarela Frimesa kg</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Frimesa</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Abacaxi Grande Und.</t>
+          <t>QUEIJO MUSSARELA FATIADA FRIMESA 150G</t>
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4826,47 +4874,47 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Leite Integral Piracanjuba 1L</t>
+          <t>Margarina c/ Sal Qualy 500g</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Qualy</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Leite Piracanjuba Desnatado ou Semi 1 Litro</t>
+          <t>Margarina Qualy com Sal pote 500 g R$ 8,99 un</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>6.49</v>
+        <v>8.99</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -4876,47 +4924,47 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Leite Fermentado Real Garrafa 800g</t>
+          <t>Requeijão Cremoso Catupiry 200g</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Catupiry</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>LEITE FERMENTADO REAL GARRAFA 800G</t>
+          <t>REQUEIJÃO CREMOSO TRADICIONAL OU LIGHT CATUPIRY 200G</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4926,40 +4974,40 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Leite Fermentado Real 800g</t>
+          <t>Margarina c/ Sal Qualy 500g</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Qualy</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>LEITE FERMENTADO REAL GARRAFA 800G DE R$ 10,49 POR: R$ 6,99 UND</t>
+          <t>MARGARINA QUALY CREMOSA 500G</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -4976,47 +5024,47 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Queijo Mussarela Santa Clara kg</t>
+          <t>Leite em Pó Ninho Integral Nestlé 380g</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>380g</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA FATIADA SANTA CLARA 150G</t>
+          <t>LEITE EM PÓ NINHO NESTLÉ INTEGRAL 380G</t>
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>7.99</v>
+        <v>17.99</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814629649_1684107763719621_7837942697509336236_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4ODU5NjIzNDI5NDU2MDQ3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K3NkVzT_2RQQ7kNvwE4TCkp&amp;_nc_oc=AdqM4kh5AyzI9GfC6D9jP39iQeFdbSKuUhGdkGRtYyZDxLCW_AvETh5M6It3PSkob8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQK1W-GEV-9vtE2eHblbY0KhICkNXn0B79wDljYwrz-Ulw&amp;oe=6AB31B6C</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5026,47 +5074,47 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Queijo Mussarela Piracanjuba kg</t>
+          <t>Chantily Amélia 1L</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Amélia</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA PIRACANJUBA FATIADO 300G</t>
+          <t>CHANTILY AMÉLIA TRADICIONAL 1L</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5076,40 +5124,40 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Queijo Mussarela Piracanjuba kg</t>
+          <t>Manteiga c/ Sal Aviação 200g</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Aviação</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA PIRACANJUBA FATIADO 300G DE R$ 18,90 POR: R$ 14,90 UND</t>
+          <t>MANTEIGA AVIAÇÃO C/ SAL 500G</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>14.9</v>
+        <v>35.99</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -5126,40 +5174,36 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Leite em Pó Ninho Integral 380g</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Ninho</t>
-        </is>
-      </c>
+          <t>Queijo Mussarela kg</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>380g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>LEITE EM PÓ NINHO INTEGRAL 380G DE: R$ 25,99 POR: R$ 17,99</t>
+          <t>QUEIJO MUSSARELA FATIADA</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>17.99</v>
+        <v>44.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -5171,52 +5215,52 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Chantily Amélia 1L</t>
+          <t>Saponáceo Cremoso Ypê 300ml</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Amélia</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>CHANTILY AMÉLIA TRADICIONAL 1L</t>
+          <t>SAPONÁCEO CREMOSO YPÊ 300ML</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>19.9</v>
+        <v>6.99</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5226,47 +5270,47 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Limpador Perfumado Casa&amp;perfume 500ml</t>
+          <t>Água Sanitária Qboa 2L</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Casa&amp;Perfume</t>
+          <t>Qboa</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>LIMPADOR PERFUMADO CASA&amp;PERFUME 500ML</t>
+          <t>Água Sanitária Qboa 2 litros</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -5276,40 +5320,40 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Limpador Perfumado Casa Perfume Casa &amp; Perfume 500ml</t>
+          <t>Limpador Perfumado Casaflor 1.75L</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Casa &amp; Perfume</t>
+          <t>Casaflor</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1.75L</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>LIMPADOR PERFUMADO CASA&amp;PERFUME 500ML</t>
+          <t>LIMPADOR PERFUMADO CASAFLOR 1,75LT</t>
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>3.99</v>
+        <v>12.99</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -5326,47 +5370,47 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Limpador Multiuso Ypê 500ml</t>
+          <t>Inseticida Aerosol Fragrâncias Baygon 360ml</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Baygon</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>360ml</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Limpador Multiuso Ype 500ml fragrancias</t>
+          <t>Inseticida Baygon Fragrâncias 360 ml</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>4.99</v>
+        <v>17.99</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -5376,47 +5420,47 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Alvejante Girando Sol Perfumado com Cloro 2L</t>
+          <t>Água Sanitária Qboa 5L</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Girando Sol</t>
+          <t>Qboa</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>5L</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>ALVEJANTE GIRANDO SOL PERFUMADO C/ CLORO 2L</t>
+          <t>ÁGUA SANITÁRIA QBOA 5L</t>
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5426,239 +5470,247 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Vassoura Santa Maria Phenix com Cabo</t>
+          <t>Soda Cáustica 99% Gioca 1kg</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Phenix</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>Gioca</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>VASSOURA SANTA MARIA PHENIX C/ CABO</t>
+          <t>Soda Cáustica Gioca 99% 1 kg</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>11.9</v>
+        <v>21.99</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Vassoura com Cabo Santa Maria Phenix</t>
+          <t>Detergente Líquido Tixan Ypê 500ml</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr"/>
+          <t>Tixan Ypê</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>800g</t>
+        </is>
+      </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>VASSOURA SANTA MARIA PHENIX C/ CABO</t>
+          <t>Detergente em Pó Tixan Fragrâncias sachê 800 g</t>
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>11.9</v>
+        <v>12.99</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Pinho Sol 2L</t>
+          <t>Sabão em Barra Neutro Ypê 5x 160g</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Pinho Sol</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>750ml</t>
+          <t>160g</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Pinho Sol 1.750ml Fragrâncias</t>
+          <t>SABÃO BARRA YPÊ NEUTRO PCT 5X160G</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>18.99</v>
+        <v>14.99</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Luva Volk Látex Tam com Amido c/ 100</t>
+          <t>Amaciante Downy 2L</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Volk</t>
+          <t>Downy</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>c/ 100</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>LUVA VOLK LÁTEX TAM G C/ AMIDO C/ 100UND</t>
+          <t>AMACIANTE ROUPAS CONCENTRADO DOWNY ALFAZEMA OU VERÃO TROPICAL 1L</t>
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>23.9</v>
+        <v>22.99</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Lixeira Linha Ágata Mor 3L</t>
+          <t>Amaciante Ypê 2L</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>3L</t>
+          <t>5L</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>LIXEIRA MOR LINHA ÁGATA 3L</t>
+          <t>AMACIANTE ROUPAS YPÊ 5L</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>54.9</v>
+        <v>22.99</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -5668,40 +5720,40 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Alvejante Perfumado com Cloro Girando Sol 2L</t>
+          <t>Sabão Líquido Lavagem Perfeita Omo 1.8L</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Girando Sol</t>
+          <t>Omo</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>1.8L</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>ALVEJANTE GIRANDO SOL PERFUMADO C/ CLORO 2L</t>
+          <t>SABÃO LÍQUIDO OMO LAVAGEM PERFEITA 1,8L</t>
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>7.99</v>
+        <v>22.99</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -5718,47 +5770,47 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Ypê 2L</t>
+          <t>Detergente Líquido Tixan Ypê 500ml</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Tixan Ypê</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>2.2kg</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Tradicional Ype 2l Fragrâncias</t>
+          <t>Detergente em Pó Tixan Primavera 2,2 kg - Caixa 10% Promocional</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>9.99</v>
+        <v>26.99</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -5768,76 +5820,76 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Detergente Líquido Tixan Ypê 500ml</t>
+          <t>Sabão em Pó Omo 1.6kg</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Omo</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>2.2kg</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Detergente em Pó Tixan 800g Caixa</t>
+          <t>SABÃO PÓ OMO LAVAGEM PERFEITA 2,2KG</t>
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>12.99</v>
+        <v>29.99</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Detergente Líquido Ypê 500ml</t>
+          <t>Arroz Branco Tipo 1 São João 5kg</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>São João</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>DETERGENTE LÍQUIDO YPÊ NEUTRO OU CLEAR PACK C/6UNI DE 500ML DE: R$ 19,14 POR: R$ 13,99</t>
+          <t>Arroz São João Agulhinha 5 kg R$ 17,49</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>13.99</v>
+        <v>17.49</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5846,198 +5898,198 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Downy 2L</t>
+          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Downy</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Concentrado Downy 500ml Fragrâncias</t>
+          <t>ARROZ KOBLENZ PCT C/5KG</t>
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>14.49</v>
+        <v>24.99</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Kit Esponja Bettanin Esfrebom Abrasiva c/ 6</t>
+          <t>Açúcar Cristal Barralcool 2kg</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Bettanin</t>
+          <t>Barralcool</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>c/ 6</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>KIT ESPONJA BETTANIN ESFREBOM ABRASIVA C/ 6UND</t>
+          <t>Açúcar Barralcool 2 Kg R$ 5,19</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>17.9</v>
+        <v>5.19</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Kit Esponja Abrasiva Esfrebom Bettanin c/ 6</t>
+          <t>Açúcar Cristal Doce Dia 2kg</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Bettanin</t>
+          <t>Doce Dia</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>c/ 6</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>KIT ESPONJA BETTANIN ESFREBOM ABRASIVA C/ 6UND</t>
+          <t>AÇÚCAR CRISTAL DOCE DIA PCT C/2KG</t>
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>17.9</v>
+        <v>5.99</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Pó Brilhante 1.6kg</t>
+          <t>Biscoito Recheado Twister Renata 112g</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Brilhante</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>2.2kg</t>
+          <t>112g</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>SABÃO PÓ BRILHANTE LIMPEZA TOTAL CX C/2,2KG DE: R$ 28,69 POR: R$ 21,99</t>
+          <t>Biscoito Renata Twister Sabores 112g R$ 1,99</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>21.99</v>
+        <v>1.99</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6046,469 +6098,469 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Detergente Líquido Tixan Ypê 500ml</t>
+          <t>Biscoito Wafer Bauducco 140g</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>1.6kg</t>
+          <t>140g</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Detergente Po Tixan 1.6kg sch. Primavera</t>
+          <t>BISCOITO WAFER BAUDUCCO 140G</t>
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>24.99</v>
+        <v>3.59</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
+          <t>Biscoito Cream Cracker Rancheiro 300g</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Rancheiro</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2.4kg</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ TIXAN YPÊ PCT 2,4KG</t>
+          <t>Biscoito Rancheiro Cream Cracker 300g R$ 3,99</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>26.9</v>
+        <v>3.99</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
+          <t>Chocolate Wafer Hershey's 120g</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Hershey'S</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>2.4kg</t>
+          <t>120g</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ TIXAN YPÊ PCT 2,4KG</t>
+          <t>CHOCOLATE WAFER HERSHEY 120G</t>
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>26.9</v>
+        <v>3.99</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Detergente Líquido Ypê 500ml</t>
+          <t>Biscoito Maisena Mabel 300g</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>5L</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Detergente Líquido Ypê 5L fragrâncias</t>
+          <t>BISCOITO LAMINADO MABEL LEITE OU MAISENA 300G</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>26.99</v>
+        <v>5.99</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Detergente Líquido Tixan Ypê 500ml</t>
+          <t>Biscoito Rosquinha Coco Mabel 600g</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>2.2kg</t>
+          <t>600g</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Detergente Pó Tixan 2.2kg caixa Primavera 10% Promo.</t>
+          <t>BISCOITO ROSQUINHA MABEL COCO 600G</t>
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>27.99</v>
+        <v>7.99</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.frec31-1.fna.fbcdn.net/v/t51.82787-15/814535091_18377967157237813_92955118397073883_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4ODE4NDUzNTM5MTc5NDM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NmUSjMmyTNAQ7kNvwFqBOf1&amp;_nc_oc=AdqkX6aB07OEKxXZOaBdsmRQ3b7GOfWqgVY1lO6dwNebD07xnMs5MPhdzRymwuxJApo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.frec31-1.fna&amp;_nc_gid=kdtFWiMKFc_E9B6ZL6Bbyg&amp;_nc_ss=7a22e&amp;oh=00_AQL92I5e01VYpBjofOdA304qAhF3hnPNgbf8oFHP1DXyIQ&amp;oe=6AB317AB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdY4LRiu_TG/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Ypê 2L</t>
+          <t>Biscoito Biscuit Choco Bauducco 80g</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>7L</t>
+          <t>80g</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>AMACIANTE YPÊ PRO ROUPAS E TECIDOS 7L</t>
+          <t>BISCOITO BAUDUCCO BISCUIT CHOCO 80G</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>29.9</v>
+        <v>7.99</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809910658_1377509091135715_4732246856632306275_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NzgwMzM2ODUxNjgzOTQ5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ybaao4wNm5IQ7kNvwH8odYH&amp;_nc_oc=AdpRcaWZt1ub4ccPKgxzd2JYAYrONq7Z-cbjLh-9nC8j-mkUNBozX7nRd8zGBB8iU549htGHHY6GNdFXlnpZv-9d&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQLmJSbPs4G4O1eJE5k6YpJQnUsPdGBBzTLOfNZInlI7og&amp;oe=6AB314DB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Ypê 2L</t>
+          <t>Doce de Leite Comajul 400g</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Comajul</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>7L</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE YPÊ PRO ROUPAS E TECIDOS 7L</t>
+          <t>DOCE LEITE TRADICIONAL COMAJUL 400G</t>
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>29.9</v>
+        <v>9.99</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/806022333_1377509087802382_6887347780323628127_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NzgwMzM2ODE0Nzc2NjQ3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=oSDmMf9ZcYkQ7kNvwEkkw3u&amp;_nc_oc=Adqq5kfjfxnv0t8XrXdvUDpbwl_RjDvykLsGjiaQs-W4dvwc7Yrn0lFup3trGoIlt4aIN3nI8PN4kC2mR5EJGpiy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQJXbpIstRYsWO_tC1n8HWNG2AgkshARdSAYZgpNVbMkng&amp;oe=6AB31630</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
+          <t>Batata Inglesa Pringles Kg</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>109g</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TIPO1 PCT 5KG</t>
+          <t>Batata Chips Pringles Sabores 109g R$ 10,99</t>
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>21.9</v>
+        <v>10.99</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
+          <t>Bombons Favoritos Lacta 250 6g</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>Lacta</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>6g</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TIPO1 PCT 5KG DE R$ 23,90 POR: R$ 21,90 UND</t>
+          <t>BOMBONS SORTIDOS LACTA FAVORITOS 250,6G DE: R$ 20,89 POR: R$ 14,99</t>
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>21.9</v>
+        <v>14.99</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6518,47 +6570,47 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Recheado Glub Sagra 80g</t>
+          <t>Cereal Matinal Snow Flakes Nestlé 800g</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Sagra</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>80g</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>BISCOITO SAGRA GLUB RECHEADO 80G</t>
+          <t>CEREAL MATINAL NESTLÉ SNOW FLAKES 800G</t>
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>1.79</v>
+        <v>15.99</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -6568,112 +6620,112 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Recheado Glub Sagra 80g</t>
+          <t>Creme de Avelã Nutella 700g</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Sagra</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>80g</t>
+          <t>700g</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO SAGRA GLUB RECHEADO 80G DE R$ 2,29 POR: R$ 1,79 UND</t>
+          <t>CREME AVELÃ NUTELLA 700G</t>
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.79</v>
+        <v>49.99</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Recheado Chocolate Passatempo 130g</t>
+          <t>Café Tradicional Rancheiro 500g</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Passatempo</t>
+          <t>Rancheiro</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>130g</t>
+          <t>250g</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Rech. Passatempo Chocolate 130g</t>
+          <t>Café Rancheiro Tradicional/ Extra Forte 250g R$ 10,99</t>
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>2.49</v>
+        <v>10.99</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Rosquinha Coco Marilan 500g</t>
+          <t>Café Tradicional Brasileiro 500g</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Marilan</t>
+          <t>Brasileiro</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -6683,311 +6735,311 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO MARILAN ROSQUINHA COCO 500G</t>
+          <t>CAFÉ BRASILEIRO TRADICIONAL E EXTRA FORTE PCT 500G</t>
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>4.99</v>
+        <v>26.99</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Rosquinha Coco Marilan 500g</t>
+          <t>Feijão Carioca Rei 1kg</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Marilan</t>
+          <t>Rei</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>BISCOITO MARILAN ROSQUINHA COCO 500G DE R$ 5,99 POR: R$ 4,99 UND</t>
+          <t>Feijão Carioca Rei pacote 1 kg R$ 6,99</t>
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Rosquinha Coco Mabel 600g</t>
+          <t>Macarrão Espaguete Galo 500g</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Mabel</t>
+          <t>Galo</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Rosquinhas Mabel Coco - 600g</t>
+          <t>MACARRÃO SÊMOLA GALO ESPAGUETE 8 500G</t>
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Cereal Matinal Sucrilhos Original Kellogg's 240g</t>
+          <t>Óleo de Soja Liza 900ml</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Kellogg'S</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>240g</t>
+          <t>900ml</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Cereal Sucrilhos Original 240g</t>
+          <t>ÓLEO SOJA LIZA OU CONCÓRDIA 900ML</t>
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>8.49</v>
+        <v>6.99</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Club Social 288g</t>
+          <t>Azeite de Oliva Extra Virgem Borges 500ml</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>Borges</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>288g</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO CLUB SOCIAL 288G</t>
+          <t>AZEITE OLIVA EXTRA VIRGEM BORGES 500ML</t>
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>9.98</v>
+        <v>27.99</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Club Social 288g</t>
+          <t>Lenha Eucalipto Saco São Luiz 12kg</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>São Luiz</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>288g</t>
+          <t>12kg</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>BISCOITO CLUB SOCIAL 288G DE R$ 14,79 POR: R$ 9,98 UND</t>
+          <t>Lenha Eucalipto São Luiz Saco c/ 12kg R$ 31,99</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>9.98</v>
+        <v>31.99</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Creme de Avelã Nutella 350g</t>
+          <t>Mandioca Congelada Goiana 1kg</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Goiana</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>350g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>CREME AVELÃ NUTELLA 375/350G DE: R$ 35,99 POR: R$ 25,99</t>
+          <t>Mandioca Congelada Goiana R$ 5,99 kg</t>
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -6996,1112 +7048,562 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Café Tradicional Pilão 500g</t>
+          <t>Pão de Queijo Cuiabá 1kg</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Pilão</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>CAFÉ PILÃO À VÁCUO 500G</t>
+          <t>Pão de Queijo Cuiabá pacote 1 kg R$ 9,99 un</t>
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>23.9</v>
+        <v>9.99</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Café Tradicional Pilão 500g</t>
+          <t>Alho Bello Kg</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Pilão</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>CAFÉ PILÃO À VÁCUO 500G DE R$ 28,90 POR: R$ 23,90 UND</t>
+          <t>Pão de Alho Tradicional Bello 300g R$ 9,99</t>
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>23.9</v>
+        <v>9.99</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Fermento em Pó Dona Benta 100g</t>
+          <t>Pão de Queijo Congelado Mc 1kg</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Dona Benta</t>
+          <t>Mc</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>FERMENTO EM PÓ DONA BENTA TRADICIONAL 100G</t>
+          <t>PÃO QUEIJO CONGELADO MC PCT C/ 1KG</t>
         </is>
       </c>
       <c r="G136" s="3" t="n">
-        <v>2.99</v>
+        <v>17.99</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Fermento em Pó Dona Benta 100g</t>
+          <t>Pizza Sadia 460g</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Dona Benta</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>460g</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>FERMENTO EM PÓ DONA BENTA TRADICIONAL 100G DE R$ 3,79 POR: R$ 2,99 UND</t>
+          <t>PIZZA SADIA SABORES 460G DE: R$ 25,49 POR: R$ 21,99</t>
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2.99</v>
+        <v>21.99</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Tipo 1 Sol 1kg</t>
+          <t>Pão Bisnaguinha Visconti 240g</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Sol</t>
+          <t>Visconti</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>240g</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO SOL 1KG</t>
+          <t>PÃO BISNAGUINHA TRADICIONAL VISCONTI 240G</t>
         </is>
       </c>
       <c r="G138" s="3" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Tipo 1 Sol 1kg</t>
+          <t>Pão Bauducco 390g</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Sol</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>390g</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO SOL 1KG DE R$ 5,29 POR: R$ 3,99 UND</t>
+          <t>PÃO FATIADO TRADICIONAL BAUDUCCO 390G</t>
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Coco Ralado Adoçado Mais Coco 100g</t>
+          <t>Alho Dabrasa Kg</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Mais Coco</t>
+          <t>Dabrasa</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>450g</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>COCO RALADO MAIS COCO ADOÇADO 100G</t>
+          <t>Pão De Alho Dabrasa Sabores 450gr R$ 11,99 un</t>
         </is>
       </c>
       <c r="G140" s="3" t="n">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Coco Ralado Adoçado Mais Coco 100g</t>
+          <t>Ração para Gato Mimiau 1kg</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Mais Coco</t>
+          <t>Mimiau</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>COCO RALADO MAIS COCO ADOÇADO 100G DE R$ 7,49 POR: R$ 4,99 UND</t>
+          <t>Ração para Gato Mimiau - Carne/Natural/Peixe 1 kg</t>
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>4.99</v>
+        <v>12.29</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Azeitona Verde Rivoli 120g</t>
+          <t>Ração para Cão Carne com Cereais Maikão 7kg</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Rivoli</t>
+          <t>Maikão</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>120g</t>
+          <t>7kg</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE RIVOLI EM CONSERVA FATIADA 120G</t>
+          <t>Ração para Cão Maikão - Carne com Cereais 7 kg</t>
         </is>
       </c>
       <c r="G142" s="3" t="n">
-        <v>3.79</v>
+        <v>34.9</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
+          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Azeitona Verde Rivoli 120g</t>
+          <t>Ração para Cães Adultos Thor 7kg</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Rivoli</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>120g</t>
+          <t>7kg</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE RIVOLI EM CONSERVA FATIADA 120G DE R$ 4,79 POR: R$ 3,79 UND</t>
+          <t>RAÇÃO PARA CÃES ADULTOS THOR SACO 7KG</t>
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>3.79</v>
+        <v>59.9</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Macarrão Espaguete Galo 500g</t>
+          <t>Ração para Cães Pedigree 10.1kg</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Galo</t>
+          <t>Pedigree</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10.1kg</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Macarrão Sêmola Galo Espaguete N8 ou Parafuso 500g</t>
+          <t>RAÇÃO P/CÃES PEDIGREE SAÇO C/ 10,1KG</t>
         </is>
       </c>
       <c r="G144" s="3" t="n">
-        <v>4.59</v>
+        <v>139.99</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
+          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Massas</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Macarrão Espaguete D'Italia 500g</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>D'Italia</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>MACARRÃO D'ITÁLIA CASEIRO 1KG</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Massas</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Macarrão Espaguete D'Italia 500g</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>D'Italia</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>MACARRÃO D'ITALIA CASEIRO 1KG DE R$ 16,49 POR: R$ 12,90 UND</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>Tomate Longa Vida Olé Kg</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>Olé</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>MOLHO DE TOMATE OLÉ TRADICIONAL SACHÊ 300G</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I147" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/805696776_1377509094469048_1577834635713617598_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NzgwMzM2ODE3MjkyNDA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8knkhVXRbbIQ7kNvwE9K3Vw&amp;_nc_oc=AdqHFP7NfdXMsO9wo4Lsp_RA_2NlF-GuOLQHX7GlR93wrg9eKapqWZIp3MCm8b00cIEKhCcj-NTJjohghLTzYJT0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQI4QpecMlGbu1FkWcglwfuPFVBNRDCWntHg6KzFV3CV7g&amp;oe=6AB311A9</t>
-        </is>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Tomate Longa Vida Olé Kg</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Olé</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>MOLHO DE TOMATE OLÉ TRADICIONAL SACHÊ 300G DE R$ 2,29 POR: R$ 1,79 UND</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Maionese Hellmann's Sachê 200g</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>Hellmann'S</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>200g</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>Maionese Hellmann's Sachê 200g</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/813912361_18195006877391764_5313260300159225180_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjA4OTU5MzUyNTA1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUdD_QSepKYQ7kNvwG8--TU&amp;_nc_oc=AdoWcMM1KhOIsE3e0Kg1gts16slzbPwSkUAX5c01g4OYzgtzrYJSA87Eh2Fb3IZyzNPdCvRrSCzmfvkWnT4eZ2U7&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQKYanKlXZReSBsxuyBLJuy-QMb3zWR1l-QbnFuzAVlWRA&amp;oe=6AB30E0E</t>
-        </is>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Molhos e Condimentos</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Tomate Longa Vida Elefante Kg</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Elefante</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>Extrato de Tomate Elefante 300g</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Óleos e Azeites</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Azeite de Oliva Extra Virgem Gomes da Costa 500ml</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>Gomes Da Costa</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>AZEITE OLIVA EXTRA VIRGEM GOMES DA COSTA 500ML DE: R$ 43,99 POR: R$ 26,99</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I151" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/814535011_1684107770386287_6016690985642303944_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODU5NjIzMTc4NjM1MjQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H-p26_nE8CEQ7kNvwFACLC3&amp;_nc_oc=AdrP8tuGjcORiJ7TLgKCkXATqfrro2QzOYZ9EOriTe6I47B9Q6o3YyJ4a-DnV73bcy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQLSYHCbo2Zz-twbFvg7BEhlYTTJvBWcglIezDUzE0-TAg&amp;oe=6AB32C1F</t>
-        </is>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Machadão Atacadista</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Empanado de Frango Sadia 100g</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>EMPANADO DE FRANGO SADIA 100G DE R$ 1,99 POR: R$ 1,49 UND</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/809978819_1377509084469049_4609400797491219297_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NzgwMzM2Nzg1NDEyNzc1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lzX2tW83FkgQ7kNvwH2aY0g&amp;_nc_oc=AdrZ-64vQCwq7z95RPNdquwyxsQqtZVD56VW_lYFuFOtgqcS-lsHw0-tvcoTzZwd3SBR8LcFK8kEovkJmfrE6h1j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=0bNZPWNaUvZwKmiYhcEV0A&amp;_nc_ss=7a22e&amp;oh=00_AQK5y0akQY-hAVN7Fi8o9xQEefVH04IGzJS_U_rGy-UcEg&amp;oe=6AB31DFE</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdXhg0bDWSd/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Pão de Forma Visconti 400g</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>Visconti</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>Pão de Forma Visconti Tradicional 400g</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-mia3-3.cdninstagram.com/v/t51.82787-15/814493738_18195006904391764_6581779085052338220_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODMzNjEyMjQ0MzI3NjQ3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vAyiYRdL6l8Q7kNvwGmTRYy&amp;_nc_oc=AdoQIR2io0gs-T7vUHYON5aXKHzUwROaX6LEcKZduC8Dfx5u4Hrq91WgoXAWRdE3DsNAgUPPStxTHtGwgdcOZsnX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.cdninstagram.com&amp;_nc_gid=onGMskwl8lW2SQ3Z5Q0T8w&amp;_nc_ss=7a22e&amp;oh=00_AQIX3BX0QPgVJk_pYNzdb2Qeuc1cXy8tW-9GbfvhrOCAgQ&amp;oe=6AB2FECF</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdZapvTl_4u/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Pão Bisnaguinha Visconti 240g</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Visconti</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>240g</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>PÃO BISNAGUINHA TRADICIONAL VISCONTI 240G</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Pão Bauducco 390g</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>Bauducco</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>390g</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>PÃO FATIADO TRADICIONAL BAUDUCCO 390G</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/797694597_1684107760386288_8909864380049925233_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODU5NjIzMTg0NTA5NzIyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AaPkzZUi_nYQ7kNvwFWn7C2&amp;_nc_oc=AdqHVeLHmG96CN9jv2PT3cf7LLOdH_0ic5DOGdqV3eqs2cyv6MsnJ-02TXKFpYDMQJs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=o_RbDUfZwnHx2GWatJnxwg&amp;_nc_ss=7a22e&amp;oh=00_AQIdtfVstQK89EWXhFXFh-bw5oTXUWMRIYgvCOVMlDSTYQ&amp;oe=6AB31195</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdaVygxFhJs/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -8116,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8160,16 +7662,16 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>17.2275</v>
+        <v>15.70255813953488</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3.29</v>
+        <v>1.29</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>27.99</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -8179,73 +7681,35 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>17.6659375</v>
+        <v>29.43</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>1.49</v>
+        <v>16.99</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>89.90000000000001</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>26.90666666666667</v>
+        <v>25.42231707317073</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10.99</v>
+        <v>1.39</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>47.99</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Super Compras Supermercado</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>14.45142857142857</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>51.99</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>21.01676470588235</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>39.99</v>
+        <v>159.9</v>
       </c>
     </row>
   </sheetData>
@@ -8259,10 +7723,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -8297,189 +7761,189 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>44.75090909090909</v>
+        <v>92.218</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3.99</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>23.67857142857143</v>
+        <v>30.99</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>2.49</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8.84</v>
+        <v>24.87857142857143</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8.69</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>13.49</v>
+        <v>10.24</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13.58090909090909</v>
+        <v>18.99</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>33.04882352941177</v>
+        <v>13.3525</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>12.99</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>18.65666666666667</v>
+        <v>35.04</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>11.49</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>15.5525</v>
+        <v>34.65666666666667</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>22.99</v>
+        <v>15.92333333333333</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>15.28181818181818</v>
+        <v>15.59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3.29</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>16.154</v>
+        <v>26.38142857142857</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7.49</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>6.49</v>
+        <v>28.32333333333333</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -8489,13 +7953,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>12.01875</v>
+        <v>13.77538461538462</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6.49</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -8505,13 +7969,13 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>15.83888888888889</v>
+        <v>14.99</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8521,13 +7985,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20.72066666666667</v>
+        <v>21.99</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>7.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -8540,58 +8004,58 @@
         <v>2</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>21.9</v>
+        <v>21.24</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>21.9</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>7.748</v>
+        <v>5.59</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1.79</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>23.9</v>
+        <v>11.45666666666667</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>23.9</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>3.99</v>
+        <v>18.99</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -8601,13 +8065,13 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>3.79</v>
+        <v>6.99</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.79</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -8617,45 +8081,45 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>10.13</v>
+        <v>3.99</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>4.215</v>
+        <v>17.49</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1.79</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>26.99</v>
+        <v>31.99</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>26.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -8665,13 +8129,13 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1.49</v>
+        <v>13.19</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8684,10 +8148,26 @@
         <v>3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>6.323333333333333</v>
+        <v>8.323333333333332</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>5.99</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>12.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="77" customWidth="1" min="6" max="6"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="618" customWidth="1" min="9" max="9"/>
+    <col width="620" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -544,7 +544,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -554,43 +554,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Copo Americano 190ml</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>190ml</t>
-        </is>
-      </c>
+          <t>Varal de Chão Slim Branco Mor</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mor</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Copo Americano 190 ml</t>
+          <t>VARAL CHÃO MOR SLIM BRANCO UNI R$: 119,90</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.49</v>
+        <v>119.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -600,40 +600,36 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Assadeira Vidro Reta com Tampa Marinex 3.5L</t>
+          <t>Liquidificador Preto L900 127v Mondial</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Marinex</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>3.5L</t>
-        </is>
-      </c>
+          <t>Mondial</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Assadeira Marinex Reta com Tampa 3,5 litros R$ 49,90</t>
+          <t>LIQUIDIFICADOR MONDIAL PRETO L900 127V UNI R$: 129,90</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>49.9</v>
+        <v>129.9</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -650,22 +646,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Varal de Chão Mor Slim Branco</t>
+          <t>Ventilador Mondial Power 40cm 127v</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Mondial</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>VARAL CHÃO MOR SLIM BRANCO UNI</t>
+          <t>VENTILADOR MONDIAL SUPER POWER 40CM 127V</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>119.9</v>
+        <v>159.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -674,12 +670,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -691,27 +687,31 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Liquidificador Mondial Preto L900 127v</t>
+          <t>Gin Rock's 1L</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mondial</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>Rock'S</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>LIQUIDIFICADOR MONDIAL PRETO L900 127V UNI</t>
+          <t>BEBIDA GIN ROCK'S 1L</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>129.9</v>
+        <v>26.99</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -720,12 +720,12 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -737,27 +737,31 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ventilador Mondial Power 40cm 127v</t>
+          <t>Vinho Reservado Concha Toro Concha Y Toro 750ml</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mondial</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>Concha Y Toro</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>750ml</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>VENTILADOR MONDIAL SUPER POWER 40CM 127V UNI DE: R$ 199,99 POR: R$ 159,90</t>
+          <t>VINHO CHILENO RESERVADO CONCHA Y TORO 750ML</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>159.9</v>
+        <v>34.99</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -766,7 +770,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -783,31 +787,31 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Gin Rock's 1L</t>
+          <t>Cerveja Extra Corona 330ml</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Rock'S</t>
+          <t>Corona</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>330ml</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA GIN ROCK'S 1L DE: R$ 35,99 POR: R$ 26,99</t>
+          <t>CERVEJA CORONA EXTRA 330ML</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>26.99</v>
+        <v>6.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -816,7 +820,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -833,31 +837,31 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Cervejas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Vinho Reservado Concha Toro Concha Y Toro 750ml</t>
+          <t>Cerveja 12x Itaipava 269ml</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Concha Y Toro</t>
+          <t>Itaipava</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750ml</t>
+          <t>269ml</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>VINHO CHILENO RESERVADO CONCHA Y TORO 750ML DE: R$ 48,99 POR: R$ 34,99</t>
+          <t>CERVEJA ITAIPAVA CX C/12X269ML</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>34.99</v>
+        <v>26.99</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -866,7 +870,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -878,7 +882,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -888,140 +892,140 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Lata Itaipava 269ml</t>
+          <t>Cerveja Michelob Ultra 6x 330ml</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Itaipava</t>
+          <t>Michelob Ultra</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>330ml</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Itaipava lata 269 mL</t>
+          <t>CERVEJA MICHELOB ULTRA CX C/6X330ML</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.99</v>
+        <v>36.99</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/809209189_18378178603237813_4341481546895005542_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1MjMxMjQ1MTk5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ltusphbvbjUQ7kNvwHWptYf&amp;_nc_oc=Adqobdk4EhA_pDwSoN4MAOGE9ieVB-p6BIIBGirchg6MVpJXK-gOa58hkqUL8dlPb6uRGk9vLRyil8fHoEDmUYWZ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKU5WNF10-qia92LY4Dzmrh4C4zaNj1uYD0_5444pzabQ&amp;oe=6AB44D3A</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Long Neck Stella Artois 330ml</t>
+          <t>Refrigerante Guaraná Original Antarctica 2L</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Stella Artois</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Stella Artois Long Neck Tradicional 330ml R$ 6,99</t>
+          <t>REFRIGERANTE GUARANÁ ANTARCTICA ORIGINAL 2L</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Extra Long Neck Corona 330ml</t>
+          <t>Refrigerante Pet Coca-Cola 2.5L</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Corona</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>2.5L</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA CORONA EXTRA 330ML DE: R$ 7,59 POR: R$ 6,99</t>
+          <t>REFRIGERANTE COCA COLA PET 2,5L</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.99</v>
+        <v>10.9</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
         </is>
       </c>
     </row>
@@ -1033,31 +1037,31 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cerveja 12x Itaipava 269ml</t>
+          <t>Uva Niagara Garibaldi 500g</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Itaipava</t>
+          <t>Garibaldi</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>1.5L</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CERVEJA ITAIPAVA CX C/12X269ML DE: R$ 35,88 POR: R$ 26,99</t>
+          <t>SUCO UVA TINTO INTEGRAL GARIBALDI 1,5LTS</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>26.99</v>
+        <v>15.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1066,12 +1070,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -1083,31 +1087,31 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Michelob Ultra 6x 330ml</t>
+          <t>Água Mineral Puríssima Fardo 12x 500ml</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Michelob Ultra</t>
+          <t>Puríssima</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA MICHELOB ULTRA CX C/6X330ML DE: R$ 47,94 POR: R$ 36,99</t>
+          <t>ÁGUA MINERAL PURÍSSIMA COM E SEM GÁS FD C/ 12X497/ 500ML</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>36.99</v>
+        <v>23.99</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1116,112 +1120,112 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Pilsen Lata Pack 15 Skol 269ml</t>
+          <t>Empanado de Frango Perdigão 100g</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Skol</t>
+          <t>Perdigão</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Skol 269ml Multipack c/15 Latas R$ 43,35</t>
+          <t>EMPANADO FRANGO TRADICIONAL PERDIGÃO 100G</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>43.35</v>
+        <v>1.89</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Original Lata Pack 15 269ml</t>
+          <t>Frango Oriental Pedaços Seara 275g</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>275g</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Original Multipack C/ 15 Latas de 269ml R$ 50,85</t>
+          <t>FRANGO ORIENTAL SEARA PEDAÇOS 275G</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>50.85</v>
+        <v>6.99</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -1233,31 +1237,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Antarctica 2L</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Antarctica</t>
-        </is>
-      </c>
+          <t>Coxinha da Asa de Frango kg</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANÁ ANTARCTICA ORIGINAL 2L DE: R$ 9,49 POR: R$ 8,99</t>
+          <t>COXINHAS DAS ASAS FRANGO S/TEMPERO R$: 11,99 KG</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1266,62 +1266,62 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Refrigerante Pet Coca-Cola 2.5L</t>
+          <t>Moela de Frango Seara 1kg</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2.5L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Refrigerante Coca-Cola Tradicional/Zero PET 2,5 litros R$ 11,49</t>
+          <t>MOELA FRANGO SEARA BDJ 1KG</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>11.49</v>
+        <v>15.99</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -1333,31 +1333,31 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Uva Niagara Garibaldi 500g</t>
+          <t>Frango Inteiro Nho Bento kg</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Garibaldi</t>
+          <t>Nho Bento</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>SUCO UVA TINTO INTEGRAL GARIBALDI 1,5LTS</t>
+          <t>FRANGO INTEIRO CAIPIRA NHO BENTO DE: R$ 23,99 POR: R$ 17,99 KG</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>15.99</v>
+        <v>17.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -1383,31 +1383,31 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Achocolatado em Pó Toddy 750g</t>
+          <t>Filé de Peito de Frango Lar kg</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Toddy</t>
+          <t>Lar</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO PÓ TODDY 750G</t>
+          <t>FILÉ PEITO FRANGO LAR BDJ C/ 1KG</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>16.99</v>
+        <v>18.99</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -1433,31 +1433,31 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Água Mineral Puríssima Fardo 12x 500ml</t>
+          <t>Meio da Asa de Frango Seara 1kg</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Puríssima</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA MINERAL PURÍSSIMA COM E SEM GÁS FD C/ 12X497/ 500ML</t>
+          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG R$: 24,99</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>23.99</v>
+        <v>24.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1488,40 +1488,36 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Empanado de Frango Perdigão 100g</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Perdigão</t>
-        </is>
-      </c>
+          <t>Meio da Asa de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>EMPANADO FRANGO TRADICIONAL PERDIGÃO 100G</t>
+          <t>MEIO DA ASA R$ 29,99 Kg</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.89</v>
+        <v>29.99</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1529,31 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Frango Oriental Pedaços Seara 275g</t>
+          <t>Hambúrguer Bovino Aves Sadia 56g</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275g</t>
+          <t>56g</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>FRANGO ORIENTAL SEARA PEDAÇOS 275G</t>
+          <t>HAMBÚRGUER BOVINO E AVES SADIA 56G</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.99</v>
+        <v>1.39</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1562,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1578,50 +1574,46 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Sobrecoxa de Frango Canção kg</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Canção</t>
-        </is>
-      </c>
+          <t>Costela Bovina kg</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Coxas e Sobrecoxa Canção R$ 7,99 kg</t>
+          <t>COSTELA BOVINA R$ 19,99 Kg</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1625,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Coxinha das Asas de Frango Sem Tempero Kg</t>
+          <t>Costela Bovina Minga kg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1649,11 +1641,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>COXINHAS DAS ASAS FRANGO S/TEMPERO</t>
+          <t>COSTELA MINGA kg R$ 25,99</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11.99</v>
+        <v>25.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1662,86 +1654,78 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Moela de Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Ponta de Peito Sem Osso Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SEARA BDJ 1KG DE: R$ 19,99 POR: R$ 15,99</t>
+          <t>PONTA DE PEITO S/ OSSO R$ 34,99 Kg</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>15.99</v>
+        <v>34.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Frango Inteiro Nho Bento kg</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Nho Bento</t>
-        </is>
-      </c>
+          <t>Coxão Duro Bovino kg</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1749,75 +1733,71 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>FRANGO INTEIRO CAIPIRA NHO BENTO</t>
+          <t>COXÃO DURO R$ 36,99 Kg</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>17.99</v>
+        <v>36.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Lar kg</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Lar</t>
-        </is>
-      </c>
+          <t>Contrafilé Bovino kg</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>FILÉ PEITO FRANGO LAR BDJ C/1KG DE: R$ 24,99 POR: R$ 18,99</t>
+          <t>CONTRA FILÉ C/ OSSO R$ 37,99 Kg</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>18.99</v>
+        <v>37.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
@@ -1829,31 +1809,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Meio das Asas de Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Contrafilé Bovino kg</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG</t>
+          <t>CAPA CONTRA FILÉ BOV. kg R$ 37,99</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>24.99</v>
+        <v>37.99</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1862,19 +1838,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1884,47 +1860,43 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Hambúrguer Bovino Aves Sadia 56g</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Capa de Filé Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>56g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>HAMBÚRGUER BOVINO E AVES SADIA 56G</t>
+          <t>CAPA C. FILÉ R$ 39,99 Kg</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.39</v>
+        <v>39.99</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1934,40 +1906,36 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina Sulbeef kg</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Sulbeef</t>
-        </is>
-      </c>
+          <t>Cupim Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina Sulbeef R$ 22,99 kg</t>
+          <t>CUPIM BOV. kg R$ 45,99</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>22.99</v>
+        <v>45.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1952,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Costela Bovina Minga kg</t>
+          <t>Picanha Bovina kg</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -1995,11 +1963,11 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>COSTELA MINGA kg R$ 25,99</t>
+          <t>PICANHA FATIADA BOV. kg R$ 45,99</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>25.99</v>
+        <v>45.99</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2008,7 +1976,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
+          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2030,7 +1998,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
+          <t>Maminha Bovina kg</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -2041,11 +2009,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CAPA CONTRA FILÉ BOV. kg R$ 37,99</t>
+          <t>Maminha Bov. kg R$ 49,99</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>37.99</v>
+        <v>49.99</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2054,7 +2022,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2076,7 +2044,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Cupim Bovina Kg</t>
+          <t>Alcatra Bovina kg</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
@@ -2087,11 +2055,11 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>CUPIM BOV. kg R$ 45,99</t>
+          <t>Coração Alcatra kg R$ 49,99</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45.99</v>
+        <v>49.99</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2100,7 +2068,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2117,27 +2085,31 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Picanha Bovina kg</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Camarão Inteiro Costa Sul 400g</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Costa Sul</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>PICANHA FATIADA BOV. kg R$ 45,99</t>
+          <t>CAMARÃO COSTA SUL INTEIRO PCT C/ 400G</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45.99</v>
+        <v>24.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2146,12 +2118,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2163,27 +2135,31 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Maminha Bovina kg</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
+          <t>Filé de Peixe Tilápia Bello 800g</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Maminha Bov. kg R$ 49,99</t>
+          <t>FILÉ PEIXE TILÁPIA BELLO 800G</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>49.99</v>
+        <v>35.99</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2192,12 +2168,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2185,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Alcatra Bovina kg</t>
+          <t>Peixe Inteiro Pintado</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Coração Alcátra kg R$ 49,99</t>
+          <t>PEIXE INTEIRO PINTADO</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>49.99</v>
+        <v>42.99</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2238,12 +2210,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2255,31 +2227,31 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Camarão Inteiro Costa Sul 400g</t>
+          <t>Mortadela Defumada Seara 180g</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Costa Sul</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>180g</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTA SUL INTEIRO PCT C/ 400G</t>
+          <t>MORTADELA DEFUMADA SEARA 180G</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>24.99</v>
+        <v>7.99</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2288,7 +2260,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2305,31 +2277,31 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Filé de Tilápia Bello 800g</t>
+          <t>Linguiça Toscana Seara kg</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>370g</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>FILÉ PEIXE TILÁPIA BELLO 800G DE: R$ 48,99 POR: R$ 35,99</t>
+          <t>LINGUIÇA PAIO SEARA 370G DE: R$ 15,99 POR: R$ 8,99</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>35.99</v>
+        <v>8.99</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2338,7 +2310,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2355,23 +2327,31 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Peixe Inteiro Pintado</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
+          <t>Presunto Cozido Seara kg</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>180g</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>PEIXE INTEIRO PINTADO</t>
+          <t>PRESUNTO FATIADO SEARA 180G</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>42.99</v>
+        <v>9.99</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2380,7 +2360,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2402,26 +2382,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Seara 180g</t>
+          <t>Linguiça Toscana Sadia kg</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>180g</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>MORTADELA DEFUMADA SEARA 180G</t>
+          <t>LINGUIÇA TIPO PORTUGUESA SADIA 400G</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2430,7 +2410,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2452,26 +2432,26 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Seara kg</t>
+          <t>Salsicha Hot Dog Perdigão kg</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Perdigão</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>370g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA PAIO SEARA 370G</t>
+          <t>SALSICHA HOT DOG PERDIGÃO R$: 10,99 KG</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>8.99</v>
+        <v>10.99</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -2480,19 +2460,19 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2502,40 +2482,36 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Salsicha Hot Dog Perdigão kg</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Perdigão</t>
-        </is>
-      </c>
+          <t>Linguiça Toscana kg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Salsicha Seara/ Perdigão R$ 9,99 kg</t>
+          <t>LINGUIÇA FINA APIMENTADA R$ 16,99 Kg</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
@@ -2552,26 +2528,26 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Presunto Cozido Seara kg</t>
+          <t>Linguiça Toscana Excelência kg</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Excelência</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>180g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>PRESUNTO FATIADO SEARA 180G</t>
+          <t>LINGUIÇA TOSCANA EXCELÊNCIA kg R$ 16,99</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2580,12 +2556,12 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -2597,31 +2573,27 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Sadia kg</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Mandioca Congelada Kg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA TIPO PORTUGUESA SADIA 400G</t>
+          <t>Mandioca Congelada kg R$ 5,99</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2630,62 +2602,62 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Pernil Suíno Max Free kg</t>
+          <t>Tekitos Seara 300g</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Max Free</t>
+          <t>Seara</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Pernil Suíno Frigorífico Max Free R$ 10,99 kg</t>
+          <t>TEKITOS TRADICIONAL SEARA 300G DE: R$ 11,99 POR: R$ 8,99</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2697,31 +2669,31 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Salsicha Hot Dog Perdigão kg</t>
+          <t>Lasanha Sadia 600g</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>600g</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>SALSICHA HOT DOG PERDIGÃO</t>
+          <t>LASANHA SADIA SABORES 600G</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.99</v>
+        <v>16.99</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2730,62 +2702,62 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Perdigão kg</t>
+          <t>Açaí Origem 1.5L</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Perdigão</t>
+          <t>Origem</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>1.5L</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Suína Perdigão R$ 14,99 kg</t>
+          <t>AÇAÍ ORIGEM TODA HORA 1,5L DE: R$ 30,49 POR: R$ 22,99</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>14.99</v>
+        <v>22.99</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -2797,31 +2769,31 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Excelência kg</t>
+          <t>Papel Sulfite A4 Chamex 500 Folhas 75g</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Excelência</t>
+          <t>Chamex</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>75g</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA TOSCANA EXCELÊNCIA kg R$ 16,99</t>
+          <t>PAPEL A4 75G CHAMEX C/500 FOLHAS R$: 27,99</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16.99</v>
+        <v>27.99</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2830,312 +2802,296 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwHNcsa_&amp;_nc_oc=AdoJuhCPaNxSEvj4rTt8zljcSrwFW6Kd_Mr1Op4dASe80--dnXQUdY_QEgC-9vVZ6Xk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQI7D_Wk_Qq5vEyERfsxqTmgMEgFIqtxuyRBD7zi71ArJw&amp;oe=6AB464CC</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Costela Suína Max Free 1kg</t>
+          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Max Free</t>
+          <t>Mili</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>c/ 24</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Costela Suína Max Free R$ 18,99 kg</t>
+          <t>PAPEL HIGIÊNICO MILI SENSITIVE CARE PCT C/24 ROLOS</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>18.99</v>
+        <v>39.99</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Fricó kg</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Fricó</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Fina Apimentada Fricó R$ 19,99 kg</t>
+          <t>LARANJA PERA RIO Kg R$ 2,49</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>19.99</v>
+        <v>2.49</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Calabresa Excelência kg</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Excelência</t>
-        </is>
-      </c>
+          <t>Batata Inglesa Kg</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Calabresa Excelência R$ 19,99 kg</t>
+          <t>BATATA INGLESA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>19.99</v>
+        <v>4.99</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Presunto Cozido Excelência kg</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Excelência</t>
-        </is>
-      </c>
+          <t>Cenoura Kg</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Presunto Cozido Excelência R$ 22,99 kg</t>
+          <t>CENOURA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>22.99</v>
+        <v>4.99</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Uva Niagara 500g</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Mortadela Seara Defumada R$ 25,99 kg</t>
+          <t>UVA VITORIA BDJ Bdj R$ 7,99</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>25.99</v>
+        <v>7.99</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Bacon em Manta Seara kg</t>
+          <t>Creme de Leite Piracanjuba 200g</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Piracanjuba</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Bacon Manta Seara R$ 29,99 kg</t>
+          <t>CREME LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>29.99</v>
+        <v>2.99</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -3147,27 +3103,31 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Mandioca Congelada Kg</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
+          <t>Leite Integral Piracanjuba 1L</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Piracanjuba</t>
+        </is>
+      </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Mandioca Congelada kg R$ 5,99</t>
+          <t>LEITE INTEGRAL PIRACANJUBA 1L</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -3176,12 +3136,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -3193,31 +3153,31 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Tekitos Seara 300g</t>
+          <t>Leite Condensado Piracanjuba 395g</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Piracanjuba</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>395g</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>TEKITOS TRADICIONAL SEARA 300G</t>
+          <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3226,12 +3186,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -3243,31 +3203,31 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Lasanha Sabores Sadia 600g</t>
+          <t>Queijo Mussarela Frimesa kg</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Frimesa</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>150g</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>LASANHA SADIA SABORES 600G</t>
+          <t>QUEIJO MUSSARELA FATIADA FRIMESA 150G</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -3276,7 +3236,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3288,50 +3248,50 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sorvete Gebon 1.5L</t>
+          <t>Requeijão Cremoso Catupiry 200g</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Gebon</t>
+          <t>Catupiry</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Sorvete Gebon Sabores 1,5 litros R$ 22,99 un</t>
+          <t>REQUEIJÃO CREMOSO TRADICIONAL OU LIGHT CATUPIRY 200G DE: R$ 12,99 POR: R$ 8,99</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>22.99</v>
+        <v>8.99</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -3343,31 +3303,31 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Açaí Origem Toda Hora 1.5L</t>
+          <t>Margarina c/ Sal Qualy 500g</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Origem Toda Hora</t>
+          <t>Qualy</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>AÇAÍ ORIGEM TODA HORA 1,5L</t>
+          <t>MARGARINA QUALY CREMOSA 500G R$: 8,99</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>22.99</v>
+        <v>8.99</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3376,198 +3336,194 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Sabonete em Barra Fragrâncias Nivea 85g</t>
+          <t>Leite em Pó Ninho Integral Nestlé 380g</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Nivea</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>85g</t>
+          <t>380g</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Sabonete em Barra Nivea Fragrâncias 85g</t>
+          <t>LEITE EM PÓ NINHO NESTLÉ INTEGRAL 380G</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2.29</v>
+        <v>17.99</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Dentes Brancos Sorriso 120g</t>
+          <t>Chantilly Amélia 1L</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Sorriso</t>
+          <t>Amélia</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>120g</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Sorriso Dentes Brancos 120 g</t>
+          <t>CHANTILY AMÉLIA TRADICIONAL 1L DE: R$ 24,99 POR: R$ 19,90</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>4.99</v>
+        <v>19.9</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Kit Shampoo Condicionador Seda 300ml</t>
+          <t>Manteiga c/ Sal Aviação 200g</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Seda</t>
+          <t>Aviação</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Kit Shampoo Seda 300 ml + Condicionador 190 ml</t>
+          <t>MANTEIGA AVIAÇÃO C/ SAL 500G</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>16.99</v>
+        <v>35.99</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Shampoo Huggies 360ml</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Huggies</t>
-        </is>
-      </c>
+          <t>Queijo Mussarela kg</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>SHAMPOO HUGGIES 360ML</t>
+          <t>QUEIJO MUSSARELA FATIADA R$: 44,99 KG</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>16.99</v>
+        <v>44.99</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -3576,48 +3532,48 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Shampoo Huggies 360ml</t>
+          <t>Saponáceo Cremoso Ypê 300ml</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Huggies</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>SHAMPOO HUGGIES 360ML</t>
+          <t>SAPONÁCEO CREMOSO YPÊ 300ML R$: 6,99</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>16.99</v>
+        <v>6.99</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3626,48 +3582,48 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Shampoo Kids Huggies 360ml</t>
+          <t>Limpador Perfumado Casaflor 1.75L</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Huggies</t>
+          <t>Casaflor</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>1.75L</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>SHAMPOO HUGGIES 360ML</t>
+          <t>LIMPADOR PERFUMADO CASAFLOR 1,75LT</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>16.99</v>
+        <v>12.99</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3676,48 +3632,48 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Condicionador Huggies 360ml</t>
+          <t>Água Sanitária Qboa 5L</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Huggies</t>
+          <t>Qboa</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>5L</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>CONDICIONADOR HUGGIES 360ML</t>
+          <t>ÁGUA SANITÁRIA QBOA 5L R$: 19,99</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>17.9</v>
+        <v>19.99</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3726,12 +3682,12 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -3743,81 +3699,81 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Condicionador Huggies 360ml</t>
+          <t>Esponja de Aço Bombril 45g</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Huggies</t>
+          <t>Bombril</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>45g</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>CONDICIONADOR HUGGIES 360ML</t>
+          <t>ESPONJA DE AÇO BOMBRIL 45G</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>17.9</v>
+        <v>1.99</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Condicionador Kids Huggies 360ml</t>
+          <t>Sabão em Barra Neutro Ypê 5x 160g</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Huggies</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>360ml</t>
+          <t>160g</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>CONDICIONADOR HUGGIES 360ML</t>
+          <t>SABÃO BARRA YPÊ NEUTRO PCT 5X160G</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>17.9</v>
+        <v>14.99</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3826,44 +3782,48 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Noturno 30 Intimus</t>
+          <t>Amaciante Downy 2L</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Intimus</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr"/>
+          <t>Downy</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
+          <t>AMACIANTE ROUPAS CONCENTRADO DOWNY ALFAZEMA OU VERÃO TROPICAL 1L</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>25.99</v>
+        <v>22.99</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3872,48 +3832,48 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Absorvente Noturno Intimus c/ 30</t>
+          <t>Amaciante Ypê 2L</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Intimus</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>c/ 30</t>
+          <t>5L</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
+          <t>AMACIANTE ROUPAS YPÊ 5L</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>25.99</v>
+        <v>22.99</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3922,48 +3882,48 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Intimus Noturno Leve Mais Pague Menos c/ 30</t>
+          <t>Sabão Líquido Lavagem Perfeita Omo 1.8L</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Intimus</t>
+          <t>Omo</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>c/ 30</t>
+          <t>1.8L</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO LV+ PG- C/ 30UND</t>
+          <t>SABÃO LÍQUIDO OMO LAVAGEM PERFEITA 1,8L R$: 22,99</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>25.99</v>
+        <v>22.99</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3972,44 +3932,48 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Roupa Íntima Unissex Classic Plenitud</t>
+          <t>Sabão em Pó Omo 1.6kg</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plenitud</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
+          <t>Omo</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2.2kg</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
+          <t>SABÃO PÓ OMO LAVAGEM PERFEITA 2,2KG</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>28.9</v>
+        <v>29.99</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4018,48 +3982,48 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Roupa Íntima Unissex Classic Plenitud c/ 8</t>
+          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Plenitud</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>c/ 8</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
+          <t>ARROZ KOBLENZ PCT C/5KG</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>28.9</v>
+        <v>24.99</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -4068,48 +4032,48 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Roupa Íntima Plenitud Unissex Classic c/ 8</t>
+          <t>Açúcar Cristal Doce Dia 2kg</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plenitud</t>
+          <t>Doce Dia</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>c/ 8</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>ROUPA ÍNTIMA PLENITUD UNISSEX CLASSIC C/ 8UND</t>
+          <t>AÇÚCAR CRISTAL DOCE DIA PCT C/2KG</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>28.9</v>
+        <v>5.99</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4118,44 +4082,48 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Noturno Suave Abas 24 Intimus</t>
+          <t>Biscoito Wafer Bauducco 140g</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Intimus</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
+          <t>Bauducco</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>140g</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
+          <t>BISCOITO WAFER BAUDUCCO 140G</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>31.9</v>
+        <v>3.59</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -4164,48 +4132,48 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Absorvente Noturno Suave com Abas Intimus c/ 24</t>
+          <t>Chocolate Wafer Hershey's 120g</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Intimus</t>
+          <t>Hershey'S</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>c/ 24</t>
+          <t>120g</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
+          <t>CHOCOLATE WAFER HERSHEY 120G DE: R$ 4,99 POR: R$ 3,99</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>31.9</v>
+        <v>3.99</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4214,12 +4182,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -4231,77 +4199,81 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Intimus Noturno Suave com Abas c/ 24</t>
+          <t>Biscoito Salgado Salt Plus Sol 360g</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Intimus</t>
+          <t>Sol</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>c/ 24</t>
+          <t>360g</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>ABSORVENTE INTIMUS NOTURNO SUAVE C/ABAS C/24UND</t>
+          <t>BISCOITO SOL SALT PLUS 360G</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>31.9</v>
+        <v>4.89</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Fralda Supreme Mega Huggies</t>
+          <t>Biscoito Maisena Mabel 300g</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Huggies</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+          <t>Mabel</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
+          <t>BISCOITO LAMINADO MABEL LEITE OU MAISENA 300G</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>54.9</v>
+        <v>5.99</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4310,44 +4282,48 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818043908_1379693007583990_6458156877646800763_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTY2NTQzMzI1ODk5NDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sttanOQemN0Q7kNvwH76yOy&amp;_nc_oc=AdoZlUKihuWGTQbQkGDnVBjknG5w-cXPisDpJ2peyaMQ4o2HpTkhDTU3YyXdSi_b32k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQLVlN5hgAYhs3H5jyG9FFgapWIslM-lw6gdVVnkcIjeyg&amp;oe=6AB44CC8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Fralda Supreme Mega Huggies</t>
+          <t>Biscoito Rosquinha Coco Mabel 600g</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Huggies</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr"/>
+          <t>Mabel</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
+          <t>BISCOITO ROSQUINHA MABEL COCO 600G</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>54.9</v>
+        <v>7.99</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -4356,44 +4332,48 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/818297702_1379693017583989_7214049581671091617_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTY2NTQzMzQ0MzUwOTA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=a0lImFSxcCsQ7kNvwFb-OtU&amp;_nc_oc=AdqlC_Y2WcLUp-sPx8os33-IceZsvrirGG85M9mlVjFVz71_4-cLljEzr_4EgM0Zris&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIr527kw8r2-el4QIciDnnNRYB9YX_AQ7h1CY8JhdjOgg&amp;oe=6AB44933</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Fralda Supreme Mega Huggies</t>
+          <t>Biscoito Biscuit Choco Bauducco 80g</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Huggies</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>Bauducco</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>80g</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES SUPREME MEGA PCT</t>
+          <t>BISCOITO BAUDUCCO BISCUIT CHOCO 80G</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>54.9</v>
+        <v>7.99</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4402,62 +4382,62 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ssn1-1.cdninstagram.com/v/t39.30808-6/795485740_1379693000917324_1898594911285622035_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTY2NTQzMjY1NTAzMjcwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6pebU7ggefEQ7kNvwFDJlsc&amp;_nc_oc=Adrmm52C3zOYAxIcjJOyT0sTtYJ0NnFpvd6wCK2Vs3CBak9q_9Zkh8lF-48OjzKmbGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=HYBa3bKfVJdxWy_zpzqQEg&amp;_nc_ss=7a22e&amp;oh=00_AQIaJNlWECrFZ8v4yh5iUitPwX1Rf3Ky4L4bGRJak_8GvA&amp;oe=6AB45324</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdeI5aAjke9/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
+          <t>Doce de Leite Comajul 400g</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Duetto</t>
+          <t>Comajul</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Duetto Folha Dupla 30 m com 12 unidades</t>
+          <t>DOCE LEITE TRADICIONAL COMAJUL 400G DE: R$ 11,59 POR: R$ 9,99</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>16.99</v>
+        <v>9.99</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -4469,31 +4449,31 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Papel A4 Chamex 500 Folhas 75g</t>
+          <t>Bombons Sortidos Lacta Favoritos 250 6g</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Chamex</t>
+          <t>Lacta</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>75g</t>
+          <t>6g</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>PAPEL A4 75G CHAMEX C/500 FOLHAS</t>
+          <t>BOMBONS SORTIDOS LACTA FAVORITOS 250,6G</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>27.99</v>
+        <v>14.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4502,12 +4482,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -4519,31 +4499,31 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
+          <t>Cereal Matinal Snow Flakes Nestlé 800g</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Mili</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>c/ 24</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>PAPEL HIGIÊNICO MILI SENSITIVE CARE PCT C/ 24 ROLOS</t>
+          <t>CEREAL MATINAL NESTLÉ SNOW FLAKES 800G</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>39.99</v>
+        <v>15.99</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -4552,7 +4532,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -4564,50 +4544,50 @@
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Achocolatado Líquido Pirakids 200ml</t>
+          <t>Achocolatado em Pó Toddy 750g</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Pirakids</t>
+          <t>Toddy</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>750g</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Achocolatado Líquido Pirakids 200ml R$ 1,29</t>
+          <t>ACHOCOLATADO PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1.29</v>
+        <v>16.99</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -4619,31 +4599,31 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba 200g</t>
+          <t>Creme de Avelã Nutella 700g</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>700g</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200G</t>
+          <t>CREME AVELÃ NUTELLA 700G</t>
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2.99</v>
+        <v>49.99</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4652,7 +4632,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -4664,50 +4644,50 @@
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Leite Integral Piracanjuba 1L</t>
+          <t>Café Tradicional Brasileiro 500g</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Brasileiro</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Leite UHT Piracanjuba Integral/Semidesnatado/Desnatado 1 Litro R$ 6,99 UN</t>
+          <t>CAFÉ BRASILEIRO TRADICIONAL E EXTRA FORTE PCT 500G</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>6.99</v>
+        <v>26.99</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/814124080_18378178621237813_8140421816201533348_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1Mzk5ODM0ODAxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OKVTVwPFdrcQ7kNvwFQoYiF&amp;_nc_oc=AdrtbWnEh6udxDhPxzFbu1TEJIOapw09aOO5r62VHZOUNt2Z9LjSOJLmOFIOENHeavP2TX1APHCiMO66xAy8BP-l&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQJbhnlOg0mUYw2ulv-G6j-I7217oYLjEvmxf56AT0qLCQ&amp;oe=6AB45481</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
         </is>
       </c>
     </row>
@@ -4719,31 +4699,31 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Leite Integral Piracanjuba 1L</t>
+          <t>Macarrão Espaguete Galo 500g</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Galo</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>LEITE INTEGRAL PIRACANJUBA 1L</t>
+          <t>MACARRÃO SÊMOLA GALO ESPAGUETE 8 500G</t>
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4752,7 +4732,7 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -4769,27 +4749,27 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Leite Condensado Piracanjuba 395g</t>
+          <t>Óleo de Soja Liza 900ml</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Piracanjuba</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>395g</t>
+          <t>900ml</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
+          <t>ÓLEO SOJA LIZA OU CONCÓRDIA 900ML</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
@@ -4802,7 +4782,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4819,31 +4799,31 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Queijo Mussarela Frimesa kg</t>
+          <t>Azeite de Oliva Extra Virgem Borges 500ml</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Frimesa</t>
+          <t>Borges</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA FATIADA FRIMESA 150G</t>
+          <t>AZEITE OLIVA EXTRA VIRGEM BORGES 500ML DE: R$ 49,29 POR: R$ 27,99</t>
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>7.99</v>
+        <v>27.99</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4852,7 +4832,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -4864,100 +4844,100 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Margarina c/ Sal Qualy 500g</t>
+          <t>Lenha Eucalipto Saco São Luiz 12kg</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Qualy</t>
+          <t>São Luiz</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>12kg</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Margarina Qualy com Sal pote 500 g R$ 8,99 un</t>
+          <t>Lenha Eucalipto São Luiz Saco C/12kg R$ 31,99</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>8.99</v>
+        <v>31.99</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Requeijão Cremoso Catupiry 200g</t>
+          <t>Alho Bello Kg</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Catupiry</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>REQUEIJÃO CREMOSO TRADICIONAL OU LIGHT CATUPIRY 200G</t>
+          <t>PÃO DE ALHO BELLO 300G R$ 9,99</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
@@ -4969,31 +4949,31 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Margarina c/ Sal Qualy 500g</t>
+          <t>Alho Bello Kg</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Qualy</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>MARGARINA QUALY CREMOSA 500G</t>
+          <t>Pão de Alho Tradicional Bello 300g R$ 9,99</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5002,12 +4982,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
         </is>
       </c>
     </row>
@@ -5019,27 +4999,27 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Leite em Pó Ninho Integral Nestlé 380g</t>
+          <t>Pão de Queijo Congelado Mc 1kg</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Mc</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>380g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>LEITE EM PÓ NINHO NESTLÉ INTEGRAL 380G</t>
+          <t>PÃO QUEIJO CONGELADO MC PCT C/ 1KG</t>
         </is>
       </c>
       <c r="G93" s="5" t="n">
@@ -5052,12 +5032,12 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -5069,31 +5049,31 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Chantily Amélia 1L</t>
+          <t>Pizza Sabores Sadia 460g</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Amélia</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>460g</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>CHANTILY AMÉLIA TRADICIONAL 1L</t>
+          <t>PIZZA SADIA SABORES 460G</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>19.9</v>
+        <v>21.99</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5102,7 +5082,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5119,31 +5099,31 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Manteiga c/ Sal Aviação 200g</t>
+          <t>Pão Bisnaguinha Visconti 240g</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Aviação</t>
+          <t>Visconti</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>240g</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>MANTEIGA AVIAÇÃO C/ SAL 500G</t>
+          <t>PÃO BISNAGUINHA TRADICIONAL VISCONTI 240G DE: R$ 7,29 POR: R$ 5,99</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>35.99</v>
+        <v>5.99</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -5152,7 +5132,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5169,27 +5149,31 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Queijo Mussarela kg</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>Pão Bauducco 390g</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Bauducco</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>390g</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA FATIADA</t>
+          <t>PÃO FATIADO TRADICIONAL BAUDUCCO 390G DE: R$ 9,79 POR: R$ 6,99</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44.99</v>
+        <v>6.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5198,12 +5182,12 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
       </c>
     </row>
@@ -5215,31 +5199,31 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Saponáceo Cremoso Ypê 300ml</t>
+          <t>Ração para Cães Adultos Thor 7kg</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>7kg</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>SAPONÁCEO CREMOSO YPÊ 300ML</t>
+          <t>RAÇÃO PARA CÃES ADULTOS THOR SACO 7KG R$: 59,90</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>6.99</v>
+        <v>59.9</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -5248,7 +5232,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5260,2348 +5244,48 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Bianchi</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 2L</t>
+          <t>Ração para Cães Saco Pedigree 10.1kg</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Qboa</t>
+          <t>Pedigree</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>10.1kg</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 2 litros</t>
+          <t>RAÇÃO P/ CÃES PEDIGREE SACO C/ 10,1KG DE: R$ 179,99 POR: R$ 139,99</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>9.99</v>
+        <v>139.99</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Limpador Perfumado Casaflor 1.75L</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Casaflor</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>1.75L</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>LIMPADOR PERFUMADO CASAFLOR 1,75LT</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Inseticida Aerosol Fragrâncias Baygon 360ml</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Baygon</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>360ml</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Inseticida Baygon Fragrâncias 360 ml</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Água Sanitária Qboa 5L</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Qboa</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>5L</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>ÁGUA SANITÁRIA QBOA 5L</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Cuidados com a Casa</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Soda Cáustica 99% Gioca 1kg</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Gioca</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Soda Cáustica Gioca 99% 1 kg</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Detergente Líquido Tixan Ypê 500ml</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Tixan Ypê</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>800g</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Detergente em Pó Tixan Fragrâncias sachê 800 g</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Sabão em Barra Neutro Ypê 5x 160g</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Ypê</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>160g</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>SABÃO BARRA YPÊ NEUTRO PCT 5X160G</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Amaciante Downy 2L</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Downy</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>AMACIANTE ROUPAS CONCENTRADO DOWNY ALFAZEMA OU VERÃO TROPICAL 1L</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Amaciante Ypê 2L</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Ypê</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>5L</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>AMACIANTE ROUPAS YPÊ 5L</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Sabão Líquido Lavagem Perfeita Omo 1.8L</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>1.8L</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>SABÃO LÍQUIDO OMO LAVAGEM PERFEITA 1,8L</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Detergente Líquido Tixan Ypê 500ml</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Tixan Ypê</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>2.2kg</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Detergente em Pó Tixan Primavera 2,2 kg - Caixa 10% Promocional</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Limpeza / Lavanderia e Louça</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>2.2kg</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>SABÃO PÓ OMO LAVAGEM PERFEITA 2,2KG</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Arroz</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Arroz Branco Tipo 1 São João 5kg</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>São João</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Arroz São João Agulhinha 5 kg R$ 17,49</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Arroz</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Koblenz</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>ARROZ KOBLENZ PCT C/5KG</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Açúcar</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Barralcool 2kg</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Barralcool</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>2kg</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Açúcar Barralcool 2 Kg R$ 5,19</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Açúcar</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Doce Dia 2kg</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Doce Dia</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>2kg</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>AÇÚCAR CRISTAL DOCE DIA PCT C/2KG</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Recheado Twister Renata 112g</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Renata</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>112g</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Renata Twister Sabores 112g R$ 1,99</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Biscoito Wafer Bauducco 140g</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Bauducco</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>140g</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>BISCOITO WAFER BAUDUCCO 140G</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Cream Cracker Rancheiro 300g</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Rancheiro</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Rancheiro Cream Cracker 300g R$ 3,99</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Chocolate Wafer Hershey's 120g</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>Hershey'S</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>120g</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>CHOCOLATE WAFER HERSHEY 120G</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Maisena Mabel 300g</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Mabel</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>BISCOITO LAMINADO MABEL LEITE OU MAISENA 300G</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Biscoito Rosquinha Coco Mabel 600g</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Mabel</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>600g</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>BISCOITO ROSQUINHA MABEL COCO 600G</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Biscoito Biscuit Choco Bauducco 80g</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Bauducco</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>80g</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>BISCOITO BAUDUCCO BISCUIT CHOCO 80G</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Doce de Leite Comajul 400g</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Comajul</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>DOCE LEITE TRADICIONAL COMAJUL 400G</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Batata Inglesa Pringles Kg</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>109g</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Batata Chips Pringles Sabores 109g R$ 10,99</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Bombons Favoritos Lacta 250 6g</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>Lacta</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>6g</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>BOMBONS SORTIDOS LACTA FAVORITOS 250,6G DE: R$ 20,89 POR: R$ 14,99</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
-        </is>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Cereal Matinal Snow Flakes Nestlé 800g</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>800g</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>CEREAL MATINAL NESTLÉ SNOW FLAKES 800G</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwEh-Vmt&amp;_nc_oc=AdrjeO2Kl2gdrJ2EL96aqrsajw9mQwvq3bXgwuwlfMPyugtSoPn3i91gQyc-YRCrC_7EzM6uaXVvnKQV6vhAfFgl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIHBLxM7lBXJjTEeDeQKKTTllCblx2mYTjTE4cY0ftNSA&amp;oe=6AB45DB8</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Biscoitos e Doces</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Creme de Avelã Nutella 700g</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>Nutella</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>700g</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>CREME AVELÃ NUTELLA 700G</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Café</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Café Tradicional Rancheiro 500g</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Rancheiro</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>250g</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Café Rancheiro Tradicional/ Extra Forte 250g R$ 10,99</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Café</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Café Tradicional Brasileiro 500g</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>Brasileiro</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>CAFÉ BRASILEIRO TRADICIONAL E EXTRA FORTE PCT 500G</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Grãos e Conservas</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Feijão Carioca Rei 1kg</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Rei</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Feijão Carioca Rei pacote 1 kg R$ 6,99</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/806298851_18378178645237813_7256411155206921068_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4OTExNTA1NTM5OTQwMDI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vbqHn0ZquyYQ7kNvwH-CE-F&amp;_nc_oc=AdrGftwsyJEi8FwyYYz1wsqMkhMMox309ljI1FVBlwEyY4dtYjCcWGrj76pUFWhCTLu3Ffr8pcFphpouCbqyGLv-&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKxR9Da9tpqvpP5D1HLd1WoUpfM6YBH2Iqz44rfqc5RlA&amp;oe=6AB45CBD</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Massas</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Macarrão Espaguete Galo 500g</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>Galo</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>MACARRÃO SÊMOLA GALO ESPAGUETE 8 500G</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Mercearia / Óleos e Azeites</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Óleo de Soja Liza 900ml</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Liza</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>900ml</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>ÓLEO SOJA LIZA OU CONCÓRDIA 900ML</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwHQh5w-&amp;_nc_oc=AdrOEoIEsVIxT6Rwsp5vCN4EA7E7-FsQn7Q69BWolbpRMsBHxQTRCXS8xD9qGAZnV2qqQdwzL5UA4r0_NIT32Wni&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQLT__FK8nMrodxtynCuwG_MNzJX2_-7j_cjjjLlmldl-g&amp;oe=6AB472AA</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Mercearia / Óleos e Azeites</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Azeite de Oliva Extra Virgem Borges 500ml</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>Borges</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>AZEITE OLIVA EXTRA VIRGEM BORGES 500ML</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Lenha Eucalipto Saco São Luiz 12kg</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>São Luiz</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>12kg</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Lenha Eucalipto São Luiz Saco c/ 12kg R$ 31,99</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Mandioca Congelada Goiana 1kg</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>Goiana</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>Mandioca Congelada Goiana R$ 5,99 kg</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
-        </is>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Pão de Queijo Cuiabá 1kg</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Pão de Queijo Cuiabá pacote 1 kg R$ 9,99 un</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Alho Bello Kg</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Pão de Alho Tradicional Bello 300g R$ 9,99</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-qro3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwHFnR0x&amp;_nc_oc=AdrsVjW4QAYbus2SphH6_PjlRzyMEb4P6gM2vVnxairmFYNJWiIysdtt-NrVsfbZBok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-qro3-1.cdninstagram.com&amp;_nc_gid=fTGIoWJEPF_Y1hjx1tPeew&amp;_nc_ss=7a22e&amp;oh=00_AQLDGSnAnSjE2cT4crofsWHP8IFk_fY2Nigzv_EiNGQejg&amp;oe=6AB460F0</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Pão de Queijo Congelado Mc 1kg</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Mc</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>PÃO QUEIJO CONGELADO MC PCT C/ 1KG</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kgER09lmxY0Q7kNvwFkQa-J&amp;_nc_oc=AdoZV-9kL4Dr_nW1y3xlYXeWjCJqfIxJpYZ-OYKRoKVIK2xsR5_5eC4QLKDpkNuXLj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQL53Fb5SBpi6ILfBInuxPIdJxnRv1ywdXAiFNE7R3Sj3A&amp;oe=6AB46EF8</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Pizza Sadia 460g</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>460g</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>PIZZA SADIA SABORES 460G DE: R$ 25,49 POR: R$ 21,99</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I137" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwGKDvTW&amp;_nc_oc=AdrssPE33bPsq7jEBBD_qmf8dOVcz4wLAICiPstibTCwrugw6YwwOeJ0XT2_QExacxo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXcBNTYYFVeknErHK7TWsN8GYTXNo75UNCT9F1f83OTQ&amp;oe=6AB45915</t>
-        </is>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Pão Bisnaguinha Visconti 240g</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Visconti</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>240g</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>PÃO BISNAGUINHA TRADICIONAL VISCONTI 240G</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Pão Bauducco 390g</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>Bauducco</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>390g</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>PÃO FATIADO TRADICIONAL BAUDUCCO 390G</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Alho Dabrasa Kg</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Dabrasa</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>450g</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Pão De Alho Dabrasa Sabores 450gr R$ 11,99 un</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-1.fna.fbcdn.net/v/t51.82787-15/815468390_18378178630237813_4685728080070321924_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4OTExNTA1NDYwMjM1NTIwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Eq33owxbVYwQ7kNvwEDbua2&amp;_nc_oc=Ado1iEsudZ_WWmK0OmaO8VKMCn7lV0wjsq5IIcL_d_1hUUcNp8deSwRTD4y7VwmGjwQmQGxC6eBXlUOYWpAAv6Fm&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-1.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKsO39zqTOU0HhyBTl1blbGAVqPmsuXO7POrf0O4lRnDQ&amp;oe=6AB460A4</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Ração para Gato Mimiau 1kg</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>Mimiau</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>Ração para Gato Mimiau - Carne/Natural/Peixe 1 kg</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Ração para Cão Carne com Cereais Maikão 7kg</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Maikão</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>7kg</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Ração para Cão Maikão - Carne com Cereais 7 kg</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fmxp13-2.fna.fbcdn.net/v/t51.82787-15/813825164_18378178612237813_8446380212609256970_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTExNTA1NTUwMDAwNzUzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iqPAl8Bw_egQ7kNvwEdHtys&amp;_nc_oc=AdqXKDQygQuuhS4erXofHrQC_TimkcRWMM4L5SAyFZCLBtQnslRJRE4lYfvjaDMgRZZb9ka8R4L2V5F28q9gXH71&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmxp13-2.fna&amp;_nc_gid=iOM4XZR1OJe4KMgr-vNZQg&amp;_nc_ss=7a22e&amp;oh=00_AQKDTqI9pGUYMOtxpQ89DYdhKRxgnnqRorwUR9aqfhDh5Q&amp;oe=6AB454A4</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DdcLxh1D6uP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Ração para Cães Adultos Thor 7kg</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Thor</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>7kg</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>RAÇÃO PARA CÃES ADULTOS THOR SACO 7KG</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGg1mV1&amp;_nc_oc=AdpXpvkToZu9nxE3e5eyp1ur-5wWNgtyGVEOinTejNSdd131XfE31GcPLPXiy49UnerfdQXazb3Y-vTfNSjkdKJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=Gi4PWOwN2xmxBwp3mVq3oQ&amp;_nc_ss=7a22e&amp;oh=00_AQIbF6nt-P-2jzdJ4LAPGPZ9H_F-jE2gfO8OB4PBinyS_g&amp;oe=6AB47ECE</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Bianchi</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Ração para Cães Pedigree 10.1kg</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Pedigree</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>10.1kg</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>RAÇÃO P/CÃES PEDIGREE SAÇO C/ 10,1KG</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fvcp2-1.fna.fbcdn.net/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FCOWv3TnFiMQ7kNvwEIJFq6&amp;_nc_oc=AdpRr7Ix7uLvbIBgv_-bOWB5kqkN1kwSGXsUWjYM88aWbxklMHsoiGf7BW2FHahhJSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvcp2-1.fna&amp;_nc_gid=xX5q4NVmTCqjzdBULrcd6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLhOAZx5lggPApzjK7P41IUc7miKjqF7ZZauZMhbNzD8Q&amp;oe=6AB4509A</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
         </is>
@@ -7621,7 +5305,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -7658,39 +5342,39 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>15.70255813953488</v>
+        <v>5.926666666666667</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1.29</v>
+        <v>1.99</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>50.85</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>29.43</v>
+        <v>20.615</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>16.99</v>
+        <v>2.49</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>54.9</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -7723,7 +5407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7761,13 +5445,13 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>92.218</v>
+        <v>136.5666666666667</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1.49</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -7793,13 +5477,13 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>24.87857142857143</v>
+        <v>23.65666666666667</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -7812,7 +5496,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>10.24</v>
+        <v>9.945</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>8.99</v>
@@ -7825,10 +5509,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18.99</v>
+        <v>19.99</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>15.99</v>
@@ -7844,7 +5528,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>13.3525</v>
+        <v>16.1025</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1.89</v>
@@ -7857,10 +5541,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>35.04</v>
+        <v>35.60666666666667</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>1.39</v>
@@ -7889,10 +5573,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>15.92333333333333</v>
+        <v>11.70428571428571</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>7.99</v>
@@ -7905,10 +5589,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>15.59</v>
+        <v>13.74</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>5.99</v>
@@ -7917,33 +5601,33 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>26.38142857142857</v>
+        <v>33.99</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.29</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>28.32333333333333</v>
+        <v>5.115</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>16.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -7953,13 +5637,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>13.77538461538462</v>
+        <v>16.181</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -7969,10 +5653,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>14.99</v>
+        <v>13.32333333333333</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>6.99</v>
@@ -7985,13 +5669,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21.99</v>
+        <v>19.32333333333333</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>12.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -8001,13 +5685,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>21.24</v>
+        <v>24.99</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>17.49</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -8017,13 +5701,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>5.59</v>
+        <v>5.99</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5.19</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -8033,13 +5717,13 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>11.45666666666667</v>
+        <v>12.94454545454545</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -8049,90 +5733,90 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18.99</v>
+        <v>26.99</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>3.99</v>
+        <v>17.49</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>17.49</v>
+        <v>31.99</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>6.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>31.99</v>
+        <v>14.99</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>31.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>13.19</v>
+        <v>6.49</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>5.99</v>
@@ -8141,33 +5825,17 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>8.323333333333332</v>
+        <v>99.94500000000001</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>61.77</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>12.29</v>
+        <v>59.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="82" customWidth="1" min="6" max="6"/>
+    <col width="71" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="620" customWidth="1" min="9" max="9"/>
+    <col width="622" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -544,7 +544,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -554,43 +554,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Varal de Chão Slim Branco Mor</t>
+          <t>Frigideira Alumínio Funda Loreto 24cm Tramontina</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mor</t>
+          <t>Tramontina</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>VARAL CHÃO MOR SLIM BRANCO UNI R$: 119,90</t>
+          <t>FRIGIDEIRA TRAMONTINA ALUMÍNIO FUNDA LORETO 24CM</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>119.9</v>
+        <v>58.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -600,614 +600,594 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Liquidificador Preto L900 127v Mondial</t>
+          <t>Bule Térmico Aço Inox Exata Tramontina 1L</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Mondial</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+          <t>Tramontina</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>LIQUIDIFICADOR MONDIAL PRETO L900 127V UNI R$: 129,90</t>
+          <t>BULE TÉRMICO TRAMONTINA AÇO INOX EXATA 1L</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>129.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ventilador Mondial Power 40cm 127v</t>
+          <t>Vinho Cabeza de Piedra 750ml</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mondial</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Cabeza De Piedra</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>750ml</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>VENTILADOR MONDIAL SUPER POWER 40CM 127V</t>
+          <t>VINHO IMPORTADO CABEZA DE PIEDRA 750ML</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>159.9</v>
+        <v>19.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Gin Rock's 1L</t>
+          <t>Polpa de Fruta Pura Polpa 100g</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Rock'S</t>
+          <t>Pura Polpa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA GIN ROCK'S 1L</t>
+          <t>Polpa de Suco Pura Polpa Acerola, Caju, Goiaba, Limão ou Manga 100g</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>26.99</v>
+        <v>1.99</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Vinho Reservado Concha Toro Concha Y Toro 750ml</t>
+          <t>Polpa de Fruta Cupuaçu Polpanorte 100g</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Concha Y Toro</t>
+          <t>Polpanorte</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>750ml</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>VINHO CHILENO RESERVADO CONCHA Y TORO 750ML</t>
+          <t>POLPA POLPANORTE CUPUAÇU 100G</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>34.99</v>
+        <v>3.99</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Extra Corona 330ml</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Corona</t>
-        </is>
-      </c>
+          <t>Fígado de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA CORONA EXTRA 330ML</t>
+          <t>FIGADO DE FRANGO KG</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Cerveja 12x Itaipava 269ml</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Itaipava</t>
-        </is>
-      </c>
+          <t>Dorso de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CERVEJA ITAIPAVA CX C/12X269ML</t>
+          <t>DORSO DE FRANGO KG</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>26.99</v>
+        <v>4.99</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Michelob Ultra 6x 330ml</t>
+          <t>Coxa e Sobrecoxa de Frango Sadia kg</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Michelob Ultra</t>
+          <t>Sadia</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>330ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA MICHELOB ULTRA CX C/6X330ML</t>
+          <t>Coxa com Sobrecoxa de Frango Sadia - Kg 9,99</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>36.99</v>
+        <v>9.99</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Original Antarctica 2L</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Antarctica</t>
-        </is>
-      </c>
+          <t>Pé de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANÁ ANTARCTICA ORIGINAL 2L</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.99</v>
+        <v>10.59</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Refrigerante Pet Coca-Cola 2.5L</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
+          <t>Moela de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2.5L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA PET 2,5L</t>
+          <t>MOELA DE FRANGO KG</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>10.9</v>
+        <v>11.99</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Uva Niagara Garibaldi 500g</t>
+          <t>Coxinha da Asa de Frango Perdigão kg</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Garibaldi</t>
+          <t>Perdigão</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>SUCO UVA TINTO INTEGRAL GARIBALDI 1,5LTS</t>
+          <t>COXINHA DA ASA DE FRANGO PERDIGÃO IQF PCT 800G</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>15.99</v>
+        <v>13.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Água Mineral Puríssima Fardo 12x 500ml</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Puríssima</t>
-        </is>
-      </c>
+          <t>Meio da Asa de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ÁGUA MINERAL PURÍSSIMA COM E SEM GÁS FD C/ 12X497/ 500ML</t>
+          <t>Meio da Asa Kg R$ 29,99</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>23.99</v>
+        <v>29.99</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Empanado de Frango Perdigão 100g</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Perdigão</t>
-        </is>
-      </c>
+          <t>Língua Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>EMPANADO FRANGO TRADICIONAL PERDIGÃO 100G</t>
+          <t>Língua Bovina Kg</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.89</v>
+        <v>5.99</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Frango Oriental Pedaços Seara 275g</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Língua Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>275g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>FRANGO ORIENTAL SEARA PEDAÇOS 275G</t>
+          <t>LÍNGUA BOVINA 6,99 KG</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -1215,34 +1195,34 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango kg</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1253,99 +1233,91 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>COXINHAS DAS ASAS FRANGO S/TEMPERO R$: 11,99 KG</t>
+          <t>CORAÇÃO BOVINO 6,99 KG</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Moela de Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Bucho Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SEARA BDJ 1KG</t>
+          <t>BUCHO BOVINO 8,99 KG</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>15.99</v>
+        <v>8.99</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Frango Inteiro Nho Bento kg</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Nho Bento</t>
-        </is>
-      </c>
+          <t>Mocotó Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1353,125 +1325,117 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>FRANGO INTEIRO CAIPIRA NHO BENTO DE: R$ 23,99 POR: R$ 17,99 KG</t>
+          <t>MOCOTÓ BOVINO 8,99 KG</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>17.99</v>
+        <v>8.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Lar kg</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Lar</t>
-        </is>
-      </c>
+          <t>Fígado Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>FILÉ PEITO FRANGO LAR BDJ C/ 1KG</t>
+          <t>FÍGADO BOVINO 8,99 KG</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>18.99</v>
+        <v>8.99</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Meio da Asa de Frango Seara 1kg</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Mocotó Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG R$: 24,99</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>24.99</v>
+        <v>8.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1447,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Meio da Asa de Frango Kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -1499,32 +1463,32 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>MEIO DA ASA R$ 29,99 Kg</t>
+          <t>MOCOTÓ BOVINO KG R$ 8,99</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>29.99</v>
+        <v>8.99</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1534,47 +1498,43 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Hambúrguer Bovino Aves Sadia 56g</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Recorte Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>HAMBÚRGUER BOVINO E AVES SADIA 56G</t>
+          <t>RECORTE BOVINO KG</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.39</v>
+        <v>9.99</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1584,7 +1544,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -1595,32 +1555,32 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA R$ 19,99 Kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1630,7 +1590,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina Minga kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1641,32 +1601,32 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>COSTELA MINGA kg R$ 25,99</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>25.99</v>
+        <v>9.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1676,7 +1636,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Ponta de Peito Sem Osso Bovina Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1687,25 +1647,25 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>PONTA DE PEITO S/ OSSO R$ 34,99 Kg</t>
+          <t>Fígado Bovino - Kg 9,99</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>34.99</v>
+        <v>9.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1682,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1733,32 +1693,32 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>COXÃO DURO R$ 36,99 Kg</t>
+          <t>BUCHO BOVINO KG R$ 9,99</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>36.99</v>
+        <v>9.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1768,7 +1728,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -1779,32 +1739,32 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>CONTRA FILÉ C/ OSSO R$ 37,99 Kg</t>
+          <t>Mocotó Bovino - Kg 10,99</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37.99</v>
+        <v>10.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1814,7 +1774,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1825,25 +1785,25 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CAPA CONTRA FILÉ BOV. kg R$ 37,99</t>
+          <t>Bucho Bovino Kg 10,99</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>37.99</v>
+        <v>10.99</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1820,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Capa de Filé Bovina Kg</t>
+          <t>Ossobuco Bovino Kg</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -1871,32 +1831,32 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>CAPA C. FILÉ R$ 39,99 Kg</t>
+          <t>OSSOBUCO KG R$ 19,99</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>39.99</v>
+        <v>19.99</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1906,7 +1866,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cupim Bovino Kg</t>
+          <t>Costela Bovina kg</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1917,32 +1877,32 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>CUPIM BOV. kg R$ 45,99</t>
+          <t>Costela Bovina Kg R$ 19,99</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.99</v>
+        <v>19.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1952,7 +1912,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Picanha Bovina kg</t>
+          <t>Carne Moída Bovina kg</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -1963,32 +1923,32 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>PICANHA FATIADA BOV. kg R$ 45,99</t>
+          <t>Carne Moída Kg</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>45.99</v>
+        <v>22.99</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1998,7 +1958,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Maminha Bovina kg</t>
+          <t>Costela Bovina kg</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -2009,32 +1969,32 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Maminha Bov. kg R$ 49,99</t>
+          <t>Costela Bovina Para Panela Kg</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>49.99</v>
+        <v>24.99</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2044,7 +2004,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Alcatra Bovina kg</t>
+          <t>Rabada Bovina Kg</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
@@ -2055,324 +2015,308 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Coração Alcatra kg R$ 49,99</t>
+          <t>RABADA BOVINA 25,99 KG</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>49.99</v>
+        <v>25.99</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Camarão Inteiro Costa Sul 400g</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Costa Sul</t>
-        </is>
-      </c>
+          <t>Rabo Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTA SUL INTEIRO PCT C/ 400G</t>
+          <t>RABO BOVINO KG R$ 27,99</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>24.99</v>
+        <v>27.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Filé de Peixe Tilápia Bello 800g</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
+          <t>Ponta de Peito Sem Osso Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>FILÉ PEIXE TILÁPIA BELLO 800G</t>
+          <t>Ponta de Peito S/ Osso Kg R$ 34,99</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>35.99</v>
+        <v>34.99</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Peixe Inteiro Pintado</t>
+          <t>Patinho Bovino kg</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>PEIXE INTEIRO PINTADO</t>
+          <t>PATINHO BOVINO KG R$ 36,99</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>42.99</v>
+        <v>36.99</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Mortadela Defumada Seara 180g</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Coxão Duro Bovino kg</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>180g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>MORTADELA DEFUMADA SEARA 180G</t>
+          <t>Coxão Duro Kg R$ 36,99</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>7.99</v>
+        <v>36.99</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Seara kg</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Contrafilé Bovino kg</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>370g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA PAIO SEARA 370G DE: R$ 15,99 POR: R$ 8,99</t>
+          <t>Contra Filé C/ Osso Kg R$ 37,99</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8.99</v>
+        <v>37.99</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Presunto Cozido Seara kg</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Capa de Filé Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>180g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>PRESUNTO FATIADO SEARA 180G</t>
+          <t>Capa C. Filé Kg R$ 39,99</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>9.99</v>
+        <v>39.99</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2382,47 +2326,43 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Sadia kg</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Pé Suíno Kg</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA TIPO PORTUGUESA SADIA 400G</t>
+          <t>PÉ SUÍNO KG</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2432,14 +2372,10 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Salsicha Hot Dog Perdigão kg</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Perdigão</t>
-        </is>
-      </c>
+          <t>Pé Suíno Kg</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2447,32 +2383,32 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>SALSICHA HOT DOG PERDIGÃO R$: 10,99 KG</t>
+          <t>PÉ SUÍNO KG R$ 9,99</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2482,10 +2418,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana kg</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Salsicha Hot Dog Seara kg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2493,32 +2433,32 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA FINA APIMENTADA R$ 16,99 Kg</t>
+          <t>Salsicha Seara Kg</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16.99</v>
+        <v>11.29</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2528,14 +2468,10 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Excelência kg</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Excelência</t>
-        </is>
-      </c>
+          <t>Linguiça Toscana kg</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2543,7 +2479,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA TOSCANA EXCELÊNCIA kg R$ 16,99</t>
+          <t>Linguiça Fina Apimentada Kg R$ 16,99</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
@@ -2551,24 +2487,24 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t39.30808-6/816394345_1685454466918284_5336394654510285947_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4OTU5ODMyMjQ1NjI5MzE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=u13-VrQj4XoQ7kNvwH-sIi9&amp;_nc_oc=Adruk6PHcYfJ8I2P7NFuLIk8AeeceBfLyZTZ7YmGCYRjhtDAi-SWMmnWOl7efMATfjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIX8IVW69yP3UH2XIfQ6k5-6tHY9klCa6zaTG-d51D9dQ&amp;oe=6AB5B64C</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2578,456 +2514,472 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mandioca Congelada Kg</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Mandioca Descascada Pão da Terra Congelada 1kg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Pão Da Terra</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Mandioca Congelada kg R$ 5,99</t>
+          <t>MANDIOCA PÃO DA TERRA DESCASCADA CONGELADA 1KG</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>5.99</v>
+        <v>5.79</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Tekitos Seara 300g</t>
+          <t>Sabonete Farnese 85g</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Seara</t>
+          <t>Farnese</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>85g</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>TEKITOS TRADICIONAL SEARA 300G DE: R$ 11,99 POR: R$ 8,99</t>
+          <t>Sabonete Farnese 85g</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>8.99</v>
+        <v>1.69</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Lasanha Sadia 600g</t>
+          <t>Creme Dental Tripla Limpeza Completa Sorriso 70g</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Sorriso</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>70g</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>LASANHA SADIA SABORES 600G</t>
+          <t>CREME DENTAL SORRISO TRIPLA LIMPEZA COMPLETA 70G</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>16.99</v>
+        <v>2.99</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Açaí Origem 1.5L</t>
+          <t>Absorvente Interno Intimus c/ 8</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Origem</t>
+          <t>Intimus</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1.5L</t>
+          <t>c/ 8</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>AÇAÍ ORIGEM TODA HORA 1,5L DE: R$ 30,49 POR: R$ 22,99</t>
+          <t>Absorvente Interno Intimus c/8 unidades</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>22.99</v>
+        <v>9.99</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Papel Sulfite A4 Chamex 500 Folhas 75g</t>
+          <t>Creme Dental Total 12 Colgate 90g</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Chamex</t>
+          <t>Colgate</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>75g</t>
+          <t>90g</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>PAPEL A4 75G CHAMEX C/500 FOLHAS R$: 27,99</t>
+          <t>Creme Dental Colgate Total 12 90g</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>27.99</v>
+        <v>9.99</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
+          <t>Desodorante Aerosol Dove 150ml</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Mili</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>c/ 24</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>PAPEL HIGIÊNICO MILI SENSITIVE CARE PCT C/24 ROLOS</t>
+          <t>Desodorante Dove 150ml</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>39.99</v>
+        <v>16.99</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+          <t>Fralda Descartável Tripla Proteção Mega Huggies</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Huggies</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LARANJA PERA RIO Kg R$ 2,49</t>
+          <t>FRALDA HUGGIES TRIPLA PROTEÇÃO MEGA PCT</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2.49</v>
+        <v>32.9</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Mili</t>
+        </is>
+      </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BATATA INGLESA Kg R$ 4,99</t>
+          <t>PAPEL HIGIÊNICO MIILL ATUALLE FOLHA DUPLA 20M 12 ROLOS</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Duetto</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>CENOURA Kg R$ 4,99</t>
+          <t>Papel Hig. Duetto - 20m Folha Dupla Neutro c/ 12 Rolos</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>4.99</v>
+        <v>13.99</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Uva Niagara 500g</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr"/>
+          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Duetto</t>
+        </is>
+      </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>UVA VITORIA BDJ Bdj R$ 7,99</t>
+          <t>Papel higiênico Duetto 30m c/12 unidades</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>7.99</v>
+        <v>18.99</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -3036,479 +2988,443 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEE4Vnz&amp;_nc_oc=AdqlNRpiLCULjlsazK0tXT4cStRHtLEzeySLw-mXUsDHiuh29bNdprGSiNDaB22o0eu-DHWA9P3zLniHCrlua7If&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQKUAwaSN0haZX1brcpz0VHlX8DNrEchR3eUeNfU30l00A&amp;oe=6AB5A85E</t>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba 200g</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Piracanjuba</t>
-        </is>
-      </c>
+          <t>Alho Kg</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200G</t>
+          <t>Alho Nacional R$ 2,49 A Cada 100g</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2.99</v>
+        <v>2.49</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Leite Integral Piracanjuba 1L</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Piracanjuba</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>LEITE INTEGRAL PIRACANJUBA 1L</t>
+          <t>LARANJA PERA RIO Kg R$ 2,49</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>6.99</v>
+        <v>2.49</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Leite Condensado Piracanjuba 395g</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Piracanjuba</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>395g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
+          <t>Laranja Pera Rio Kg 2,59</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Queijo Mussarela Frimesa kg</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Frimesa</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA FATIADA FRIMESA 150G</t>
+          <t>Laranja Kg R$ 2,89</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>7.99</v>
+        <v>2.89</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Requeijão Cremoso Catupiry 200g</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Catupiry</t>
-        </is>
-      </c>
+          <t>Melancia Kg</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>REQUEIJÃO CREMOSO TRADICIONAL OU LIGHT CATUPIRY 200G DE: R$ 12,99 POR: R$ 8,99</t>
+          <t>Melancia Kg 2,99</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Margarina c/ Sal Qualy 500g</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Qualy</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>MARGARINA QUALY CREMOSA 500G R$: 8,99</t>
+          <t>Laranja Nacional R$ 3,49 KG</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>8.99</v>
+        <v>3.49</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Leite em Pó Ninho Integral Nestlé 380g</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé</t>
-        </is>
-      </c>
+          <t>Beterraba Kg</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>380g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>LEITE EM PÓ NINHO NESTLÉ INTEGRAL 380G</t>
+          <t>Beterraba Kg R$ 3,79</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>17.99</v>
+        <v>3.79</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Chantilly Amélia 1L</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Amélia</t>
-        </is>
-      </c>
+          <t>Banana Nanica Kg</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>CHANTILY AMÉLIA TRADICIONAL 1L DE: R$ 24,99 POR: R$ 19,90</t>
+          <t>Banana Nanica Kg R$ 3,79</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>19.9</v>
+        <v>3.79</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Manteiga c/ Sal Aviação 200g</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Aviação</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>MANTEIGA AVIAÇÃO C/ SAL 500G</t>
+          <t>Repolho Verde Kg R$ 3,89</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>35.99</v>
+        <v>3.89</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Queijo Mussarela kg</t>
+          <t>Mandioca Kg</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -3519,757 +3435,709 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>QUEIJO MUSSARELA FATIADA R$: 44,99 KG</t>
+          <t>MANDIOCA KG</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>44.99</v>
+        <v>3.99</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Saponáceo Cremoso Ypê 300ml</t>
+          <t>Banana Nanica Desconhecida Kg</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Desconhecida</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>SAPONÁCEO CREMOSO YPÊ 300ML R$: 6,99</t>
+          <t>Banana Nanica - Kg</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Limpador Perfumado Casaflor 1.75L</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Casaflor</t>
-        </is>
-      </c>
+          <t>Abóbora Kabotiã 1kg</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1.75L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>LIMPADOR PERFUMADO CASAFLOR 1,75LT</t>
+          <t>Abóbora Kabotiã R$ 3,99 KG</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>12.99</v>
+        <v>3.99</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 5L</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Qboa</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>5L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA SANITÁRIA QBOA 5L R$: 19,99</t>
+          <t>Repolho Verde R$ 3,99 KG</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>19.99</v>
+        <v>3.99</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Esponja de Aço Bombril 45g</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Bombril</t>
-        </is>
-      </c>
+          <t>Beterraba Kg</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>45g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>ESPONJA DE AÇO BOMBRIL 45G</t>
+          <t>Beterraba R$ 3,99 kg</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
+          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t51.82787-15/817191708_18378579520237813_1831888496483920375_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjAyNzg0MTE3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sWfomYKgDMUQ7kNvwFtR6Ue&amp;_nc_oc=Adr3WN5xWIGwHcJE4LWUi6UX7GUwMQs28Th-W_MThiwIatwwpO7oFSHLuZdIAkaP6Vs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJn2zsP7bx7vvljb8DhyAKkI3C5aPtLj8NyvFszjscWjw&amp;oe=6AB72BDC</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Barra Neutro Ypê 5x 160g</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Ypê</t>
-        </is>
-      </c>
+          <t>Banana Nanica Kg</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>160g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>SABÃO BARRA YPÊ NEUTRO PCT 5X160G</t>
+          <t>Banana Nanica R$ 4,49 KG</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>14.99</v>
+        <v>4.49</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Downy 2L</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Downy</t>
-        </is>
-      </c>
+          <t>Batata Doce Kg</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE ROUPAS CONCENTRADO DOWNY ALFAZEMA OU VERÃO TROPICAL 1L</t>
+          <t>Batata Doce R$ 4,99 KG</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>22.99</v>
+        <v>4.99</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Ypê 2L</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Ypê</t>
-        </is>
-      </c>
+          <t>Cebola Nacional Kg</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>5L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>AMACIANTE ROUPAS YPÊ 5L</t>
+          <t>Cebola Nacional R$ 4,99 KG</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>22.99</v>
+        <v>4.99</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Sabão Líquido Lavagem Perfeita Omo 1.8L</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
+          <t>Batata Inglesa Kg</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1.8L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>SABÃO LÍQUIDO OMO LAVAGEM PERFEITA 1,8L R$: 22,99</t>
+          <t>BATATA INGLESA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>22.99</v>
+        <v>4.99</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Pó Omo 1.6kg</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Omo</t>
-        </is>
-      </c>
+          <t>Cenoura Kg</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2.2kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>SABÃO PÓ OMO LAVAGEM PERFEITA 2,2KG</t>
+          <t>CENOURA Kg R$ 4,99</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>29.99</v>
+        <v>4.99</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Arroz Branco Tipo 1 Koblenz 5kg</t>
+          <t>Batata Inglesa Desconhecida Kg</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>Desconhecida</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ PCT C/5KG</t>
+          <t>Batata Inglesa Kg</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>24.99</v>
+        <v>5.49</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Açúcar</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Açúcar Cristal Doce Dia 2kg</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Doce Dia</t>
-        </is>
-      </c>
+          <t>Cenoura Kg</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>AÇÚCAR CRISTAL DOCE DIA PCT C/2KG</t>
+          <t>Cenoura Kg R$ 5,59</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>5.99</v>
+        <v>5.59</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Wafer Bauducco 140g</t>
+          <t>Cenoura Desconhecida Kg</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Desconhecida</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>140g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO WAFER BAUDUCCO 140G</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3.59</v>
+        <v>5.59</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Chocolate Wafer Hershey's 120g</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Hershey'S</t>
-        </is>
-      </c>
+          <t>Mamão Formosa Kg</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>120g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>CHOCOLATE WAFER HERSHEY 120G DE: R$ 4,99 POR: R$ 3,99</t>
+          <t>Mamão Formosa Kg R$ 5,99</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Salt Plus Sol 360g</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Sol</t>
-        </is>
-      </c>
+          <t>Maçã Kg</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>360g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO SOL SALT PLUS 360G</t>
+          <t>Maçã Nacional Kg 5,99</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>4.89</v>
+        <v>5.99</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/800642793_1379165584303399_9003255061552634856_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4OTk3Nzg1MDUzODI4OTE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=z_ZdfFHZPEcQ7kNvwG2wkBf&amp;_nc_oc=AdqqZuKcQZXgugPWOKCkWGDj9Fo-VcIswEl9AfUDZWmRaKGuUgWtuzX16kY5dHHwWLA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=Cih5T5nH7DrU_3xcFge5Eg&amp;_nc_ss=7a22e&amp;oh=00_AQKpvoTWU614q11aA7iEp2b-EhtpjHjr5Kg-eIuXDWHBRA&amp;oe=6AB5C41D</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfP7cbAugF/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Maisena Mabel 300g</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Mabel</t>
-        </is>
-      </c>
+          <t>Abacate Kg</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>BISCOITO LAMINADO MABEL LEITE OU MAISENA 300G</t>
+          <t>Abacate Kg 5,99</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
@@ -4277,1017 +4145,2703 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Rosquinha Coco Mabel 600g</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Mabel</t>
-        </is>
-      </c>
+          <t>Mamão Formosa Kg</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA MABEL COCO 600G</t>
+          <t>Mamão Formosa - Kg 5,99</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Biscuit Choco Bauducco 80g</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Bauducco</t>
-        </is>
-      </c>
+          <t>Cenoura Kg</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>80g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>BISCOITO BAUDUCCO BISCUIT CHOCO 80G</t>
+          <t>Cenoura KG</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/795341841_18378579571237813_1586404088888970145_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjUwMDk3MjgzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P6K8R92ap6UQ7kNvwFx_fF2&amp;_nc_oc=Adr9Tg4AdBYc-Ag0pG4CEbHoNpnQBULdSOJ8hr7HsRIt84S4jc8vfwgMhiFmY0rjZt4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQITtkkK641O9ehU7qsvTOzf8X2qQuuJra5Rh-KFZu1EKA&amp;oe=6AB726DC</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Doce de Leite Comajul 400g</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Comajul</t>
-        </is>
-      </c>
+          <t>Abacate Kg</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>DOCE LEITE TRADICIONAL COMAJUL 400G DE: R$ 11,59 POR: R$ 9,99</t>
+          <t>Abacate R$ 5,99 KG</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Bombons Sortidos Lacta Favoritos 250 6g</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Lacta</t>
-        </is>
-      </c>
+          <t>Banana da Terra Kg</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>BOMBONS SORTIDOS LACTA FAVORITOS 250,6G</t>
+          <t>Banana Da Terra R$ 5,99 KG</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>14.99</v>
+        <v>5.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Cereal Matinal Snow Flakes Nestlé 800g</t>
+          <t>Ovos Vermelhos c/ 30 Fenix</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Fenix</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>CEREAL MATINAL NESTLÉ SNOW FLAKES 800G</t>
+          <t>OVO VERMELHO FENIX C/12UN R$ 5,99</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Achocolatado em Pó Toddy 750g</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Toddy</t>
-        </is>
-      </c>
+          <t>Melão Amarelo Kg</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO PÓ TODDY 750G</t>
+          <t>Melão Amarelo Kg R$ 6,69</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>16.99</v>
+        <v>6.69</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/816310125_1685420953588302_3447760873232905007_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3NDIyMjU4MzAyNjA0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MYN4rbKmIcsQ7kNvwHQ259d&amp;_nc_oc=AdrZyuOmG5J9LB_4zWknBBWOdm07bmsXPvh4zSoMKU5yzMg5eOMjVhm7OkUscCIty7oJSXJYKGfat_NOrI39gUey&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJx5KAjS9OmABczinPIFe091zrySJXLNOD2KJofss0f9A&amp;oe=6AB5AF38</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Creme de Avelã Nutella 700g</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Nutella</t>
-        </is>
-      </c>
+          <t>Melão Amarelo Kg</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>700g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>CREME AVELÃ NUTELLA 700G</t>
+          <t>Melão Amarelo - Kg 6,99</t>
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>49.99</v>
+        <v>6.99</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Café Tradicional Brasileiro 500g</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Brasileiro</t>
-        </is>
-      </c>
+          <t>Mamão Formosa Kg</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>CAFÉ BRASILEIRO TRADICIONAL E EXTRA FORTE PCT 500G</t>
+          <t>Mamão Formoso R$ 6,99 KG</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>26.99</v>
+        <v>6.99</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Macarrão Espaguete Galo 500g</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Galo</t>
-        </is>
-      </c>
+          <t>Cebola Nacional Kg</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>MACARRÃO SÊMOLA GALO ESPAGUETE 8 500G</t>
+          <t>Cebola Kg R$ 7,39</t>
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3.99</v>
+        <v>7.39</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Óleo de Soja Liza 900ml</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Liza</t>
-        </is>
-      </c>
+          <t>Uva Niagara 500g</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>900ml</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>ÓLEO SOJA LIZA OU CONCÓRDIA 900ML</t>
+          <t>Uva Vitória Bdj. 500g 7,99</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t39.30808-6/816452598_1685420946921636_6128012569102372457_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4OTU3NDIyMjA3MTI4NTEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hpBevGu6vscQ7kNvwH8uox3&amp;_nc_oc=Adpy8B1HVi2HK3reRNK1xOHOXXcpVVQe6HC0Cs2Zf7u7UH_ohmfyfgxCbyR2lOdrpNKC1wS70K10CLcvMpn-aQNI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQLOcOkAw04NN5nG50ZyhV6kyCNmebKRdROI6JjSNGAUrg&amp;oe=6AB5C42A</t>
+          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Azeite de Oliva Extra Virgem Borges 500ml</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Borges</t>
-        </is>
-      </c>
+          <t>Uva Niagara 500g</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>AZEITE OLIVA EXTRA VIRGEM BORGES 500ML DE: R$ 49,29 POR: R$ 27,99</t>
+          <t>UVA VITORIA BDJ Bdj R$ 7,99</t>
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>27.99</v>
+        <v>7.99</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Lenha Eucalipto Saco São Luiz 12kg</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>São Luiz</t>
-        </is>
-      </c>
+          <t>Maçã Fuji Kg</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>12kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Lenha Eucalipto São Luiz Saco C/12kg R$ 31,99</t>
+          <t>Maçã Fuji Kg R$ 8,29</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>31.99</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Alho Bello Kg</t>
+          <t>Uva Niagara Vitória / Isís 500g</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Vitória / Isís</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>PÃO DE ALHO BELLO 300G R$ 9,99</t>
+          <t>Uva Vitória/Isís Bandeja 500G R$ 8,99 UN</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwGMrQCT&amp;_nc_oc=Adr7meULCiuIIW8sxGFbFWqhxKx0yIkdZGuRrblhLI_n4At3B_50ARtBLLJOWiz79yiTm5vSXGIp1sE49A0qOe6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=4U8K8K4Lmj9WOkNorMCJGA&amp;_nc_ss=7a22e&amp;oh=00_AQJB7aIFEtHH1j9JLaRB9V-YqvPh5WIapo5BMRKP_2uJDg&amp;oe=6AB5C799</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Alho Bello Kg</t>
+          <t>Ovos Brancos c/ 30 Mantiqueira</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
+          <t>Mantiqueira</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Pão de Alho Tradicional Bello 300g R$ 9,99</t>
+          <t>Ovos Brancos Mantiqueira c/20 R$ 10,79</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>9.99</v>
+        <v>10.79</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/817961814_1685454463584951_4039844944953148956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4OTU5ODMyMjY0MDgzOTU1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=uyaxmvdysAgQ7kNvwGjlj6_&amp;_nc_oc=Adp6Avcy8LbIRovNsf4lLYCr9_bANGYZKLFDQQCv-mSvvZToRvHBVdP7Fydt39_8peM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=_cpa66jQEVwAWR6Ikt4XOQ&amp;_nc_ss=7a22e&amp;oh=00_AQIxhf8b3qSfkILtf0Z5EsUUBq9Z5mpjLLb3Sr6b3MQQ9w&amp;oe=6AB5B270</t>
+          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd5owUAEbx/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Pão de Queijo Congelado Mc 1kg</t>
+          <t>Ovos Brancos c/ 30 Mantiqueira</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Mc</t>
+          <t>Mantiqueira</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>c/ 20</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>PÃO QUEIJO CONGELADO MC PCT C/ 1KG</t>
+          <t>Ovo Mantiqueira Com 20 Unidades R$ 12,99 UN</t>
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>17.99</v>
+        <v>12.99</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817719502_1685420176921713_1083522880512170904_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4OTU3MzcyOTc2ODc0MDk5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JYjLipO-M_4Q7kNvwGmo8sJ&amp;_nc_oc=AdotzBRiHT1EU0yaSooOZJTzhcPGLsqSBrvjmkGN2JsNw_6Krl4rUVY2lvcMh3ddJxw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQKsccg2HswafT9v5Rkwz_5_IAi5OHmWSgQeq20ATaasDA&amp;oe=6AB5C078</t>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Pizza Sabores Sadia 460g</t>
+          <t>Ovos Brancos c/ 30 Campo Verde</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Campo Verde</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>460g</t>
+          <t>c/ 30</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>PIZZA SADIA SABORES 460G</t>
+          <t>Ovos Brancos Campo Verde Bdj. 30 Und.</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>21.99</v>
+        <v>15.99</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/817217627_1685420160255048_6887450375741801176_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3MzczMDA5NTg3MzkyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=u0NsFjVlza4Q7kNvwHXECZt&amp;_nc_oc=AdoMOFONiWwGX_mvZ7zlRGgOZHlPRiw5Nh1qA7RiMUNarKVE8ENX0aW1ScU53ynd1fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQLSOKL885B-KckmrWJ08i3aSvXsUxsQirFWmAfnm1_QCA&amp;oe=6AB5AA95</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Pão Bisnaguinha Visconti 240g</t>
+          <t>Creme de Leite Italac 200g</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Visconti</t>
+          <t>Italac</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>240g</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>PÃO BISNAGUINHA TRADICIONAL VISCONTI 240G DE: R$ 7,29 POR: R$ 5,99</t>
+          <t>CREME DE LEITE ITALAC 10% DE GORDURA 200G</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Pão Bauducco 390g</t>
+          <t>Cream Cheese Scala Pote 150g</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Scala</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>390g</t>
+          <t>150g</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>PÃO FATIADO TRADICIONAL BAUDUCCO 390G DE: R$ 9,79 POR: R$ 6,99</t>
+          <t>CREAM CHEESE SCALA POTE 150G</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Pet Shop</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Ração para Cães Adultos Thor 7kg</t>
+          <t>Doce de Leite Frimesa 400g</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Frimesa</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>7kg</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>RAÇÃO PARA CÃES ADULTOS THOR SACO 7KG R$: 59,90</t>
+          <t>Doce de Leite Frimesa 400g</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>59.9</v>
+        <v>8.99</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-mxp2-1.cdninstagram.com/v/t39.30808-6/796527923_1685420950254969_3813493912658075038_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4OTU3NDIyMTc2MDk1MTc4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6gwKdUC_fF8Q7kNvwGwS6LS&amp;_nc_oc=Adr9pm7-usE5WwboO0OVUH0eEsUi1lFVb-NhrptykPL8cdA6v9GnCvQRKL5YQ2kq18dvh3xfv7YY5VzPYiwDNUrz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=MJXzRJTuzfCU-5D9yVvF6Q&amp;_nc_ss=7a22e&amp;oh=00_AQJ6b3StGgUXmlKphvEj5q6c_hLyePhV6X0ymbi8YxxWnw&amp;oe=6AB5D04E</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddd0KLbHcLN/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Margarina c/ Sal Qualy 500g</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Qualy</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>MARGARINA QUALY CREMOSA C/SAL 1KG</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Limpador Multiuso Azulim 500ml</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Azulim</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>LIMPADOR AZULIM MULTIUSO 500ML</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Desinfetante Girando Sol 2L</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Girando Sol</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Desinfetante Girando Sol 500ml</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Limpador Multiuso Veja 500ml</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Veja</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Limpador Multiuso Veja 500ml</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura Madri com Cabo Condor</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Condor</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>VASSOURA CONDOR MADRI C/ CABO</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Água Sanitária Ypê 2L</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Ypê</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>2L</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>ÁGUA SANITÁRIA YPÊ 2L</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Água Sanitária Qboa 2L</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Qboa</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2L</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Água Sanitária Qboa 2L</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Desinfetante Pinho Bril 2L</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Pinho Bril</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>1.75L</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>DESINFETANTE PINHO BRIL 1,75L</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Balde Plástico Sanremo 8L</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Sanremo</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>8L</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>BALDE SANREMO 8L REF:610/7</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Rodo Plástico com Cabo Condor</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Condor</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>RODO CONDOR PLÁSTICO C/ CABO</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Detergente Líquido Polylar 500ml</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Polylar</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>DETERGENTE POLYLAR 500ML</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Esponja de Aço Bombril 45g</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Bombril</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>45g</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Esponja de Aço Bombril 45g</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Esponja Multiuso Scotch Brite Scotch-Brite c/ 4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Scotch-Brite</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>c/ 4</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Esponja Multiuso Scotch-Brite leve 4, pague 3</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Tixan Ypê</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>800g</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Sabão em Pó Tixan Ypê Primavera ou Maciez 800g</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Amaciante Girando Sol 2L</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Girando Sol</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Amaciante Concentrado Girando Sol 1L</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Amaciante Mon Bijou 2L</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Mon Bijou</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>5L</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>AMACIANTE MON BIJOU 5L</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Sabão em Pó Ápyce 1.6kg</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Ápyce</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>SABÃO EM PÓ ÁPYCE MULTIAÇÃO 4KG</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Amaciante Ypê 2L</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Ypê</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>7L</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>AMACIANTE YPÊ PRO ROUPAS E TECIDOS 7L</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Arroz</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Arroz Branco Tipo 1 Fartura 5kg</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Fartura</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Arroz Fartura Pct. 5 Kg</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Biscoito de Leite Marilan 300g</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Marilan</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>BISCOITO MARILAN LEITE 300G</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Achocolatado em Pó Toddy 750g</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Toddy</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Batata Inglesa Boa Kg</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>800g</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>BATATA PALHA BOA TRADICIONAL 800G</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Farináceos</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo Tipo 1 Anaconda 1kg</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Anaconda</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>FARINHA DE TRIGO ANACONDA PREMIUM 1KG</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Azeitona Verde Rivoli Sachê 100g</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Rivoli</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>AZEITONA VERDE RIVOLI SACHÊ 100G</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Feijão Carioca Koblenz 1kg</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Koblenz</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>FEIJÃO CARIOCA KOBLENZ TIPO1 PCT 1KG</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Pepino em Conserva Vale Fértil Vidro 300g</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Vale Fértil</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>PEPINO VALE FÉRTIL CONSERVA VIDRO 300G</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Amendoim Mape 1kg</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Mape</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Amendoim Mape 1 kg R$ 14,99 UN</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Molhos e Condimentos</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Tomate Longa Vida Val Kg</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>MOLHO DE TOMATE VAL TRADICIONAL SACHÊ 300G</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Abóbora Cabotiá Desconhecida Kg</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Desconhecida</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Abóbora Cabotiá - Kg</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Repolho Verde Desconhecida Kg</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Desconhecida</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Repolho Verde - Kg</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Chuchu Desconhecida Kg</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Desconhecida</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Chuchu - Kg</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Mandioca Kg</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>MANDIOCA KG R$ 4,99</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Mexerica Kg</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Mexerica R$ 7,49 KG</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Alho Bello Kg</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Alho Bello 300g R$ 9,99</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Forma Eliane 500g</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Eliane</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>PÃO DE FORMA ELIANE 500G</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
           <t>Pet Shop</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Ração para Cães Saco Pedigree 10.1kg</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Pedigree</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Ração para Gatos Sabor Frango Catsy 10.1kg</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Catsy</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>10.1kg</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>RAÇÃO P/ CÃES PEDIGREE SACO C/ 10,1KG DE: R$ 179,99 POR: R$ 139,99</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/795253803_1685420180255046_7500292178422943859_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4OTU3MzczMDkwMTE3ODcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Hu5TS7eTjmIQ7kNvwFJ5Gjx&amp;_nc_oc=AdqAqVDKhFxxDywLgYB-zQpLd3zD6Qiv4xABZyCDDeq7SZ4_O4KSMkPeDOtYUTXQOn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=fMGHgWPss2qImC3P_cO2Xw&amp;_nc_ss=7a22e&amp;oh=00_AQK71asqpW5Ft4VhMrg94m4A3CYFxer49h1f3iDf79EDJw&amp;oe=6AB5A21A</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Ddd0C-8mOgi/</t>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>RAÇÃO CATSY PRÉMIUM FRANGO 10,1KG</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -5302,10 +6856,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -5342,58 +6896,134 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>5.926666666666667</v>
+        <v>6.365</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>10.9</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>20.615</v>
+        <v>17.5165625</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>2.49</v>
+        <v>1.19</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>39.99</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Bianchi</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>25.42231707317073</v>
+        <v>18.615</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>159.9</v>
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>9.631666666666666</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>9.106666666666666</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Tuiuiú</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9.156666666666666</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>25.99</v>
       </c>
     </row>
   </sheetData>
@@ -5407,10 +7037,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -5445,13 +7075,13 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>136.5666666666667</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>119.9</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -5461,170 +7091,170 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>30.99</v>
+        <v>19.9</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>26.99</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>23.65666666666667</v>
+        <v>2.99</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Refrigerantes</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>9.945</v>
+        <v>12.07571428571429</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>19.99</v>
+        <v>17.91307692307692</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>16.1025</v>
+        <v>11.815</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.89</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>35.60666666666667</v>
+        <v>5.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1.39</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>34.65666666666667</v>
+        <v>12.425</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>24.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>11.70428571428571</v>
+        <v>14.32333333333333</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>13.74</v>
+        <v>5.816829268292683</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>33.99</v>
+        <v>8.717500000000001</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>27.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>5.115</v>
+        <v>9.081111111111111</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2.49</v>
@@ -5633,209 +7263,145 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>16.181</v>
+        <v>13.88125</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2.99</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>13.32333333333333</v>
+        <v>18.99</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19.32333333333333</v>
+        <v>13.59666666666667</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>24.99</v>
+        <v>4.79</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>24.99</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Açúcar</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>5.99</v>
+        <v>8.217500000000001</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>12.94454545454545</v>
+        <v>1.19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3.59</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>26.99</v>
+        <v>4.790000000000001</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>26.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Padaria / Pães</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>3.99</v>
+        <v>10.945</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Pet Shop</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>17.49</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Padaria / Congelados</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Padaria / Pães</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>99.94500000000001</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>59.9</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="71" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="622" customWidth="1" min="9" max="9"/>
+    <col width="634" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -549,27 +549,31 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Frigideira Alumínio Funda Loreto 24cm Tramontina</t>
+          <t>Vinho Cabeza de Piedra 750ml</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tramontina</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>Cabeza De Piedra</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>750ml</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FRIGIDEIRA TRAMONTINA ALUMÍNIO FUNDA LORETO 24CM</t>
+          <t>VINHO IMPORTADO CABEZA DE PIEDRA 750ML</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>58.9</v>
+        <v>19.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -578,7 +582,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -590,36 +594,36 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Bule Térmico Aço Inox Exata Tramontina 1L</t>
+          <t>Polpa de Suco Pura Polpa Acerola Caju Goiaba Limão Ou Manga 100g</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Tramontina</t>
+          <t>Pura Polpa</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>BULE TÉRMICO TRAMONTINA AÇO INOX EXATA 1L</t>
+          <t>Polpa de Suco Pura Polpa Acerola, Caju, Goiaba, Limão ou Manga 100g</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -628,12 +632,12 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -645,31 +649,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Vinho Cabeza de Piedra 750ml</t>
+          <t>Polpa de Fruta Cupuaçu Polpanorte 100g</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Cabeza De Piedra</t>
+          <t>Polpanorte</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>750ml</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>VINHO IMPORTADO CABEZA DE PIEDRA 750ML</t>
+          <t>POLPA POLPANORTE CUPUAÇU 100G</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19.9</v>
+        <v>3.99</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -678,7 +682,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,36 +694,32 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Polpa de Fruta Pura Polpa 100g</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Pura Polpa</t>
-        </is>
-      </c>
+          <t>Fígado de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Polpa de Suco Pura Polpa Acerola, Caju, Goiaba, Limão ou Manga 100g</t>
+          <t>FIGADO DE FRANGO KG</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -728,48 +728,44 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Polpa de Fruta Cupuaçu Polpanorte 100g</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Polpanorte</t>
-        </is>
-      </c>
+          <t>Dorso de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>POLPA POLPANORTE CUPUAÇU 100G</t>
+          <t>DORSO DE FRANGO KG</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -778,19 +774,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -800,10 +796,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fígado de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+          <t>Coxa e Sobrecoxa de Frango Sadia kg</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -811,11 +811,11 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>FIGADO DE FRANGO KG</t>
+          <t>Coxa com Sobrecoxa de Frango Sadia - Kg</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Dorso de Frango Kg</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -857,11 +857,11 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>DORSO DE FRANGO KG</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4.99</v>
+        <v>10.59</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -870,19 +870,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -892,14 +892,10 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Coxa e Sobrecoxa de Frango Sadia kg</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Sadia</t>
-        </is>
-      </c>
+          <t>Moela de Frango Kg</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -907,11 +903,11 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Coxa com Sobrecoxa de Frango Sadia - Kg 9,99</t>
+          <t>MOELA DE FRANGO KG</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -920,19 +916,19 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -942,22 +938,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Pé de Frango Kg</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>Coxinha da Asa de Frango Perdigão kg</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Perdigão</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>800g</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pé de Frango Kg</t>
+          <t>COXINHA DA ASA DE FRANGO PERDIGÃO IQF PCT 800G</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10.59</v>
+        <v>13.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -966,29 +966,29 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Moela de Frango Kg</t>
+          <t>Língua Bovina Kg</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -999,11 +999,11 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO KG</t>
+          <t>Língua Bovina Kg</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1012,48 +1012,40 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Perdigão kg</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Perdigão</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>800g</t>
-        </is>
-      </c>
+          <t>Língua Bovina</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO PERDIGÃO IQF PCT 800G</t>
+          <t>LÍNGUA BOVINA</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1062,65 +1054,61 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Meio da Asa de Frango Kg</t>
+          <t>Coração Bovino</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Meio da Asa Kg R$ 29,99</t>
+          <t>CORAÇÃO BOVINO</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>29.99</v>
+        <v>6.99</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1130,22 +1118,18 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Língua Bovina Kg</t>
+          <t>Bucho Bovino</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Língua Bovina Kg</t>
+          <t>BUCHO BOVINO</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1154,12 +1138,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
@@ -1176,22 +1160,18 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Língua Bovina Kg</t>
+          <t>Mocotó Bovino</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>LÍNGUA BOVINA 6,99 KG</t>
+          <t>MOCOTÓ BOVINO</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1200,7 +1180,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1222,22 +1202,18 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Coração Bovino Kg</t>
+          <t>Fígado Bovino</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO 6,99 KG</t>
+          <t>FÍGADO BOVINO</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1222,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1258,7 +1234,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1268,7 +1244,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
@@ -1279,7 +1255,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO 8,99 KG</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
@@ -1292,12 +1268,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1290,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Recorte Bovino Kg</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1325,11 +1301,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>MOCOTÓ BOVINO 8,99 KG</t>
+          <t>RECORTE BOVINO KG</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1338,7 +1314,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1350,7 +1326,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1360,7 +1336,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -1371,11 +1347,11 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>FÍGADO BOVINO 8,99 KG</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1384,12 +1360,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1382,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1417,11 +1393,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1406,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1442,7 +1418,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1452,7 +1428,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -1463,11 +1439,11 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>MOCOTÓ BOVINO KG R$ 8,99</t>
+          <t>Fígado Bovino - Kg</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1476,19 +1452,19 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1498,7 +1474,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Recorte Bovino Kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1509,11 +1485,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>RECORTE BOVINO KG</t>
+          <t>Mocotó Bovino - Kg</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1522,19 +1498,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1559,7 +1535,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1568,12 +1544,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1566,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Carne Moída Bovina kg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1601,11 +1577,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Carne Moída Kg</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.99</v>
+        <v>22.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1614,7 +1590,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1626,7 +1602,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1636,7 +1612,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino Kg</t>
+          <t>Costela Bovina kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1647,11 +1623,11 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino - Kg 9,99</t>
+          <t>Costela Bovina Para Panela Kg</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1660,19 +1636,19 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1682,22 +1658,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Rabada Bovina</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG R$ 9,99</t>
+          <t>RABADA BOVINA</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1706,12 +1678,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwHQu0U-&amp;_nc_oc=Ado11OrIWql_4kAaa-HWQKcp4o8aGQ4QYts8Ujl80AEYww9-cvjDruaxSD6fLIZXpTY7e5Kmu64S-Bd7Uhlx2LBl&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQLWj7iOpqf-l8z64rimT5u5N6WZka2SR4Vwy3I1UWo7DQ&amp;oe=6AB85D60</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
@@ -1723,27 +1695,31 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino Kg</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>Mortadela Defumada Sadia 200g</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino - Kg 10,99</t>
+          <t>Mortadela Defumada Sadia Fatiada - 200g</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>10.99</v>
+        <v>1.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1752,29 +1728,29 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fper5-1.fna.fbcdn.net/v/t51.82787-15/814452748_18195430123391764_2828999644781460138_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTIyMzUxNTQwNzQ5MTQ1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YoNcf5lMjZgQ7kNvwH-1cjp&amp;_nc_oc=Adp5YgwalAAmk2RveKrpAAa0GvzaPjZ2jV23uwALXfVj0HLzF4_1Vnh0ptYxNefBrss&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fper5-1.fna&amp;_nc_gid=CMazBgmhBBu65scWjsP1oQ&amp;_nc_ss=7a22e&amp;oh=00_AQL5e5rK0eHJUblzKg46UK70hpBAOzJCpfZ97m7A1QOF4w&amp;oe=6AB86337</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjrKQPDKF6/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg</t>
+          <t>Pé Suíno Kg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1785,11 +1761,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Bucho Bovino Kg 10,99</t>
+          <t>PÉ SUÍNO KG</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1798,32 +1774,36 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Ossobuco Bovino Kg</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
+          <t>Salsicha Hot Dog Seara kg</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1831,11 +1811,11 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>OSSOBUCO KG R$ 19,99</t>
+          <t>Salsicha Seara Kg</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>19.99</v>
+        <v>11.29</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -1844,90 +1824,94 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHPumiD&amp;_nc_oc=AdoQDQ39OzsVtc7qJaJU2Q1VEkagpGRqFl45_to_mdC0yojqyn5wfd_ked1qdEQlWTxIBfQ5sP5WRkON3-_SAS5b&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=I1Dc55Ok446xPrbhRRrWjQ&amp;_nc_ss=7a22e&amp;oh=00_AQJx5WRybJgYaSWsQIBbrX_x4vCd63nrjNTnv_QUrrQeEA&amp;oe=6AB84E3D</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Creme Dental Tripla Limpeza Completa Sorriso 70g</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sorriso</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>70g</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina Kg R$ 19,99</t>
+          <t>CREME DENTAL SORRISO TRIPLA LIMPEZA COMPLETA 70G</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.99</v>
+        <v>2.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída Bovina kg</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+          <t>Fralda Tripla Proteção Mega Huggies</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Huggies</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída Kg</t>
+          <t>FRALDA HUGGIES TRIPLA PROTEÇÃO MEGA PCT</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>22.99</v>
+        <v>32.9</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -1936,44 +1920,48 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Papel Higiênico Folha Dupla c/ 12 Atuallê</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Atuallê</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Costela Bovina Para Panela Kg</t>
+          <t>PAPEL HIGIÊNICO MILI ATUALLE FOLHA DUPLA 20M 12 ROLOS</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1982,44 +1970,48 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Rabada Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
+          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Duetto</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 12</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>RABADA BOVINA 25,99 KG</t>
+          <t>Papel Hig. Duetto - 20m Folha Dupla Neutro c/ 12 Rolos</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>25.99</v>
+        <v>13.99</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2028,44 +2020,44 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062554_18588741352067900_7879263675755426043_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTg5ODY3MjA0MTAwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=xZ19wjRz4rUQ7kNvwFqdY1G&amp;_nc_oc=Adpntyy-MVMXVUCksDu639eQXr1HoHLGclm6pa0OeatmMQqfZ1fMeAW4XgEDu_7NpALinCWbTU9go5jknhyJXUu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIeRmv179_-9Cwhh1HhN_8WvxtdmY7n7EfDr-BhAsJ-uA&amp;oe=6AB74420</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rabo Bovino Kg</t>
+          <t>Alho Kg</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>RABO BOVINO KG R$ 27,99</t>
+          <t>Alho Nacional R$ 2,49 A Cada 100g</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>27.99</v>
+        <v>2.49</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2074,12 +2066,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2083,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Ponta de Peito Sem Osso Bovina Kg</t>
+          <t>Laranja Pera Kg</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -2107,42 +2099,42 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Ponta de Peito S/ Osso Kg R$ 34,99</t>
+          <t>LARANJA PERA RIO</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>34.99</v>
+        <v>2.49</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Patinho Bovino kg</t>
+          <t>Batata Doce Kg</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -2153,11 +2145,11 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>PATINHO BOVINO KG R$ 36,99</t>
+          <t>BATATA DOCE KG</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36.99</v>
+        <v>2.59</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2166,29 +2158,29 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
+          <t>Laranja Pera Kg</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
@@ -2199,42 +2191,42 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Coxão Duro Kg R$ 36,99</t>
+          <t>Laranja Pera Rio Kg</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>36.99</v>
+        <v>2.59</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
+          <t>Laranja Pera Kg</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -2245,42 +2237,42 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Contra Filé C/ Osso Kg R$ 37,99</t>
+          <t>Laranja Kg</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>37.99</v>
+        <v>2.89</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Capa de Filé Bovina Kg</t>
+          <t>Banana Nanica Kg</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
@@ -2291,42 +2283,42 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Capa C. Filé Kg R$ 39,99</t>
+          <t>BANANA NANICA KG</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>39.99</v>
+        <v>2.99</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pé Suíno Kg</t>
+          <t>Melancia Kg</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -2337,11 +2329,11 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>PÉ SUÍNO KG</t>
+          <t>Melancia Kg</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2350,12 +2342,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2359,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Pé Suíno Kg</t>
+          <t>Banana Nanica Kg</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr"/>
@@ -2383,49 +2375,45 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>PÉ SUÍNO KG R$ 9,99</t>
+          <t>BANANA NANICA</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Salsicha Hot Dog Seara kg</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Seara</t>
-        </is>
-      </c>
+          <t>Laranja Pera Kg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -2433,11 +2421,11 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Salsicha Seara Kg</t>
+          <t>Laranja Nacional</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>11.29</v>
+        <v>3.49</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2446,29 +2434,29 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw5-1.fna.fbcdn.net/v/t51.82787-15/793278204_18198417139382122_7175832952461279571_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA4NDgzMTQzMjk5MDU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=3_jBGdaYUJ4Q7kNvwHkRxQ8&amp;_nc_oc=AdptgCFyM6I63Z2V-Q8VEHI7KWisnOJbzPJS_Ao9KuigXmeq9KRcB5bwg6sM72IfH1c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw5-1.fna&amp;_nc_gid=IGfm_V9ODVsN-6NVnYbo4g&amp;_nc_ss=7a22e&amp;oh=00_AQI4j0BF29mr1VcWChSbFiddtfgqxo-r0C6-fnw7JppO-Q&amp;oe=6AB734FD</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjLoIuA191/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana kg</t>
+          <t>Beterraba Kg</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -2479,61 +2467,57 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Fina Apimentada Kg R$ 16,99</t>
+          <t>Beterraba Kg</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>16.99</v>
+        <v>3.79</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mandioca Descascada Pão da Terra Congelada 1kg</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Pão Da Terra</t>
-        </is>
-      </c>
+          <t>Banana Nanica Kg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>MANDIOCA PÃO DA TERRA DESCASCADA CONGELADA 1KG</t>
+          <t>Banana Nanica Kg</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>5.79</v>
+        <v>3.79</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2542,98 +2526,90 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Sabonete Farnese 85g</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Farnese</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>85g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Sabonete Farnese 85g</t>
+          <t>Repolho Verde Kg</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.69</v>
+        <v>3.89</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Creme Dental Tripla Limpeza Completa Sorriso 70g</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Sorriso</t>
-        </is>
-      </c>
+          <t>Mandioca Kg</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>70g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>CREME DENTAL SORRISO TRIPLA LIMPEZA COMPLETA 70G</t>
+          <t>MANDIOCA KG</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2642,194 +2618,182 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://instagram.fgla3-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwH8Idod&amp;_nc_oc=Adp8KEH2YV1FiSuS38Ppk2v0-NCQrO0JObb2S5lHmF54cap1iNQgfnGgIcJguC8XXAmFlhMVFmYe4OI2gMpdNbGy&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgla3-2.fna&amp;_nc_gid=FJTkgESngppKY0GaNI2sSA&amp;_nc_ss=7a22e&amp;oh=00_AQIUpVg_N6RdRBq68VpbJB5FfyET8Dh1Httkyjcyty35nA&amp;oe=6AB85AAC</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Interno Intimus c/ 8</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Intimus</t>
-        </is>
-      </c>
+          <t>Banana Nanica Kg</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>c/ 8</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Interno Intimus c/8 unidades</t>
+          <t>Banana Nanica - Kg</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Creme Dental Total 12 Colgate 90g</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Colgate</t>
-        </is>
-      </c>
+          <t>Banana Nanica Kg</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>90g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Creme Dental Colgate Total 12 90g</t>
+          <t>Banana Nanica</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9.99</v>
+        <v>4.49</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Desodorante Aerosol Dove 150ml</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Dove</t>
-        </is>
-      </c>
+          <t>Batata Inglesa Kg</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Desodorante Dove 150ml</t>
+          <t>BATATA INGLESA Kg R$4,49</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>16.99</v>
+        <v>4.49</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Fralda Descartável Tripla Proteção Mega Huggies</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Huggies</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>Batata Inglesa Kg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES TRIPLA PROTEÇÃO MEGA PCT</t>
+          <t>BATATA KG</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>32.9</v>
+        <v>4.79</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2838,48 +2802,44 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Mili</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Mili</t>
-        </is>
-      </c>
+          <t>Banana Maçã Kg</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>PAPEL HIGIÊNICO MIILL ATUALLE FOLHA DUPLA 20M 12 ROLOS</t>
+          <t>BANANA MAÇÃ KG</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>9.99</v>
+        <v>4.89</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2888,48 +2848,44 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Duetto</t>
-        </is>
-      </c>
+          <t>Maçã Kg</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Papel Hig. Duetto - 20m Folha Dupla Neutro c/ 12 Rolos</t>
+          <t>MAÇÃ KG</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>13.99</v>
+        <v>4.89</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2938,62 +2894,58 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820155662_18588887581067900_8692089730644191238_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDczNjc1NjUwNTA2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Agn-ZZ2FoA4Q7kNvwG8YNNr&amp;_nc_oc=Adr0lsFsIQ4uVwEBoO7pxOrmIPoZb3FVxGMjcmdm8tizWm8UxFUMj4h8ZfbJvveqoYSOqDf_MtIJkSq-IQfIT1pz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQIMne1SNUMO8d09Qs6IHFw33JI0m3stS76CHpX4gsfOpQ&amp;oe=6AB85123</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla c/ 12 Duetto</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Duetto</t>
-        </is>
-      </c>
+          <t>Abacate Kg</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Papel higiênico Duetto 30m c/12 unidades</t>
+          <t>ABACATE KG</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>18.99</v>
+        <v>4.89</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820155662_18588887581067900_8692089730644191238_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDczNjc1NjUwNTA2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Agn-ZZ2FoA4Q7kNvwG8YNNr&amp;_nc_oc=Adr0lsFsIQ4uVwEBoO7pxOrmIPoZb3FVxGMjcmdm8tizWm8UxFUMj4h8ZfbJvveqoYSOqDf_MtIJkSq-IQfIT1pz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQIMne1SNUMO8d09Qs6IHFw33JI0m3stS76CHpX4gsfOpQ&amp;oe=6AB85123</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
@@ -3010,22 +2962,22 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Alho Kg</t>
+          <t>Batata Doce Kg</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Alho Nacional R$ 2,49 A Cada 100g</t>
+          <t>Batata Doce R$ 4,99 KG</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2.49</v>
+        <v>4.99</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3034,7 +2986,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3046,7 +2998,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3056,7 +3008,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Cebola Nacional Kg</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -3067,32 +3019,32 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>LARANJA PERA RIO Kg R$ 2,49</t>
+          <t>Cebola Nacional R$ 4,99 KG</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2.49</v>
+        <v>4.99</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3102,7 +3054,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Abacate Kg</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -3113,32 +3065,32 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Rio Kg 2,59</t>
+          <t>ABACATE</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3148,7 +3100,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Cebola Nacional Kg</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -3159,32 +3111,32 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Laranja Kg R$ 2,89</t>
+          <t>CEBOLA Kg R$4,99</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2.89</v>
+        <v>4.99</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3194,7 +3146,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Melancia Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -3205,11 +3157,11 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Melancia Kg 2,99</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2.99</v>
+        <v>5.49</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3218,19 +3170,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3240,7 +3192,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Banana Terra Kg</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
@@ -3251,11 +3203,11 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Laranja Nacional R$ 3,49 KG</t>
+          <t>BANANA TERRA KG</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>3.49</v>
+        <v>5.49</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3264,19 +3216,19 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3286,7 +3238,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Beterraba Kg</t>
+          <t>Batata Inglesa Kg</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -3297,11 +3249,11 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Beterraba Kg R$ 3,79</t>
+          <t>Batata Inglesa Kg</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>3.79</v>
+        <v>5.49</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3310,19 +3262,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3332,7 +3284,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
@@ -3343,32 +3295,32 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg R$ 3,79</t>
+          <t>MAMÃO FORMOSA</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>3.79</v>
+        <v>5.49</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3378,7 +3330,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -3389,32 +3341,32 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg R$ 3,89</t>
+          <t>CENOURA Kg R$5,49</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>3.89</v>
+        <v>5.49</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3424,7 +3376,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Mandioca Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -3435,11 +3387,11 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>MANDIOCA KG</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>3.99</v>
+        <v>5.59</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -3448,12 +3400,12 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fntr10-2.fna.fbcdn.net/v/t51.82787-15/818062270_18588741370067900_798043743598158665_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTA3OTkyNzc5NzI5NTIyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YLX86wEx0wAQ7kNvwFH2Jpy&amp;_nc_oc=AdrfOyOatZEQZ19sH1l23OPFlAz2qbsuJNrYYz0kGyriDFaQes6Db00ZT0FmdRoYCusP7faoR2A2lRBZllHSgIGn&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fntr10-2.fna&amp;_nc_gid=2VKVZoC6fUvY5_4_4t1TKw&amp;_nc_ss=7a22e&amp;oh=00_AQIuQqBIhfO_Tpj_vYkMwYj6269MDD8P5jeGs55lJquH9w&amp;oe=6AB7416C</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKhItjAG5/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
@@ -3470,14 +3422,10 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Cenoura Kg</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -3485,11 +3433,11 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica - Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3.99</v>
+        <v>5.59</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3498,7 +3446,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3510,7 +3458,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3520,22 +3468,22 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Kabotiã 1kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Abóbora Kabotiã R$ 3,99 KG</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3544,19 +3492,19 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3566,22 +3514,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde Kg</t>
+          <t>Maçã Kg</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde R$ 3,99 KG</t>
+          <t>Maçã Nacional Kg</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3590,19 +3538,19 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3612,7 +3560,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Beterraba Kg</t>
+          <t>Abacate Kg</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -3623,11 +3571,11 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Beterraba R$ 3,99 kg</t>
+          <t>Abacate Kg</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3636,19 +3584,19 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t51.82787-15/817191708_18378579520237813_1831888496483920375_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjAyNzg0MTE3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sWfomYKgDMUQ7kNvwFtR6Ue&amp;_nc_oc=Adr3WN5xWIGwHcJE4LWUi6UX7GUwMQs28Th-W_MThiwIatwwpO7oFSHLuZdIAkaP6Vs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJn2zsP7bx7vvljb8DhyAKkI3C5aPtLj8NyvFszjscWjw&amp;oe=6AB72BDC</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3658,7 +3606,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica Kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -3669,11 +3617,11 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica R$ 4,49 KG</t>
+          <t>Mamão Formosa - Kg</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3682,12 +3630,12 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3652,22 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Batata Doce Kg</t>
+          <t>Cenoura Kg</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Batata Doce R$ 4,99 KG</t>
+          <t>Cenoura R$ 5,99 KG</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3728,7 +3676,7 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/795341841_18378579571237813_1586404088888970145_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjUwMDk3MjgzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P6K8R92ap6UQ7kNvwFC-09s&amp;_nc_oc=AdoLx04Z7_eIgFfYckzkiOmFfYwcbKZLmpHl_nr-d_LHn5lLcCeMxQb4aWsoNywcD9w&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQJLeLFrliYtFglpiC0yGh6yvoYYWklqM5dVQ3dFJ0bXfw&amp;oe=6AB8785C</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3750,22 +3698,22 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Cebola Nacional Kg</t>
+          <t>Abacate Kg</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Cebola Nacional R$ 4,99 KG</t>
+          <t>Abacate</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3774,7 +3722,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -3786,7 +3734,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3796,7 +3744,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
+          <t>Banana da Terra Kg</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -3807,25 +3755,25 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>BATATA INGLESA Kg R$ 4,99</t>
+          <t>Banana Da Terra</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3790,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>Maçã Fuji Kg</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -3853,32 +3801,32 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>CENOURA Kg R$ 4,99</t>
+          <t>MAÇÃ FUJI Kg R$ 5,99</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/818517298_18096654869531849_3391688749308073253_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5Mjg5MDk2NjUyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=x60nvxbJNhYQ7kNvwFr_FHC&amp;_nc_oc=AdqhN3jZiOiSyRyvAiEA6UrhlAo-hCGnfXmg1EMSDpPp3aRcGXXb6iSBNIMXhhLDGdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLYyaWvL7Z2Yo-DMZQr6JD9u5su4qoHDe4lsrOkjD3lHA&amp;oe=6AB84AEE</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -3888,14 +3836,10 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Melão Amarelo Kg</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -3903,11 +3847,11 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Kg</t>
+          <t>Melão Amarelo Kg</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>5.49</v>
+        <v>6.69</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3916,19 +3860,19 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3938,7 +3882,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>Cebola Nacional Kg</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -3949,11 +3893,11 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg R$ 5,59</t>
+          <t>CEBOLA KG</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>5.59</v>
+        <v>6.89</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3962,19 +3906,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -3984,26 +3928,26 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Desconhecida Kg</t>
+          <t>Uva Niagara Vitória 500g</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Desconhecida</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>UVA VITÓRIA BDJ</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>5.59</v>
+        <v>6.99</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -4012,19 +3956,19 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,7 +3978,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
+          <t>Melão Amarelo Kg</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -4045,11 +3989,11 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg R$ 5,99</t>
+          <t>Melão Amarelo - Kg</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4058,19 +4002,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4080,7 +4024,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Maçã Kg</t>
+          <t>Mamão Formosa Kg</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
@@ -4091,11 +4035,11 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Maçã Nacional Kg 5,99</t>
+          <t>Mamão Formoso</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -4104,19 +4048,19 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,7 +4070,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
+          <t>Manga Tommy Kg</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -4137,32 +4081,32 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Abacate Kg 5,99</t>
+          <t>MANGA TOMMY</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4172,7 +4116,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
+          <t>Tomate Longa Vida Kg</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -4183,32 +4127,32 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa - Kg 5,99</t>
+          <t>TOMATE LV</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819164681_18096654857531849_956624900874370249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MTg3NTkxNDMwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GtyCen0QVMYQ7kNvwHlvlmo&amp;_nc_oc=AdqV36dZa0VZ4iryUZKXydKMgK2ASeQ3nkHu14NAaAwWCcfusXCan25siawPTNNWIm4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLhNAORuNQ5WhJgRO2quWJCnZF_ust5nh0hdivIcbtTMg&amp;oe=6AB86B92</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,7 +4162,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>Mexerica Kg</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -4229,32 +4173,32 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Cenoura KG</t>
+          <t>MEXERICA Kg R$ 6,99</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/795341841_18378579571237813_1586404088888970145_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjUwMDk3MjgzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P6K8R92ap6UQ7kNvwFx_fF2&amp;_nc_oc=Adr9Tg4AdBYc-Ag0pG4CEbHoNpnQBULdSOJ8hr7HsRIt84S4jc8vfwgMhiFmY0rjZt4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQITtkkK641O9ehU7qsvTOzf8X2qQuuJra5Rh-KFZu1EKA&amp;oe=6AB726DC</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/818517298_18096654869531849_3391688749308073253_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5Mjg5MDk2NjUyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=x60nvxbJNhYQ7kNvwFr_FHC&amp;_nc_oc=AdqhN3jZiOiSyRyvAiEA6UrhlAo-hCGnfXmg1EMSDpPp3aRcGXXb6iSBNIMXhhLDGdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLYyaWvL7Z2Yo-DMZQr6JD9u5su4qoHDe4lsrOkjD3lHA&amp;oe=6AB84AEE</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4264,7 +4208,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Abacate Kg</t>
+          <t>Tomate Longa Vida Kg</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -4275,32 +4219,32 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Abacate R$ 5,99 KG</t>
+          <t>TOMATE SALADETE Kg R$ 6,99</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/818517298_18096654869531849_3391688749308073253_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5Mjg5MDk2NjUyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=x60nvxbJNhYQ7kNvwFr_FHC&amp;_nc_oc=AdqhN3jZiOiSyRyvAiEA6UrhlAo-hCGnfXmg1EMSDpPp3aRcGXXb6iSBNIMXhhLDGdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLYyaWvL7Z2Yo-DMZQr6JD9u5su4qoHDe4lsrOkjD3lHA&amp;oe=6AB84AEE</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,22 +4254,18 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Banana da Terra Kg</t>
+          <t>Abacaxi Pérola un</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Banana Da Terra R$ 5,99 KG</t>
+          <t>ABACAXI UNIDADE</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>5.99</v>
+        <v>7.29</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4334,19 +4274,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820155662_18588887581067900_8692089730644191238_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDczNjc1NjUwNTA2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Agn-ZZ2FoA4Q7kNvwG8YNNr&amp;_nc_oc=Adr0lsFsIQ4uVwEBoO7pxOrmIPoZb3FVxGMjcmdm8tizWm8UxFUMj4h8ZfbJvveqoYSOqDf_MtIJkSq-IQfIT1pz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQIMne1SNUMO8d09Qs6IHFw33JI0m3stS76CHpX4gsfOpQ&amp;oe=6AB85123</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -4356,26 +4296,22 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos c/ 30 Fenix</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Fenix</t>
-        </is>
-      </c>
+          <t>Cebola Nacional Kg</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr"/>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>c/ 12</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>OVO VERMELHO FENIX C/12UN R$ 5,99</t>
+          <t>Cebola Kg</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>5.99</v>
+        <v>7.39</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -4384,19 +4320,19 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4406,22 +4342,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Melão Amarelo Kg</t>
+          <t>Uva Niagara 500g</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Melão Amarelo Kg R$ 6,69</t>
+          <t>Uva Vitória Bdj. 500g</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>6.69</v>
+        <v>7.99</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4430,19 +4366,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pnGGsDqG5SIQ7kNvwGv62Sl&amp;_nc_oc=AdpMorsMkEgdLtn3C7P5yMCYX7OHddh8HMCqdVJJ0vJwlwOrQtUtPPfQ11vf3koN-Q3KJq3qH8RvvCcKLYcu6Z3j&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQLV0VpKS1Y25BIURTb_UcjjF88r8cJjsyqFETFXgrcmNA&amp;oe=6AB87090</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4452,7 +4388,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Melão Amarelo Kg</t>
+          <t>Maçã Fuji Kg</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
@@ -4463,11 +4399,11 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Melão Amarelo - Kg 6,99</t>
+          <t>Maçã Fuji Kg</t>
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>6.99</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4476,12 +4412,12 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
@@ -4498,22 +4434,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Mamão Formosa Kg</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>Uva Niagara Vitória/Isís 500g</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Vitória/Isís</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Mamão Formoso R$ 6,99 KG</t>
+          <t>Uva Vitória/Isís Bandeja 500G</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4522,7 +4462,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4534,7 +4474,7 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4544,43 +4484,43 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Cebola Nacional Kg</t>
+          <t>Ovos Brancos c/ 30</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 20</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Cebola Kg R$ 7,39</t>
+          <t>OVO BCO GRANDE C/20UN R$ 8,99</t>
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>7.39</v>
+        <v>8.99</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/818517298_18096654869531849_3391688749308073253_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5Mjg5MDk2NjUyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=x60nvxbJNhYQ7kNvwFr_FHC&amp;_nc_oc=AdqhN3jZiOiSyRyvAiEA6UrhlAo-hCGnfXmg1EMSDpPp3aRcGXXb6iSBNIMXhhLDGdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQLYyaWvL7Z2Yo-DMZQr6JD9u5su4qoHDe4lsrOkjD3lHA&amp;oe=6AB84AEE</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4601,11 +4541,11 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Uva Vitória Bdj. 500g 7,99</t>
+          <t>UVA THOMPSON BDJ</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>7.99</v>
+        <v>9.49</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4614,19 +4554,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr6-1.cdninstagram.com/v/t51.82787-15/818062380_18195346117391764_7522837376708114625_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDY4MTg5MjkwMzQyNzEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8DeHXAiKiEcQ7kNvwFjdRtX&amp;_nc_oc=AdoBdE3tCLPWcwnVPHbOMDds-1wG9jaeNqW_HlBcE3wbCn-2_X_gZ6PlHCWDGIXuiN7VmCfuv-G3LGNJvYgcoRV2&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr6-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI9nqVhUhpzEjI_5JrVbI6C-9vku63B4D82awk2HpwJqw&amp;oe=6AB71F10</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820017005_18588887554067900_1261011816828767689_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDcwODY3OTg1ODQ2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8uUYFLoRcvAQ7kNvwFcZ56i&amp;_nc_oc=Adq18b-qrDR6b1Ucz7STxTHaQ2IdDPGEuq5otz-I0EdvRZEzqPUjrqEtgjVu1FxtmnFlH90wV6zhiFNIYYjGxa5_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQKFG12klwZTH6u9209xYr-oCZ4QgWWvqYh6zpj2Af8LKA&amp;oe=6AB873B6</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -4636,43 +4576,47 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Uva Niagara 500g</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
+          <t>Ovos Brancos c/ 30 Mantiqueira</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Mantiqueira</t>
+        </is>
+      </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>c/ 20</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>UVA VITORIA BDJ Bdj R$ 7,99</t>
+          <t>Ovos Brancos Mantiqueira c/20</t>
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>7.99</v>
+        <v>10.79</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/807284465_18096415970531849_5081126783308372488_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDAyNDk1NzgxOTUwMzEyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2u7hCrwuEZUQ7kNvwEe90Un&amp;_nc_oc=Ado4V3XtDe-7wnjjZBioPFvTfTI8PjhwvK7yFMUIAR48jjmChWg6gZK7CyF8tZlTqy4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQIZy1wwm88PpEU1uNP-rxiHyVNDiy6PZNPovXqQ6WNNDg&amp;oe=6AB7321E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwHVT5rR&amp;_nc_oc=AdqZly5NWfnPuwSoIr866kaIFiZgtcCF4Zn4V6gRwJbu1HvVo-Kb5nk60ZZvXOaEgZm2gC4WGyRBaSzCnLf6ZqrJ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=QANh0X8nlvuP-W3UjTLpag&amp;_nc_ss=7a22e&amp;oh=00_AQJ0RfvUeNZ-tqszQ4GDjan7kj5Ry04zZMVr9v6ke3y03w&amp;oe=6AB8663F</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,22 +4626,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Maçã Fuji Kg</t>
+          <t>Ovos Brancos c/ 30</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>c/ 30</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Maçã Fuji Kg R$ 8,29</t>
+          <t>OVOS BRANCO RED 30X1</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>11.99</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4706,12 +4650,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
@@ -4728,26 +4672,26 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Uva Niagara Vitória / Isís 500g</t>
+          <t>Ovo Mantiqueira c/ 20</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Vitória / Isís</t>
+          <t>Mantiqueira</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>c/ 20</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Uva Vitória/Isís Bandeja 500G R$ 8,99 UN</t>
+          <t>Ovo Mantiqueira Com 20 Unidades</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>8.99</v>
+        <v>12.99</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4756,7 +4700,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -4768,7 +4712,7 @@
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4778,22 +4722,26 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ovos Brancos c/ 30 Mantiqueira</t>
+          <t>Ovos Brancos c/ 30 Campo Verde</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Mantiqueira</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>Campo Verde</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>c/ 30</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Ovos Brancos Mantiqueira c/20 R$ 10,79</t>
+          <t>Ovos Brancos Campo Verde Bdj. 30 Und.</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>10.79</v>
+        <v>15.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4802,19 +4750,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftrc2-1.fna.fbcdn.net/v/t51.82787-15/813965899_18198416068382122_6577832328386159461_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3OTkyODc3ODE3NTQ4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hcWXJbnkbCgQ7kNvwGpYi57&amp;_nc_oc=AdoHZB5i_p_wLiTRrKKHxFDIHz7pXaZRq2HUxLBA8ZVbBRN2HmfEsrvMdIASA2ujabM6D59A6rlDhMvYbOls4BBc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftrc2-1.fna&amp;_nc_gid=KQoFhKF8J7HfRTcqeIukVQ&amp;_nc_ss=7a22e&amp;oh=00_AQLFKybbW02i4yKGEVnYir7NuDL--4LhCG6jC7b0MiXYxQ&amp;oe=6AB714BF</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjKgyxA7P-/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -4824,26 +4772,22 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Ovos Brancos c/ 30 Mantiqueira</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Mantiqueira</t>
-        </is>
-      </c>
+          <t>Alho Kg</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>c/ 20</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Ovo Mantiqueira Com 20 Unidades R$ 12,99 UN</t>
+          <t>ALHO IMPORTADO KG</t>
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>12.99</v>
+        <v>25.49</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4852,48 +4796,48 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ovos Brancos c/ 30 Campo Verde</t>
+          <t>Creme de Leite Italac 200g</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Campo Verde</t>
+          <t>Italac</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>c/ 30</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Ovos Brancos Campo Verde Bdj. 30 Und.</t>
+          <t>CREME DE LEITE ITALAC 10% DE GORDURA 200G</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>15.99</v>
+        <v>2.49</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4902,12 +4846,12 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -4924,26 +4868,26 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Creme de Leite Italac 200g</t>
+          <t>Cream Cheese Scala Pote 150g</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Italac</t>
+          <t>Scala</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>150g</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>CREME DE LEITE ITALAC 10% DE GORDURA 200G</t>
+          <t>CREAM CHEESE SCALA POTE 150G</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>2.49</v>
+        <v>8.49</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4952,7 +4896,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -4964,7 +4908,7 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4974,26 +4918,26 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cream Cheese Scala Pote 150g</t>
+          <t>Doce de Leite Frimesa 400g</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Scala</t>
+          <t>Frimesa</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>400g</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>CREAM CHEESE SCALA POTE 150G</t>
+          <t>Doce de Leite Frimesa 400g</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>8.49</v>
+        <v>8.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5002,19 +4946,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5024,26 +4968,26 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Doce de Leite Frimesa 400g</t>
+          <t>Margarina c/ Sal Qualy 500g</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Frimesa</t>
+          <t>Qualy</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Doce de Leite Frimesa 400g</t>
+          <t>MARGARINA QUALY CREMOSA C/SAL 1KG</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>8.99</v>
+        <v>14.9</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -5052,12 +4996,12 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -5069,31 +5013,31 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Margarina c/ Sal Qualy 500g</t>
+          <t>Limpador Multiuso Azulim 500ml</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Qualy</t>
+          <t>Azulim</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>MARGARINA QUALY CREMOSA C/SAL 1KG</t>
+          <t>LIMPADOR AZULIM MULTIUSO 500ML</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>14.9</v>
+        <v>2.49</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5102,7 +5046,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5124,26 +5068,22 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Limpador Multiuso Azulim 500ml</t>
+          <t>Vassoura Condor Madri com Cabo</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Azulim</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
+          <t>Condor</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>LIMPADOR AZULIM MULTIUSO 500ML</t>
+          <t>VASSOURA CONDOR MADRI C/ CABO</t>
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>2.49</v>
+        <v>7.99</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -5152,7 +5092,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5164,7 +5104,7 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5174,47 +5114,47 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Girando Sol 2L</t>
+          <t>Água Sanitária Ypê 2L</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Girando Sol</t>
+          <t>Ypê</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Girando Sol 500ml</t>
+          <t>ÁGUA SANITÁRIA YPÊ 2L</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>3.49</v>
+        <v>8.99</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -5224,40 +5164,40 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Limpador Multiuso Veja 500ml</t>
+          <t>Desinfetante Pinho Bril 2L</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Veja</t>
+          <t>Pinho Bril</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1.75L</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Limpador Multiuso Veja 500ml</t>
+          <t>DESINFETANTE PINHO BRIL 1,75L</t>
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -5274,22 +5214,26 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Vassoura Madri com Cabo Condor</t>
+          <t>Balde Sanremo 8L</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Condor</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>Sanremo</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>8L</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>VASSOURA CONDOR MADRI C/ CABO</t>
+          <t>BALDE SANREMO 8L REF:610/7</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>7.99</v>
+        <v>14.9</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5298,7 +5242,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5320,26 +5264,22 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Água Sanitária Ypê 2L</t>
+          <t>Rodo Condor Plástico com Cabo</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Ypê</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>2L</t>
-        </is>
-      </c>
+          <t>Condor</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>ÁGUA SANITÁRIA YPÊ 2L</t>
+          <t>RODO CONDOR PLÁSTICO C/ CABO</t>
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>8.99</v>
+        <v>16.9</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -5348,7 +5288,7 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -5360,50 +5300,50 @@
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 2L</t>
+          <t>Detergente Líquido Polylar 500ml</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Qboa</t>
+          <t>Polylar</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2L</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 2L</t>
+          <t>DETERGENTE POLYLAR 500ML</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>8.99</v>
+        <v>1.89</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -5415,31 +5355,31 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Desinfetante Pinho Bril 2L</t>
+          <t>Amaciante Mon Bijou 2L</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Pinho Bril</t>
+          <t>Mon Bijou</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>1.75L</t>
+          <t>5L</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>DESINFETANTE PINHO BRIL 1,75L</t>
+          <t>AMACIANTE MON BIJOU 5L</t>
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>12.99</v>
+        <v>18.9</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -5448,7 +5388,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -5465,31 +5405,31 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Balde Plástico Sanremo 8L</t>
+          <t>Sabão em Pó Apyce 1.6kg</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sanremo</t>
+          <t>Apyce</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>8L</t>
+          <t>4kg</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>BALDE SANREMO 8L REF:610/7</t>
+          <t>SABÃO EM PÓ APYCE MULTIAÇÃO 4KG</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5498,7 +5438,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5515,27 +5455,31 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Rodo Plástico com Cabo Condor</t>
+          <t>Amaciante Ypê 2L</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Condor</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr"/>
+          <t>Ypê</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>7L</t>
+        </is>
+      </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>RODO CONDOR PLÁSTICO C/ CABO</t>
+          <t>AMACIANTE YPÊ PRÓ ROUPAS E TECIDOS 7L</t>
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>16.9</v>
+        <v>29.9</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -5544,7 +5488,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -5556,36 +5500,36 @@
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Detergente Líquido Polylar 500ml</t>
+          <t>Arroz Branco Tipo 1 Fartura 5kg</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Polylar</t>
+          <t>Fartura</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>DETERGENTE POLYLAR 500ML</t>
+          <t>Arroz Fartura Pct. 5 Kg</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.89</v>
+        <v>18.99</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5594,134 +5538,134 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Esponja de Aço Bombril 45g</t>
+          <t>Achocolatado em Pó Toddy 750g</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Bombril</t>
+          <t>Toddy</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>45g</t>
+          <t>750g</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Esponja de Aço Bombril 45g</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>2.49</v>
+        <v>14.9</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Esponja Multiuso Scotch Brite Scotch-Brite c/ 4</t>
+          <t>Biscoito de Leite Marilan 300g</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Scotch-Brite</t>
+          <t>Marilan</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>c/ 4</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Esponja Multiuso Scotch-Brite leve 4, pague 3</t>
+          <t>BISCOITO MARILAN LEITE 300G</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
+          <t>Batata Inglesa Boa Kg</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Tixan Ypê</t>
+          <t>Boa</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5731,75 +5675,75 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Sabão em Pó Tixan Ypê Primavera ou Maciez 800g</t>
+          <t>BATATA PALHA BOA TRADICIONAL 800G</t>
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>12.99</v>
+        <v>19.9</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Girando Sol 2L</t>
+          <t>Farinha de Trigo Tipo 1 Anaconda 1kg</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Girando Sol</t>
+          <t>Anaconda</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Concentrado Girando Sol 1L</t>
+          <t>FARINHA DE TRIGO ANACONDA PREMIUM 1KG</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>16.99</v>
+        <v>4.79</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fngo4-2.fna.fbcdn.net/v/t51.82787-15/799767602_17911013115496981_3713644911402730838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MDY2MzQ4MDUwNTM1NTAyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FEZBNJeut10Q7kNvwEYnYvk&amp;_nc_oc=Adr1aeMrUqr2-diI-nlof7GpuUwu8hMRMvWShEWcQg-a9b3Whu1bH_zTVTdm-w421bYks_Fwnv1Ky-nWXcGzhiq_&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fngo4-2.fna&amp;_nc_gid=W_1-P3ZUrEG1we--HpT8cA&amp;_nc_ss=7a22e&amp;oh=00_AQKRT465U3sWTiqEXGqB0rtY3RC61lF8AJtb2Bc0e0Wr1Q&amp;oe=6AB72EF8</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddhr0rFpUsT/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -5811,31 +5755,31 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Mon Bijou 2L</t>
+          <t>Azeitona Verde Rivoli Sachê 100g</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Mon Bijou</t>
+          <t>Rivoli</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>5L</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE MON BIJOU 5L</t>
+          <t>AZEITONA VERDE RIVOLI SACHÊ 100G</t>
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>18.9</v>
+        <v>1.99</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5844,7 +5788,7 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -5861,31 +5805,31 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Pó Ápyce 1.6kg</t>
+          <t>Feijão Carioca Koblenz 1kg</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Ápyce</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ ÁPYCE MULTIAÇÃO 4KG</t>
+          <t>FEIJÃO CARIOCA KOBLENZ TIPO1 PCT 1KG</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>19.9</v>
+        <v>6.9</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5894,7 +5838,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -5911,31 +5855,31 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Ypê 2L</t>
+          <t>Pepino em Conserva Vale Fértil Vidro 300g</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Ypê</t>
+          <t>Vale Fértil</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>7L</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE YPÊ PRO ROUPAS E TECIDOS 7L</t>
+          <t>PEPINO VALE FÉRTIL CONSERVA VIDRO 300G</t>
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>29.9</v>
+        <v>8.99</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5944,7 +5888,7 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -5956,36 +5900,36 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Arroz Branco Tipo 1 Fartura 5kg</t>
+          <t>Amendoim Mape 1kg</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Fartura</t>
+          <t>Mape</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Arroz Fartura Pct. 5 Kg</t>
+          <t>Amendoim Mape 1 kg R$ 14,99 UN</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>18.99</v>
+        <v>14.99</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5994,12 +5938,12 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
@@ -6011,17 +5955,17 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Biscoito de Leite Marilan 300g</t>
+          <t>Tomate Longa Vida Val Kg</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Marilan</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -6031,11 +5975,11 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>BISCOITO MARILAN LEITE 300G</t>
+          <t>MOLHO DE TOMATE VAL TRADICIONAL SACHÊ 300G</t>
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>5.99</v>
+        <v>1.19</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -6044,7 +5988,7 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -6056,36 +6000,32 @@
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Achocolatado em Pó Toddy 750g</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Toddy</t>
-        </is>
-      </c>
+          <t>Kabotiã Kg</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>KABOTIÃ KG</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>14.9</v>
+        <v>2.49</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6094,48 +6034,44 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820024576_18588887509067900_982403312533858704_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDY3MzgzMzYwOTc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OcEFL1jGKJgQ7kNvwHV0v4G&amp;_nc_oc=AdozSNr49lngvE34GVScUePS1db0my0nlEq8CFpIcm2r_QGJ43-XSWezbuXUSyUCGtrWx2HibB6bbym1xMf99r9F&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQI8PYIM9fSrH-HA5gfiE_tTTmG0SwxBxIKngGh4PER-qw&amp;oe=6AB86029</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Batata Inglesa Boa Kg</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Boa</t>
-        </is>
-      </c>
+          <t>Abóbora Cabotia Kg</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>800g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>BATATA PALHA BOA TRADICIONAL 800G</t>
+          <t>Abóbora Cabotia - Kg</t>
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>19.9</v>
+        <v>3.49</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -6144,48 +6080,44 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Tipo 1 Anaconda 1kg</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Anaconda</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO ANACONDA PREMIUM 1KG</t>
+          <t>Repolho Verde - Kg</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>4.79</v>
+        <v>3.99</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6194,48 +6126,44 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Azeitona Verde Rivoli Sachê 100g</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Rivoli</t>
-        </is>
-      </c>
+          <t>Chuchu Kg</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE RIVOLI SACHÊ 100G</t>
+          <t>Chuchu - Kg</t>
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -6244,48 +6172,44 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwHvxYdb&amp;_nc_oc=AdopzBLJwEJuwERe0wRnHPmcTlrmtsKULzsOpZMnUIBBiPfXfcLdkNgz9PpMDuZ5o0bInqlQvxw0FbGnaLAP9D8X&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=LIw9X3YzyGoK5zXB1wD9bQ&amp;_nc_ss=7a22e&amp;oh=00_AQIO-429ny_4oDmbNt3dDAba2ypIxu6aX5He_VAVnKjqIQ&amp;oe=6AB87C25</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Feijão Carioca Koblenz 1kg</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Koblenz</t>
-        </is>
-      </c>
+          <t>Beterraba Kg</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>FEIJÃO CARIOCA KOBLENZ TIPO1 PCT 1KG</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>6.9</v>
+        <v>3.99</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6294,48 +6218,44 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817191708_18378579520237813_1831888496483920375_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MjAyNzg0MTE3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sWfomYKgDMUQ7kNvwFtgvkh&amp;_nc_oc=AdonnUGQFJa_vJyP-vydAabdzrUg6oM4xhZRBma_8TAngIqNt46zotK4p0uePGEoJn4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIH9e5dtEB-urba_meeOWwjd0QJ5FIuSABhiVR8oi0mTA&amp;oe=6AB8451C</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Pepino em Conserva Vale Fértil Vidro 300g</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>Vale Fértil</t>
-        </is>
-      </c>
+          <t>Abóbora Kabotiã Kg</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>PEPINO VALE FÉRTIL CONSERVA VIDRO 300G</t>
+          <t>Abóbora Kabotiã R$ 3,99 KG</t>
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -6344,12 +6264,12 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
@@ -6361,31 +6281,27 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Amendoim Mape 1kg</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Mape</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Amendoim Mape 1 kg R$ 14,99 UN</t>
+          <t>Repolho Verde R$ 3,99 KG</t>
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>14.99</v>
+        <v>3.99</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6310,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwF2Fj9j&amp;_nc_oc=Adp0fks8mIZ_M1QOH_CXLYxRuXB-XkE1PcLnLqddDXob8CQng2Ka1S3zjr_Aq2vhlUQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQJIij51HRsCZyDdZHTdjKubgRJcAYQ2ZQaHtFag930nhw&amp;oe=6AB720C2</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/811102543_18378579523237813_3031419386862289956_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzA0NTc1NTIxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=N7-DqWgUOLIQ7kNvwHr1kwf&amp;_nc_oc=AdpT4RgYXELylrdSvkQSwTi4p73pv9hhCeaHLU4_C9dIJYwlqyUXoqoX3oG1E0vxOOQ&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIn5ix8RWDoF74ygIS-MHfaV7P5SPQWdSnucmCv6ccwRA&amp;oe=6AB87242</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6406,57 +6322,53 @@
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Tomate Longa Vida Val Kg</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>Val</t>
-        </is>
-      </c>
+          <t>Repolho Verde Kg</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>MOLHO DE TOMATE VAL TRADICIONAL SACHÊ 300G</t>
+          <t>REPOLHO VERDE Kg R$3,99</t>
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.19</v>
+        <v>3.99</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6466,14 +6378,10 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Beterraba Kg</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -6481,32 +6389,32 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Cabotiá - Kg</t>
+          <t>BETERRABA Kg R$3,99</t>
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -6516,14 +6424,10 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Abobrinha Verde Kg</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -6531,32 +6435,32 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde - Kg</t>
+          <t>ABOBRINHA VERDE Kg R$4,99</t>
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fbhx7-1.fna.fbcdn.net/v/t51.82787-15/819097519_18096654881531849_8476421480070338992_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQ4MDE5MjIwMzE4NTU3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=H75Naf6QjXUQ7kNvwF4Ij0E&amp;_nc_oc=AdqCF_1icEu0XcTFlF1s3zsQ3ATHIUPthV-MBuAc0rwrt-mdqcdPh5Vq-Ar2nK-iH5I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbhx7-1.fna&amp;_nc_gid=kCVpZ3rbH8a5VMmT4w9pTA&amp;_nc_ss=7a22e&amp;oh=00_AQKwmhImhwapraPTzf5MV9jql9GpiHJg1Nm0KP23MwsXkQ&amp;oe=6AB8672E</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkliPykagf/</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6566,14 +6470,10 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Chuchu Desconhecida Kg</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Desconhecida</t>
-        </is>
-      </c>
+          <t>Morgote Kg</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -6581,11 +6481,11 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Chuchu - Kg</t>
+          <t>MORGOTE KG</t>
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>3.99</v>
+        <v>7.39</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6594,19 +6494,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/791245711_18195346138391764_4770455648624450009_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDY4MTkyODEzNTU1NDU3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=2YaQgjurvzUQ7kNvwGYJ07T&amp;_nc_oc=AdodQ1AQ7Q3NlVhsm_8jKgGiqlxhyXlLqdVCKliJsUdDmu2ucA6jlwH-4egE_5cc7bXHRh48_43z4-6dw1g7XWu9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ygzBz0Ywe9LowZrP8tLVmA&amp;_nc_ss=7a22e&amp;oh=00_AQI6QQxzns7FL69qHMgJwLJJXEVP5MvjT1SmjtMP2NIq0A&amp;oe=6AB72AA5</t>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/820155662_18588887581067900_8692089730644191238_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTQyNDczNjc1NjUwNTA2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Agn-ZZ2FoA4Q7kNvwG8YNNr&amp;_nc_oc=Adr0lsFsIQ4uVwEBoO7pxOrmIPoZb3FVxGMjcmdm8tizWm8UxFUMj4h8ZfbJvveqoYSOqDf_MtIJkSq-IQfIT1pz&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=AVZ-5erZqRdAz1e_-jmDzA&amp;_nc_ss=7a22e&amp;oh=00_AQIMne1SNUMO8d09Qs6IHFw33JI0m3stS76CHpX4gsfOpQ&amp;oe=6AB85123</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdhwBi9FzqN/</t>
+          <t>https://www.instagram.com/p/DdkY6pblNV6/</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -6616,7 +6516,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Mandioca Kg</t>
+          <t>Mexerica Kg</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr"/>
@@ -6627,11 +6527,11 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>MANDIOCA KG R$ 4,99</t>
+          <t>Mexerica</t>
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>4.99</v>
+        <v>7.49</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -6640,19 +6540,19 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/819002807_18096589505531849_6845121165630273042_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTA1ODM4NTg2NDE5NjgwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YxOG7b-pGt0Q7kNvwFW36db&amp;_nc_oc=AdoZDXqHPMtBK_3Io6y8l0JT82Z1rAckNsZMIA1Ljph4V43lml-OOXTSg693kmLietk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=GmTze4TpCJdVIMSOSAghOg&amp;_nc_ss=7a22e&amp;oh=00_AQINL9zTxXW9uPcxIyJNkKnjFmiLHo9iR3_64cPDwRHqeQ&amp;oe=6AB72DBA</t>
+          <t>https://instagram.fbri2-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sSltOgvS2BgQ7kNvwFIvFKy&amp;_nc_oc=Adqd_xwmqn7Zl-WJh8BXeg4voxJxa59PipWn2k9erpXWtkVRu6qVmYkjSRxBhk5ZsDg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri2-1.fna&amp;_nc_gid=TxvAvJq2tvZjuL9Vie7zdw&amp;_nc_ss=7a22e&amp;oh=00_AQIriV2EmDOCzPLAaSXqeR5gsUcBTjbRwnzuu3A7TYPxKA&amp;oe=6AB84BEC</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjFnTXR4LJ/</t>
+          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6662,22 +6562,22 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mexerica Kg</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+          <t>Frigideira Tramontina Alumínio Funda Loreto 24cm</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Tramontina</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Mexerica R$ 7,49 KG</t>
+          <t>FRIGIDEIRA TRAMONTINA ALUMÍNIO FUNDA LORETO 24CM</t>
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>7.49</v>
+        <v>58.9</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6686,62 +6586,62 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fsyd7-1.fna.fbcdn.net/v/t51.82787-15/817134815_18378579538237813_3119154607973293163_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5MTA3MDc0MzM4OTY4NjU1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=A__Ht02uioAQ7kNvwF8LdLN&amp;_nc_oc=AdppRlF4Tv1RIz-9np3ZAzT__-iFI7CDaxPwLqmpD1xHShojgYDopFzRI7KsKiQaWVM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd7-1.fna&amp;_nc_gid=gixzBPN6u9I9j5U0uw2r-A&amp;_nc_ss=7a22e&amp;oh=00_AQIxi0iM5MICHaBXixgXTFIqGLMPvevl_43psewxzetwsA&amp;oe=6AB732AC</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdjIgsmFhH0/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Alho Bello Kg</t>
+          <t>Bule Térmico Tramontina Aço Inox Exata 1L</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Tramontina</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Pão de Alho Bello 300g R$ 9,99</t>
+          <t>BULE TÉRMICO TRAMONTINA AÇO INOX EXATA 1L</t>
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>9.99</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fltn1-2.fna.fbcdn.net/v/t51.82787-15/817946486_18096415979531849_7272745187504948249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDAyNDk1NzEzOTkyNjYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=y3WYlEXp5RgQ7kNvwG2yiMi&amp;_nc_oc=AdpfF4VGGePEODeLU7_WSoakeok4-plWHMeiVuNmv6FqFL9V6CRgQ-92qvpEwyFuqBg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fltn1-2.fna&amp;_nc_gid=L_tSk_dtQ1ruLElAQaDGHg&amp;_nc_ss=7a22e&amp;oh=00_AQJa2uiYs_RmpcrwhnF0epukaiAH3BKA6dP76PqTnwduRQ&amp;oe=6AB71919</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdfaqNdEbFr/</t>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
       </c>
     </row>
@@ -6753,31 +6653,31 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Pão de Forma Eliane 500g</t>
+          <t>Mandioca Descascada Congelada Pão da Terra 1kg</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Eliane</t>
+          <t>Pão Da Terra</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>PÃO DE FORMA ELIANE 500G</t>
+          <t>MANDIOCA PÃO DA TERRA DESCASCADA CONGELADA 1KG</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>11.9</v>
+        <v>5.79</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6786,7 +6686,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFaH2lp&amp;_nc_oc=AdpyJeMrigBB09qNiHZR0CXNZK-lKjm6pfSEaz7RrX6FlRi0cpQksVdSEmXPonrUKYM&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQJEpjne-nGnrEpsKiGNfv481tb67jtErvi2r4uDW3kMDg&amp;oe=6AB713E4</t>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6803,43 +6703,93 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Forma Eliane 500g</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Eliane</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>PÃO DE FORMA ELIANE 500G</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/817946982_1379800230906601_5295536509048639891_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4ODU2MjM4NTQ3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=yOr4LTDHfosQ7kNvwFyieJa&amp;_nc_oc=Adpe5c10J9wsSd4WvY8JHcy5IqxFrhWIBxnYOLgkiCAQL4c5xCODd6mf6bgLxAqDw8A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQI0b2yvvbLqeGAQlkzGMvlDpfovluo0G7QVK1Nj91PTdg&amp;oe=6AB86564</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>Pet Shop</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Ração para Gatos Sabor Frango Catsy 10.1kg</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Ração Catsy Frango 10.1kg</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Catsy</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>10.1kg</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>RAÇÃO CATSY PRÉMIUM FRANGO 10,1KG</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="n">
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>RAÇÃO CATSY PREMIUM FRANGO 10,1KG</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwENuM-e&amp;_nc_oc=AdrjVbtS0rqmKghrtqyx0FaE_-M58ZJLQUUuL57LgR4Dk12v6EikPIL4_e_TTnCWaEA&amp;_nc_ad=z-m&amp;_nc_cid=1479&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=uiTlQNxlPXvF6K_nsLZVzw&amp;_nc_ss=7a22e&amp;oh=00_AQLapl2FgGhiF9m1IE7rFLLbuU3QfSux17oZD4hgEh7CZw&amp;oe=6AB71774</t>
-        </is>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-1.cdninstagram.com/v/t39.30808-6/818353570_1379800247573266_433889070997554690_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MDcwMzc4Nzk1MDAzMTY0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=n4IfvIz6DW4Q7kNvwHi95oI&amp;_nc_oc=Adq8Bltf8gKbbjmZ_DT1H08IoWcyAPx1mquA6VXZjJ0kUk8iDj67MsnobfTb2wXD9tc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-1.cdninstagram.com&amp;_nc_gid=3pp5A4iEpwnzkyFP_brW-Q&amp;_nc_ss=7a22e&amp;oh=00_AQK_HnfiMXFqMiNP9FnPQCVm1kN-IiMgNH1owT_swueJZg&amp;oe=6AB868F4</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/p/Ddh0_Y4EW_u/</t>
         </is>
@@ -6856,7 +6806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6938,32 +6888,32 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>18.615</v>
+        <v>5.4275</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2.49</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>39.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>9.631666666666666</v>
+        <v>7.346521739130435</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>18.99</v>
@@ -6972,57 +6922,38 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7.59</v>
+        <v>9.106666666666666</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1.99</v>
+        <v>2.89</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>18.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>9.106666666666666</v>
+        <v>7.997142857142856</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>9.156666666666666</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E8" s="6" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -7071,158 +7002,158 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bazar / Eletro</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>58.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Alcoólicos Diversos</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>19.9</v>
+        <v>2.99</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>19.9</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>2.99</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1.99</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>12.07571428571429</v>
+        <v>11.99</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17.91307692307692</v>
+        <v>7.423333333333333</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>11.815</v>
+        <v>17.945</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5.79</v>
+        <v>11.99</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5.79</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Hortifruti / Ovos</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>12.425</v>
+        <v>6.301666666666667</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>14.32333333333333</v>
+        <v>8.717500000000001</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Limpeza / Cuidados com a Casa</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>5.816829268292683</v>
+        <v>10.71</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>2.49</v>
@@ -7231,145 +7162,145 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laticínios / Leites e Derivados</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>8.717500000000001</v>
+        <v>17.6475</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.49</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>9.081111111111111</v>
+        <v>18.99</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.49</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>13.88125</v>
+        <v>14.9</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.89</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Arroz</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>18.99</v>
+        <v>12.945</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>18.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>13.59666666666667</v>
+        <v>4.79</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>5.99</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>4.79</v>
+        <v>8.217500000000001</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>8.217500000000001</v>
+        <v>1.19</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1.99</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>1.19</v>
+        <v>13.39857142857143</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.19</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Padaria / Congelados</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>4.790000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3.49</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7379,13 +7310,13 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>10.945</v>
+        <v>11.9</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>9.99</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,18 +474,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="620" customWidth="1" min="9" max="9"/>
+    <col width="634" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -582,7 +582,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwHUCvRk&amp;_nc_oc=Adp9cgInuLstQCPKtXorpx7HzXrGubRXL-D4Ue85i4gDbcoO-2rc6MhATNPthjqS7LXjx9KCC1dGT_DKVXoBKe9i&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQPNgW-1v9_dL-hlhX4DNag0yhZpUs_m0iPcPSqRuaBmuA&amp;oe=6AC9E140</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwHUCvRk&amp;_nc_oc=Adp9cgInuLstQCPKtXorpx7HzXrGubRXL-D4Ue85i4gDbcoO-2rc6MhATNPthjqS7LXjx9KCC1dGT_DKVXoBKe9i&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQPNgW-1v9_dL-hlhX4DNag0yhZpUs_m0iPcPSqRuaBmuA&amp;oe=6AC9E140</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwHUCvRk&amp;_nc_oc=Adp9cgInuLstQCPKtXorpx7HzXrGubRXL-D4Ue85i4gDbcoO-2rc6MhATNPthjqS7LXjx9KCC1dGT_DKVXoBKe9i&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQPNgW-1v9_dL-hlhX4DNag0yhZpUs_m0iPcPSqRuaBmuA&amp;oe=6AC9E140</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fsyd8-1.fna.fbcdn.net/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwHUCvRk&amp;_nc_oc=Adp9cgInuLstQCPKtXorpx7HzXrGubRXL-D4Ue85i4gDbcoO-2rc6MhATNPthjqS7LXjx9KCC1dGT_DKVXoBKe9i&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd8-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQPNgW-1v9_dL-hlhX4DNag0yhZpUs_m0iPcPSqRuaBmuA&amp;oe=6AC9E140</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Refrigerante Guaraná Zero 2L</t>
+          <t>Refrigerante Guaraná Refree Marajá Refree / Marajá 2L</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Guaraná Zero</t>
+          <t>Refree / Marajá</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>GUARANÁ 2L R$ 7,99</t>
+          <t>REFRIGERANTE MARAJÁ REFREE GUARANÁ 2L R$ 3,99</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwGNjNmT&amp;_nc_oc=AdrjWkEICK2rRSbHfnc3ju2hgZn4m8LrsupSb7UzqLReT3fDXh75Vzq7JIIEti0OMuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQO7QBriXcdB9p3ctbnLbQQpWO2zIAQZCjapc2xNRpBXJw&amp;oe=6AC85943</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t39.30808-6/839497726_1394496116103679_752042907428895696_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=NDAwMTQwMTUyNjEwMzEyMjI2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SqdSRvwYj2UQ7kNvwG74dR5&amp;_nc_oc=Adq5Txh6vVlIM0KnlK6AbChTlfE66P1m5BpzbmgWql18BljsGZbF4Y2y_TqdGiGtTqM&amp;_nc_ad=z-m&amp;_nc_cid=1753&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=Oo04JEwo16IYga0fUKSE1g&amp;_nc_ss=7a22e&amp;oh=00_AQOePklzM_IpmQKvh_sVjt7t9S2dkSDr6Kvjv7xj6JiN1w&amp;oe=6AC9CF53</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeH1XzXFSFa/</t>
         </is>
       </c>
     </row>
@@ -804,26 +804,26 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Refrigerante Coca-Cola 3L</t>
+          <t>Refrigerante Guaraná Kuat 2L</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kuat</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>3L</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>COCA COLA 3L R$ 11,99</t>
+          <t>GUARANÁ 2L R$ 7,99</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwGNjNmT&amp;_nc_oc=AdrjWkEICK2rRSbHfnc3ju2hgZn4m8LrsupSb7UzqLReT3fDXh75Vzq7JIIEti0OMuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQO7QBriXcdB9p3ctbnLbQQpWO2zIAQZCjapc2xNRpBXJw&amp;oe=6AC85943</t>
+          <t>https://instagram.fsyd13-1.fna.fbcdn.net/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwHZ3KsJ&amp;_nc_oc=AdoQLPkxnraJnC1vUO1JKBzPPY1rRAmlq8QkUxWvKSr9VzdxxZ_GI1TWUM0sx6uUs3AMF0l2tohe0K1uokdeZ0_a&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd13-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQNNSbY6AqRQsmdOgJ4F-hTZd-S8VG8mf9AU5p-cPUAAvA&amp;oe=6AC9AAC3</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -844,36 +844,36 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Frango Inteiro Canção kg</t>
+          <t>Refrigerante Coca-Cola 3L</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Canção</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>3L</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>FRANGO CANÇÃO C/ MIÚDOS INTEIRO KG 7,99 KG</t>
+          <t>COCA COLA 3L R$ 11,99</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -882,48 +882,48 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t39.30808-6/834466910_1392570522962905_8671838419842771591_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDEyNDY1MjEwNTk3ODA2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MH-nKfvv9i8Q7kNvwGY6VPq&amp;_nc_oc=Ado50_tSqARsjbapGp84iaKZ4wepYHtkixiZC4R6bL_-fG-iuB6JIhmwhHKKtBqKaqqghTI4fk1TyaAI3FDb_p5t&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=tvGiFGCsyweWHW4cGynm9A&amp;_nc_ss=7a22e&amp;oh=00_AQM8he_XtnXc8wsbcYwquZhpS8kGiyj6gZyR0dqIEDXXJA&amp;oe=6AC83C43</t>
+          <t>https://instagram.fsyd13-1.fna.fbcdn.net/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwHZ3KsJ&amp;_nc_oc=AdoQLPkxnraJnC1vUO1JKBzPPY1rRAmlq8QkUxWvKSr9VzdxxZ_GI1TWUM0sx6uUs3AMF0l2tohe0K1uokdeZ0_a&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd13-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQNNSbY6AqRQsmdOgJ4F-hTZd-S8VG8mf9AU5p-cPUAAvA&amp;oe=6AC9AAC3</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDTC1yD1DR/</t>
+          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Aves</t>
+          <t>Bebidas / Sucos e Diversos</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Coxinha da Asa de Frango Sadia kg</t>
+          <t>Erva Mate Uhde 500g</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Sadia</t>
+          <t>Uhde</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA SADIA 1 KG R$ 12,99</t>
+          <t>Erva UHDE 500g</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>12.99</v>
+        <v>9.99</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -932,12 +932,12 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwGNjNmT&amp;_nc_oc=AdrjWkEICK2rRSbHfnc3ju2hgZn4m8LrsupSb7UzqLReT3fDXh75Vzq7JIIEti0OMuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQO7QBriXcdB9p3ctbnLbQQpWO2zIAQZCjapc2xNRpBXJw&amp;oe=6AC85943</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DnL2K_XcCFcG3keqBaKWSQ&amp;_nc_ss=7a22e&amp;oh=00_AQMX0jCGaqnQb_jJxZTU9WzuTN7I8qefWtxI4DSAE_eYUQ&amp;oe=6AC9C80A</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeFxi_LjJTs/</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Costela Fina Kg</t>
+          <t>Fígado de Frango Kg</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -965,25 +965,25 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>COSTELA FINA KG</t>
+          <t>FÍGADO DE FRANGO KG 4,99</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>21.99</v>
+        <v>4.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fudi1-1.fna.fbcdn.net/v/t51.82787-15/837090916_18592734526067900_9176434905280445623_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI5NTQ0NzczNzQ5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=0M1i_dltiusQ7kNvwGFTrtL&amp;_nc_oc=AdoPKBVQbB1YIVTXRZoZPPc0NBqGvxl7-ztT9d2G-EUKKMv-9IgJYT0kguHKhXUPXxQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-1.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMYqaiQCvVlFAxCTlzOgWYS2Pk6ERqoJAzUgoKUSivlmQ&amp;oe=6AC9D99E</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Costela Grossa Bovina Kg</t>
+          <t>Dorso de Frango Kg</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>COSTELA GROSSA KG R$ 21,99</t>
+          <t>DORSO DE FRANGO KG 4,99</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>21.99</v>
+        <v>4.99</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwGNjNmT&amp;_nc_oc=AdrjWkEICK2rRSbHfnc3ju2hgZn4m8LrsupSb7UzqLReT3fDXh75Vzq7JIIEti0OMuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQO7QBriXcdB9p3ctbnLbQQpWO2zIAQZCjapc2xNRpBXJw&amp;oe=6AC85943</t>
+          <t>https://instagram.fudi1-1.fna.fbcdn.net/v/t51.82787-15/837090916_18592734526067900_9176434905280445623_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI5NTQ0NzczNzQ5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=0M1i_dltiusQ7kNvwGFTrtL&amp;_nc_oc=AdoPKBVQbB1YIVTXRZoZPPc0NBqGvxl7-ztT9d2G-EUKKMv-9IgJYT0kguHKhXUPXxQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-1.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMYqaiQCvVlFAxCTlzOgWYS2Pk6ERqoJAzUgoKUSivlmQ&amp;oe=6AC9D99E</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Corte Grill Kg</t>
+          <t>Pescoço de Frango Kg</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -1057,25 +1057,25 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CORTE GRILL KG</t>
+          <t>PESCOÇO DE FRANGO KG 5,99</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>27.99</v>
+        <v>5.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fudi1-1.fna.fbcdn.net/v/t51.82787-15/837090916_18592734526067900_9176434905280445623_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI5NTQ0NzczNzQ5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=0M1i_dltiusQ7kNvwGFTrtL&amp;_nc_oc=AdoPKBVQbB1YIVTXRZoZPPc0NBqGvxl7-ztT9d2G-EUKKMv-9IgJYT0kguHKhXUPXxQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-1.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMYqaiQCvVlFAxCTlzOgWYS2Pk6ERqoJAzUgoKUSivlmQ&amp;oe=6AC9D99E</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Corte Americano Kg</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -1103,45 +1103,49 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>CORTE AMERICANO KG</t>
+          <t>PÉ DE FRANGO KG 6,99</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>27.99</v>
+        <v>6.99</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fudi1-1.fna.fbcdn.net/v/t51.82787-15/837090916_18592734526067900_9176434905280445623_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI5NTQ0NzczNzQ5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=0M1i_dltiusQ7kNvwGFTrtL&amp;_nc_oc=AdoPKBVQbB1YIVTXRZoZPPc0NBqGvxl7-ztT9d2G-EUKKMv-9IgJYT0kguHKhXUPXxQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-1.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMYqaiQCvVlFAxCTlzOgWYS2Pk6ERqoJAzUgoKUSivlmQ&amp;oe=6AC9D99E</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ponta de Peito Sem Osso Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Coxa e Sobrecoxa de Frango Seara kg</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Seara</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1149,11 +1153,11 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PONTA DE PEITO S/ OSSO Kg R$ 33,99</t>
+          <t>Coxa com Sobrecoxa de Frango Seara - Kg</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>33.99</v>
+        <v>8.99</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1162,29 +1166,29 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DnL2K_XcCFcG3keqBaKWSQ&amp;_nc_ss=7a22e&amp;oh=00_AQMX0jCGaqnQb_jJxZTU9WzuTN7I8qefWtxI4DSAE_eYUQ&amp;oe=6AC9C80A</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeFxi_LjJTs/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1195,42 +1199,42 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>BISTECA DO C. FILÉ Kg R$ 34,99</t>
+          <t>Pé de Frango Kg</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>34.99</v>
+        <v>10.59</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://instagram.fqsr1-1.fna.fbcdn.net/v/t51.82787-15/834437253_18199935490382122_5042600354098242102_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTE4NzI4MDg5NDA2MzQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fbIkJiIYzlwQ7kNvwHrP613&amp;_nc_oc=AdpNI0RxXDpNuOIyZ7iTfaNS8GP3wyPnk-GzFYFEA9diClg7avLJoE3LT7RPxlcd5GY&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fqsr1-1.fna&amp;_nc_gid=sHboKfoP7ow071eX4N-JHQ&amp;_nc_ss=7a22e&amp;oh=00_AQMwINEKvuZaHLHhJvNy2HZc_hmwNKA0pm7eNWY4iK37XA&amp;oe=6AC9CBA8</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHEqH9gHOG/</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
+          <t>Moela de Frango Kg</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1241,57 +1245,61 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>COXÃO DURO Kg R$ 36,99</t>
+          <t>MOELA DE FRANGO KG 11,99</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>36.99</v>
+        <v>11.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://instagram.fudi1-1.fna.fbcdn.net/v/t51.82787-15/837090916_18592734526067900_9176434905280445623_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI5NTQ0NzczNzQ5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=0M1i_dltiusQ7kNvwGFTrtL&amp;_nc_oc=AdoPKBVQbB1YIVTXRZoZPPc0NBqGvxl7-ztT9d2G-EUKKMv-9IgJYT0kguHKhXUPXxQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-1.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMYqaiQCvVlFAxCTlzOgWYS2Pk6ERqoJAzUgoKUSivlmQ&amp;oe=6AC9D99E</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Contrafilé Bovino kg</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+          <t>Coxinha da Asa de Frango Sadia kg</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>CONTRA FILÉ C/ OSSO Kg R$ 36,99</t>
+          <t>COXINHA DA ASA SADIA 1 KG R$ 12,99</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>36.99</v>
+        <v>12.99</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1300,44 +1308,48 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://instagram.fsyd13-1.fna.fbcdn.net/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwHZ3KsJ&amp;_nc_oc=AdoQLPkxnraJnC1vUO1JKBzPPY1rRAmlq8QkUxWvKSr9VzdxxZ_GI1TWUM0sx6uUs3AMF0l2tohe0K1uokdeZ0_a&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd13-1.fna&amp;_nc_gid=u1hLDyz_KIu2v9DvcBQtuQ&amp;_nc_ss=7a22e&amp;oh=00_AQNNSbY6AqRQsmdOgJ4F-hTZd-S8VG8mf9AU5p-cPUAAvA&amp;oe=6AC9AAC3</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Capa de Filé Bovina Kg</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>Coxinhas das Asas de Frango Sadia 1kg</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sadia</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CAPA C. FILÉ Kg R$ 38,99</t>
+          <t>Coxinhas das Asas de Frango Sadia Pct. 1 Kg</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>38.99</v>
+        <v>12.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1346,12 +1358,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DnL2K_XcCFcG3keqBaKWSQ&amp;_nc_ss=7a22e&amp;oh=00_AQMX0jCGaqnQb_jJxZTU9WzuTN7I8qefWtxI4DSAE_eYUQ&amp;oe=6AC9C80A</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeFxi_LjJTs/</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1380,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fraldinha Bovina kg</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -1379,25 +1391,25 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>FRALDINHA KG</t>
+          <t>CORAÇÃO BOVINO KG 5,99</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>44.99</v>
+        <v>5.99</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1426,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Alcatra Bovina kg</t>
+          <t>Língua Bovina Kg</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1425,32 +1437,32 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ALCATRA COMPLETA KG</t>
+          <t>LÍNGUA BOVINA KG 6,99</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>47.99</v>
+        <v>6.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1460,7 +1472,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Maminha Bovina kg</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -1471,11 +1483,11 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>MAMINHA Kg R$ 47,99</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>47.99</v>
+        <v>6.99</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1484,19 +1496,19 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DnL2K_XcCFcG3keqBaKWSQ&amp;_nc_ss=7a22e&amp;oh=00_AQMX0jCGaqnQb_jJxZTU9WzuTN7I8qefWtxI4DSAE_eYUQ&amp;oe=6AC9C80A</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeFxi_LjJTs/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1506,7 +1518,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Picanha Bovina kg</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1517,25 +1529,25 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>PICANHA KG</t>
+          <t>CORAÇÃO BOVINO KG R$ 7,49</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt1-2.cdninstagram.com/v/t39.30808-6/834601076_1760369282763556_5207717056310317743_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=NDAwMDE3NDc0MjgzMzMwOTQ4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ZCeo-nnRbWkQ7kNvwGkPJMM&amp;_nc_oc=Ado6RaUsnfg9Gu05bg8ToLCfok2L6XQgwsIps05P7hThQC97fjeSKk8JprqcaON6pIc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPe6n8eH7tNK-yV7BLJpTz1PC4bL66owQizl3Eu6thjag&amp;oe=6AC85744</t>
+          <t>https://instagram.fkix3-1.fna.fbcdn.net/v/t51.82787-15/837659941_18098256167531849_7712358873364021178_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIzOTU2NjIxOTg3OTkxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=cCFDoDFKFPIQ7kNvwEqYtnD&amp;_nc_oc=Adrtx6bni32ckI_Y2jun26sp0vdSxEXgKWCVqLVNyokkiWsUVD8kIAxGTvtPWQNTaKQJ6Cdl0Cm1fEvIoRMq20FU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix3-1.fna&amp;_nc_gid=58m1B1pYacMbikRJfzhd0Q&amp;_nc_ss=7a22e&amp;oh=00_AQO-ziQh50IgITyb9YWUMUjc5Lm6vbE00vTosNUA0zm5vg&amp;oe=6AC9C657</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHQi-dxiXu/</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1559,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Peixe Tambaqui Inteiro Kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -1563,25 +1575,25 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>PEIXE TAMBAQUI INTEIRO KG</t>
+          <t>MOCOTÓ BOVINO KG 7,99</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>21.99</v>
+        <v>7.99</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1605,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Peixe Pintado Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1609,25 +1621,25 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>PEIXE PINTADO KG</t>
+          <t>FÍGADO BOVINO KG 7,99</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>34.99</v>
+        <v>7.99</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/834356564_1760369316096886_3931137326675684922_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTc3NjM0ODY5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Bl_7kJmj8D4Q7kNvwEbsVrU&amp;_nc_oc=AdqcYdeVzX0j9SvKRlDEF1TI9Izgx08wxMr8kASdccdJSsTDkFV9Wt48vP60kaxmK0A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQPDddGx8aF0edzYkV945FikKuFAjfaIghSPoVO9m34zCg&amp;oe=6AC85780</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1651,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1655,49 +1667,45 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA SUÍNA Kg R$ 11,99</t>
+          <t>MOCOTÓ BOVINO KG R$ 7,99</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://instagram.fkix3-1.fna.fbcdn.net/v/t51.82787-15/837659941_18098256167531849_7712358873364021178_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIzOTU2NjIxOTg3OTkxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=cCFDoDFKFPIQ7kNvwEqYtnD&amp;_nc_oc=Adrtx6bni32ckI_Y2jun26sp0vdSxEXgKWCVqLVNyokkiWsUVD8kIAxGTvtPWQNTaKQJ6Cdl0Cm1fEvIoRMq20FU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix3-1.fna&amp;_nc_gid=58m1B1pYacMbikRJfzhd0Q&amp;_nc_ss=7a22e&amp;oh=00_AQO-ziQh50IgITyb9YWUMUjc5Lm6vbE00vTosNUA0zm5vg&amp;oe=6AC9C657</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHQi-dxiXu/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Mercado Talismã</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Toscana Excelência kg</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Excelência</t>
-        </is>
-      </c>
+          <t>Bucho Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Kg</t>
@@ -1705,42 +1713,42 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>LINGUIÇA TOSCANA EXCELÊNCIA KG R$ 14,99</t>
+          <t>BUCHO BOVINO KG R$ 8,49</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.99</v>
+        <v>8.49</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-nrt6-1.cdninstagram.com/v/t39.30808-6/833185385_1760369306096887_7099181520724093249_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=NDAwMDE3NDc0MTg1MTgwOTg2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=5e0FndouOskQ7kNvwGNjNmT&amp;_nc_oc=AdrjWkEICK2rRSbHfnc3ju2hgZn4m8LrsupSb7UzqLReT3fDXh75Vzq7JIIEti0OMuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=xi0qkbWcp5VLyK7wowukrg&amp;_nc_ss=7a22e&amp;oh=00_AQO7QBriXcdB9p3ctbnLbQQpWO2zIAQZCjapc2xNRpBXJw&amp;oe=6AC85943</t>
+          <t>https://instagram.fkix3-1.fna.fbcdn.net/v/t51.82787-15/837659941_18098256167531849_7712358873364021178_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIzOTU2NjIxOTg3OTkxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=cCFDoDFKFPIQ7kNvwEqYtnD&amp;_nc_oc=Adrtx6bni32ckI_Y2jun26sp0vdSxEXgKWCVqLVNyokkiWsUVD8kIAxGTvtPWQNTaKQJ6Cdl0Cm1fEvIoRMq20FU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix3-1.fna&amp;_nc_gid=58m1B1pYacMbikRJfzhd0Q&amp;_nc_ss=7a22e&amp;oh=00_AQO-ziQh50IgITyb9YWUMUjc5Lm6vbE00vTosNUA0zm5vg&amp;oe=6AC9C657</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeDecAmEcJC/</t>
+          <t>https://www.instagram.com/p/DeHQi-dxiXu/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Toscana kg</t>
+          <t>Bucho Bovino Kg</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -1751,42 +1759,42 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA FINA APIMENTADA Kg R$ 16,99</t>
+          <t>BUCHO BOVINO KG 8,99</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>16.99</v>
+        <v>8.99</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/837659412_18098131412531849_5722741872531770706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=NDAwMDQ2ODAxMTU0MTk3MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=kQx8_QkdxcgQ7kNvwFZsz2l&amp;_nc_oc=AdrhBSGigQ4AP0Qkcl8XgzmICemr8AD1_hPkkPi7O94Lp8rQlmNAEN1KaMXARYHMNzU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQP6zlliRIcig6KGSs7SiArVX_c77xaHqVyr5gJ2Di8MDA&amp;oe=6AC8483F</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Laranja Pera Kg</t>
+          <t>Recorte Bovino Kg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1797,42 +1805,42 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>LARANJA PERA Kg R$ 2,49</t>
+          <t>RECORTE BOVINO KG 8,99</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.49</v>
+        <v>8.99</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/834834403_18098131421531849_6982381203410144535_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=NDAwMDQ2ODAxMjkwMDkyNjAzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=F4S4C6tTLlwQ7kNvwHcGeLV&amp;_nc_oc=Ado2ck8YGx9g6saGJ_tiZHMwoYYvUi6yUlRZjKoAJGfFLpN22sp6IRLDdsqbuQBaf3Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQNrW-_DtL05xFadwbpLbYj7z7SRNxTN_9FoVBjpxzXKqA&amp;oe=6AC82442</t>
+          <t>https://instagram.fudi1-2.fna.fbcdn.net/v/t51.82787-15/834678160_18592734505067900_5725473358583270079_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTIyOTI3MjUzMDA3MTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EvxtLOOxI7IQ7kNvwGtWPTM&amp;_nc_oc=AdrxXVa22RQvcaOPpgxjNQz02Cg9xpJOThpXaR3vWjjPUJjVu9VDUiWfu3wQE68p8JU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fudi1-2.fna&amp;_nc_gid=2RFllZv6mHjSm4fkZo1RSA&amp;_nc_ss=7a22e&amp;oh=00_AQMEwFCqUPLV2Kl66pdCmjx01Q_O8jvkFy8vsK4UWyy-wg&amp;oe=6AC9D79A</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHOOAVjAjo/</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Cenoura Kg</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -1843,42 +1851,42 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>CENOURA Kg R$ 4,49</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>4.49</v>
+        <v>8.99</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/834834403_18098131421531849_6982381203410144535_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=NDAwMDQ2ODAxMjkwMDkyNjAzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=F4S4C6tTLlwQ7kNvwHcGeLV&amp;_nc_oc=Ado2ck8YGx9g6saGJ_tiZHMwoYYvUi6yUlRZjKoAJGfFLpN22sp6IRLDdsqbuQBaf3Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQNrW-_DtL05xFadwbpLbYj7z7SRNxTN_9FoVBjpxzXKqA&amp;oe=6AC82442</t>
+          <t>https://instagram.fqsr1-1.fna.fbcdn.net/v/t51.82787-15/834437253_18199935490382122_5042600354098242102_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTE4NzI4MDg5NDA2MzQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fbIkJiIYzlwQ7kNvwHrP613&amp;_nc_oc=AdpNI0RxXDpNuOIyZ7iTfaNS8GP3wyPnk-GzFYFEA9diClg7avLJoE3LT7RPxlcd5GY&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fqsr1-1.fna&amp;_nc_gid=sHboKfoP7ow071eX4N-JHQ&amp;_nc_ss=7a22e&amp;oh=00_AQMwINEKvuZaHLHhJvNy2HZc_hmwNKA0pm7eNWY4iK37XA&amp;oe=6AC9CBA8</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHEqH9gHOG/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Banana Terra Kg</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1889,42 +1897,42 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>BANANA TERRA Kg R$ 5,99</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/834834403_18098131421531849_6982381203410144535_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=NDAwMDQ2ODAxMjkwMDkyNjAzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=F4S4C6tTLlwQ7kNvwHcGeLV&amp;_nc_oc=Ado2ck8YGx9g6saGJ_tiZHMwoYYvUi6yUlRZjKoAJGfFLpN22sp6IRLDdsqbuQBaf3Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQNrW-_DtL05xFadwbpLbYj7z7SRNxTN_9FoVBjpxzXKqA&amp;oe=6AC82442</t>
+          <t>https://instagram.fqsr1-1.fna.fbcdn.net/v/t51.82787-15/834437253_18199935490382122_5042600354098242102_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTE4NzI4MDg5NDA2MzQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fbIkJiIYzlwQ7kNvwHrP613&amp;_nc_oc=AdpNI0RxXDpNuOIyZ7iTfaNS8GP3wyPnk-GzFYFEA9diClg7avLJoE3LT7RPxlcd5GY&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fqsr1-1.fna&amp;_nc_gid=sHboKfoP7ow071eX4N-JHQ&amp;_nc_ss=7a22e&amp;oh=00_AQMwINEKvuZaHLHhJvNy2HZc_hmwNKA0pm7eNWY4iK37XA&amp;oe=6AC9CBA8</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHEqH9gHOG/</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Tomate Longa Vida Kg</t>
+          <t>Coração Bovino Kg</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -1935,57 +1943,57 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>TOMATE Kg R$ 7,99</t>
+          <t>Coração Bovino</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/834834403_18098131421531849_6982381203410144535_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=NDAwMDQ2ODAxMjkwMDkyNjAzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=F4S4C6tTLlwQ7kNvwHcGeLV&amp;_nc_oc=Ado2ck8YGx9g6saGJ_tiZHMwoYYvUi6yUlRZjKoAJGfFLpN22sp6IRLDdsqbuQBaf3Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQNrW-_DtL05xFadwbpLbYj7z7SRNxTN_9FoVBjpxzXKqA&amp;oe=6AC82442</t>
+          <t>https://instagram.fqsr1-1.fna.fbcdn.net/v/t51.82787-15/834437253_18199935490382122_5042600354098242102_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMTE4NzI4MDg5NDA2MzQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fbIkJiIYzlwQ7kNvwHrP613&amp;_nc_oc=AdpNI0RxXDpNuOIyZ7iTfaNS8GP3wyPnk-GzFYFEA9diClg7avLJoE3LT7RPxlcd5GY&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fqsr1-1.fna&amp;_nc_gid=sHboKfoP7ow071eX4N-JHQ&amp;_nc_ss=7a22e&amp;oh=00_AQMwINEKvuZaHLHhJvNy2HZc_hmwNKA0pm7eNWY4iK37XA&amp;oe=6AC9CBA8</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeHEqH9gHOG/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Uva Niagara 500g</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>UVA THOMPSON BDJ R$ 8,99</t>
+          <t>Fígado Bovino Kg</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1994,48 +2002,44 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/v/t51.82787-15/834834403_18098131421531849_6982381203410144535_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=NDAwMDQ2ODAxMjkwMDkyNjAzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=F4S4C6tTLlwQ7kNvwHcGeLV&amp;_nc_oc=Ado2ck8YGx9g6saGJ_tiZHMwoYYvUi6yUlRZjKoAJGfFLpN22sp6IRLDdsqbuQBaf3Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_gid=VJxpQSSDX6hcSthghGqzMA&amp;_nc_ss=7a22e&amp;oh=00_AQNrW-_DtL05xFadwbpLbYj7z7SRNxTN_9FoVBjpxzXKqA&amp;oe=6AC82442</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DnL2K_XcCFcG3keqBaKWSQ&amp;_nc_ss=7a22e&amp;oh=00_AQMX0jCGaqnQb_jJxZTU9WzuTN7I8qefWtxI4DSAE_eYUQ&amp;oe=6AC9C80A</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DeEhIq1kQvA/</t>
+          <t>https://www.instagram.com/p/DeFxi_LjJTs/</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Água Sanitária Girando Sol 1L</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Girando Sol</t>
-        </is>
-      </c>
+          <t>Mocotó Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>ÁGUA SANITÁRIA GIRANDO SOL 1L 3,49 UND</t>
+          <t>Mocotó Bovino Kg</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>3.49</v>
+        <v>9.99</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2044,48 +2048,44 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fbne6-1.fna.fbcdn.net/v/t39.30808-6/834466910_1392570522962905_8671838419842771591_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAwMDEyNDY1MjEwNTk3ODA2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MH-nKfvv9i8Q7kNvwGY6VPq&amp;_nc_oc=Ado50_tSqARsjbapGp84iaKZ4wepYHtkixiZC4R6bL_-fG-iuB6JIhmwhHKKtBqKaqqghTI4fk1TyaAI3FDb_p5t&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbne6-1.fna&amp;_nc_gid=tvGiFGCsyweWHW4cGynm9A&amp;_nc_ss=7a22e&amp;oh=00_AQM8he_XtnXc8wsbcYwquZhpS8kGiyj6gZyR0dqIEDXXJA&amp;oe=6AC83C43</t>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/833603439_18196853824391764_4972405880922350855_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=NDAwMDgyMTc1MjU2OTMwNDMwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=VhOzCBX7PhAQ7kNvwH1fAdu&amp;_nc_oc=AdocCE5EyDPU8_klDLq2ucnyVH9vObiTGyd1y6KTuJBSwZYRAvi8FKr0VHDDfdzwHSk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_h